--- a/excel_model/Nestle_Data_Foundation.xlsx
+++ b/excel_model/Nestle_Data_Foundation.xlsx
@@ -12,7 +12,10 @@
     <sheet name="Segment_Data" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="Category_Data" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="H1_2024_Phasing" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="Group_PL_CF" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Income_Statement" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Cash_Flow_Statement" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="Assumptions_FY2025" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="Budget_FY2025_PL_CF" sheetId="8" state="visible" r:id="rId10"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,342 +26,8 @@
 </workbook>
 </file>
 
-<file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <authors>
-    <author>Unknown Author</author>
-  </authors>
-  <commentList>
-    <comment ref="B7" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Estimated: back-calculated from Nestlé's disclosed +19.2% YoY change to FY2022's CHF 1.0bn (FY2021 full Financial Statements report the precise figure; condensed press release only gives % change). Source: Nestlé FY2022 full-year results press release.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B9" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Estimated: back-calculated from Nestlé's disclosed +330bps YoY change to FY2022's 24.2% (FY2021 full Financial Statements report the precise figure). Source: Nestlé FY2022 full-year results press release.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B11" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Source: Nestlé FY2021 full-year results press release (17 Feb 2022) — 'Net profit grew by 38.2% to CHF 16.9 billion'.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B13" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Source: Nestlé FY2021 full-year results press release — 'Earnings per share increased ... to CHF 6.06'.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B15" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Source: Nestlé FY2021 full-year results press release — 'Cash generated from operations decreased from CHF 17.2 billion to CHF 16.6 billion'.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B16" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Source: Nestlé FY2021 full-year results press release — 'Free cash flow decreased ... to CHF 8.7 billion'.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B20" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Source: Nestlé FY2022 full-year results press release — 'Net debt was CHF 48.2 billion ... compared to CHF 32.9 billion at December 31, 2021'.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C7" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Source: Nestlé FY2022 full-year results press release (16 Feb 2023) — 'Net financial expenses increased by 19.2% to CHF 1.0 billion'.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C9" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Source: Nestlé FY2022 full-year results press release — 'Group reported tax rate increased by 330 basis points to 24.2%'.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C11" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Source: Nestlé FY2022 full-year results press release (16 Feb 2023) — 'Net profit decreased by 45.2% to CHF 9.3 billion'.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C13" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Source: Nestlé FY2022 full-year results press release — 'earnings per share decreased ... to CHF 3.42'.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C16" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Source: Nestlé FY2022 full-year results press release — 'Free cash flow decreased from CHF 8.7 billion to CHF 6.6 billion'.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C20" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Source: Nestlé FY2022 full-year results press release — 'Net debt was CHF 48.2 billion as at December 31, 2022'.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D7" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Source: Nestlé FY2024 full-year results press release (13 Feb 2025) — prior-year comparative, 'CHF 1.5 billion from CHF 1.4 billion'.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D9" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Source: Nestlé FY2024 full-year results press release — prior-year comparative, 'compared to 18.2% in the prior year'.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D11" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Source: Nestlé FY2024 full-year results press release (13 Feb 2025), FY2023 comparative column — CHF 11,209 million.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D13" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Source: Nestlé FY2024 full-year results press release, FY2023 comparative column — CHF 4.24.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D15" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Source: Nestlé FY2024 full-year results press release, FY2023 comparative — 'CHF 19.6 billion from CHF 19.2 billion in 2023'.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D16" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Source: Nestlé FY2024 full-year results press release, FY2023 comparative — CHF 10,403 million (includes CHF 0.6bn one-off Prometheus Biosciences stake disposal proceeds).</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D20" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Source: Nestlé FY2024 full-year results press release, FY2023 comparative — CHF 49.6 billion.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E7" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Source: Nestlé FY2024 full-year results press release (13 Feb 2025) — 'Net financial expenses increased to CHF 1.5 billion'.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E9" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Source: Nestlé FY2024 full-year results press release — 'Group reported tax rate was 25.0%'.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E11" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Source: Nestlé FY2024 full-year results press release (13 Feb 2025) — Net profit CHF 10,884 million.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E13" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Source: Nestlé FY2024 full-year results press release — Basic EPS CHF 4.19.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E15" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Source: Nestlé FY2024 full-year results press release — 'Cash generated from operations increased to CHF 19.6 billion'.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E16" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Source: Nestlé FY2024 full-year results press release — Free cash flow CHF 10,666 million.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E20" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Source: Nestlé FY2024 full-year results press release — 'Net debt was CHF 56.0 billion as at December 31, 2024'.</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="212">
   <si>
     <t xml:space="preserve">Nestlé FP&amp;A Case Study — Data Foundation</t>
   </si>
@@ -381,7 +50,16 @@
     <t xml:space="preserve">• H1_2024_Phasing — Half-year split of segment sales &amp; UTOP for 2023 and 2024 (H1 actual, H2 derived as FY minus H1) — the base for building monthly/quarterly phasing in the Budget Model step.</t>
   </si>
   <si>
-    <t xml:space="preserve">• Group_PL_CF — Simplified Group-level Income Statement (Sales → UTOP → simplified PBT → Net Profit) and Free Cash Flow bridge, FY2021–FY2024. Added to support a simplified 'P&amp;L + FCF' Budget Model (no detailed Balance Sheet), since Balance Sheet and Cash Flow are only disclosed by Nestlé at Group level, not by segment.</t>
+    <t xml:space="preserve">• Income_Statement — Full consolidated Income Statement, line by line (Sales, Other revenue, COGS, Distribution expenses, Marketing &amp; admin expenses, R&amp;D costs, Other trading/operating income &amp; expenses, Financial income/expense, Income from associates &amp; JVs, Taxes, NCI), FY2021–FY2024, with every subtotal (UTOP, Trading Operating Profit, Operating Profit, PBT, Profit for the Year, Net Profit) computed by formula from the disclosed line items above it — never hardcoded.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Cash_Flow_Statement — Full consolidated Statement of Cash Flows, line by line across Operating, Investing and Financing activities plus the cash reconciliation and a Free Cash Flow memo, FY2021–FY2024, with every subtotal (Cash Generated from Operations, Operating/Investing/Financing Cash Flow) computed by formula.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Assumptions_FY2025 — FY2025 budget assumptions (organic growth, FX, UTOP margin, tax rate, FCF margin, share count), each cited to Nestlé's own FY2025 guidance where available, or flagged as an explicit own-assumption where not. Yellow cells are the editable scenario levers.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Budget_FY2025_PL_CF — FY2025 Budget vs FY2024 Actual (Sales → UTOP → PBT → Net Profit, plus Free Cash Flow), fully driven by the Assumptions_FY2025 sheet. Built from guidance disclosed BEFORE FY2025 actual results were known — sets up Step 4 (Variance Analysis) of this project.</t>
   </si>
   <si>
     <t xml:space="preserve">Data sources</t>
@@ -414,7 +92,7 @@
     <t xml:space="preserve">• All monetary figures are in CHF million unless stated otherwise. Blue cells = hardcoded inputs sourced from the press releases above. Black cells = formulas (margins, YoY growth, H2 derivation).</t>
   </si>
   <si>
-    <t xml:space="preserve">• Group_PL_CF sheet: FY2021 Net Financial Expenses and Tax Rate are back-calculated from a disclosed YoY % change (flagged in cell comments) since the condensed press release doesn't state the exact FY2021 figure. FY2022's Operating Cash Flow is left blank (n/a) because Nestlé disclosed it on a different basis that year ('before working capital changes') and isn't directly comparable — see sheet footnotes.</t>
+    <t xml:space="preserve">• Income_Statement / Cash_Flow_Statement sheets: sourced from Nestlé's full Financial Statements documents (not the condensed press releases used for Segment_Data/Category_Data) for full line-item detail. FY2022's 'Cash generated from operations' section reflects the "Decrease/(increase) in working capital" and "Variation of other operating assets and liabilities" lines as disclosed that year. The 'Free Cash Flow (derived)' row will not tie exactly to Nestlé's own reported FCF figure — this is flagged on the Cash_Flow_Statement sheet, not hidden.</t>
   </si>
   <si>
     <t xml:space="preserve">Nestlé — Segment Sales &amp; Profitability, FY2021–FY2024 (CHF m unless %)</t>
@@ -600,95 +278,405 @@
     <t xml:space="preserve">Source: Nestlé Half-Year Results 2024 press release (H1 actuals); FY figures linked from Segment_Data sheet (green = cross-sheet link). Total Group UTOP row uses reported Group figures directly (see Segment_Data note on unallocated central costs).</t>
   </si>
   <si>
-    <t xml:space="preserve">Nestlé — Simplified Group Income Statement &amp; Free Cash Flow, FY2021–FY2024 (CHF m unless % or per-share)</t>
+    <t xml:space="preserve">Nestlé Group — Consolidated Income Statement, FY2021–FY2024 (CHF million unless per-share)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Line Item</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FY2021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FY2022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FY2023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FY2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other revenue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cost of goods sold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Distribution expenses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marketing and administration expenses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Research and development costs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Underlying Trading Operating Profit (UTOP)*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other trading income</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other trading expenses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trading Operating Profit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other operating income</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other operating expenses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operating Profit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Financial income</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Financial expense</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Net Financial Income/(Expense)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Profit Before Taxes, Associates and Joint Ventures</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Income from associates and joint ventures</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taxes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Profit for the Year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Of which: non-controlling interests</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Net Profit (attributable to shareholders of the parent)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UTOP Margin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trading Operating Profit Margin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operating Profit Margin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Net Profit Margin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Effective Tax Rate (Taxes ÷ PBT)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Basic earnings per share (CHF)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diluted earnings per share (CHF)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">* "Underlying Trading Operating Profit" (UTOP) is Nestlé's own key profitability KPI. It is not printed as an explicit line in the statutory income statement, but is fully derivable as Sales + Other revenue − Cost of goods sold − Distribution expenses − Marketing &amp; administration expenses − Research &amp; development costs (computed here as a formula, not hardcoded) — it ties exactly to the UTOP figures Nestlé discloses separately (e.g. FY2024: CHF 15,704m, 17.2% margin).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sources: Nestlé Financial Statements 2024 (published 13-Feb-2025) for FY2024 and FY2023 — https://www.nestle.com/sites/default/files/2025-02/2024-financial-statements-en.pdf ; Nestlé Financial Statements 2022 (published 16-Feb-2023) for FY2022 and FY2021 — https://www.nestle.com/sites/default/files/2023-02/2022-financial-statements-en.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shaded rows are subtotals computed by formula from the line items above them — never hardcoded — so every number here is traceable back to a disclosed line item.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FY2021's unusually high Net Profit (CHF 16,905m) and 'Income from associates and joint ventures' (CHF 8,651m) reflect the one-off gain on Nestlé's disposal of part of its L'Oréal stake in 2021, not a recurring item.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nestlé Group — Consolidated Statement of Cash Flows, FY2021–FY2024 (CHF million)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OPERATING ACTIVITIES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operating Profit (linked from Income_Statement)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Depreciation and amortization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Impairment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Net result on disposal of businesses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other non-cash items of income and expense</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cash Flow Before Changes in Operating Assets and Liabilities</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Decrease/(increase) in working capital</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Variation of other operating assets and liabilities</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cash Generated from Operations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interest paid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interest and dividends received</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taxes paid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dividends and interest from associates and joint ventures</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operating Cash Flow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INVESTING ACTIVITIES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Capital expenditure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Expenditure on intangible assets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acquisition of businesses, net of cash acquired</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Disposal of businesses, net of cash disposed of</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Investments (net) in associates and joint ventures</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Divestments in associates and joint ventures</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inflows/(outflows) from treasury investments</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other investing activities</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Investing Cash Flow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FINANCING ACTIVITIES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dividend paid to shareholders of the parent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dividends paid to non-controlling interests</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acquisition of non-controlling interests</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Purchase of treasury shares</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inflows from bonds and other long-term financial debt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Outflows from bonds, lease liabilities and other long-term financial debt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inflows/(outflows) from short-term financial debt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Financing Cash Flow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CASH RECONCILIATION</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Currency retranslations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Increase/(Decrease) in Cash and Cash Equivalents</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cash and cash equivalents at beginning of year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cash and Cash Equivalents at End of Year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cash and cash equivalents classified as held for sale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cash and Cash Equivalents per Balance Sheet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEMO: FREE CASH FLOW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free Cash Flow (as reported by Nestlé)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free Cash Flow (derived: Operating CF − Capex − Intangible capex)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free Cash Flow Margin (reported FCF ÷ Sales)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sources: Nestlé Financial Statements 2024 (13-Feb-2025) for FY2024/FY2023, and Nestlé Financial Statements 2022 (16-Feb-2023) for FY2022/FY2021 — same two documents cited on the Income_Statement sheet.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"Free Cash Flow (as reported by Nestlé)" is the company's own headline FCF figure quoted in its results press releases. "Free Cash Flow (derived)" is a from-first-principles calculation (Operating Cash Flow − Capex − Intangible capex) using only the line items above — the two do not tie out exactly (Nestlé's own FCF definition includes some additional adjustments not separately disclosed), which is normal and is flagged here rather than silently forced to match.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shaded rows are subtotals computed by formula, never hardcoded, so every subtotal is traceable to a disclosed line item.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"Divestments in associates and joint ventures" (CHF 9,294m in FY2021 only) reflects the one-off partial disposal of Nestlé's L'Oréal stake — see the matching note on the Income_Statement sheet.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nestlé — FY2025 Budget Assumptions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Driver</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FY2025 Assumption</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source / Rationale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Organic Sales Growth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nestlé FY2025 guidance (Full-Year Results 2024 press release, 13-Feb-2025): "organic sales growth is expected to improve compared to 2024, strengthening through the year" (FY2024 organic growth was 2.2%). 3.0% is used here as an illustrative point assumption within that guided range — Nestlé did not disclose a precise FY2025 organic growth number.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Net M&amp;A Impact</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No acquisition/divestment guidance was disclosed for FY2025 in the FY2024 results press release; assumed neutral (0.0%), consistent with FY2024's own -0.3% being a minor, non-recurring item.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Foreign Exchange (FX) Impact</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FY2025 guidance states it "assumes no significant change in key macroeconomic variables" — interpreted here as a flat (0.0%) FX assumption. In practice Nestlé's FX impact has been materially negative in FY2022-FY2024 (Swiss Franc strength), so this is a simplifying assumption, not a forecast of currency markets.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">→ Implied Reported Sales Growth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Formula: Organic Sales Growth + Net M&amp;A Impact + FX Impact (not a separate input).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Underlying Trading Operating Profit (UTOP) Margin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nestlé FY2025 guidance: UTOP margin "expected to be at or above 16.0% as we invest for growth", down from FY2024's reported 17.2%, reflecting a planned step-up in advertising &amp; marketing spend (guided to reach ~9% of sales by end-2025, from 8.1% in FY2024) and the ramp-up of the Fuel for Growth cost-savings programme. 16.5% is used as a midpoint scenario within the guided "16.0%+" range.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Net Financial Expenses Growth (vs FY2024)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Own assumption (not company guidance): Nestlé's net debt rose to CHF 56.0bn at FY2024 year-end (from CHF 49.6bn a year earlier) and the company stated it does not anticipate a new share buyback programme in 2025 — implying continued elevated net financial expenses. +5.0% growth vs FY2024's CHF 1.5bn is assumed as a reasonable continuation of the FY2023→FY2024 trend (+7.1%).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Effective Tax Rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Own assumption: close to FY2024's reported tax rate of 25.0%, with modest normalization assumed as the one-off deferred-tax write-off that inflated the FY2024 rate is not expected to repeat. No FY2025 tax-rate guidance was disclosed by Nestlé.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free Cash Flow (FCF) Margin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Own assumption: broadly in line with FY2024's 11.7% FCF margin, reflecting continued capital discipline under the Fuel for Growth programme, offset by the margin step-down (more cash absorbed by growth investment). No explicit FY2025 FCF guidance was disclosed by Nestlé.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shares Outstanding for EPS (million)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FY2024 weighted-average basic shares implied by reported EPS (Net Profit CHF 10,884m ÷ EPS CHF 4.19 = ~2,598m), reduced by the 43.5 million shares the Board proposed for cancellation in 2025 (per the FY2024 results press release). No new buyback programme is planned for 2025 per guidance, so the share count is held flat aside from that already-announced cancellation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IMPORTANT: cells highlighted in yellow are the editable scenario assumptions. Change any of them and every figure in the Budget_FY2025_PL_CF sheet recalculates automatically.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nestlé Group — FY2025 Budget vs FY2024 Actual (Simplified P&amp;L + Free Cash Flow, CHF m unless % or per-share)</t>
   </si>
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
   <si>
-    <t xml:space="preserve">FY2021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FY2022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FY2023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FY2024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sales</t>
+    <t xml:space="preserve">FY2024 Actual</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FY2025 Budget</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Budget YoY Growth</t>
   </si>
   <si>
     <t xml:space="preserve">Underlying Trading Operating Profit (UTOP)</t>
   </si>
   <si>
-    <t xml:space="preserve">UTOP Margin</t>
-  </si>
-  <si>
     <t xml:space="preserve">Net Financial Expenses</t>
   </si>
   <si>
     <t xml:space="preserve">Profit Before Tax (UTOP − Net Financial Expenses)*</t>
   </si>
   <si>
-    <t xml:space="preserve">Group Reported Tax Rate</t>
-  </si>
-  <si>
     <t xml:space="preserve">Implied Tax Expense (PBT × Tax Rate)</t>
   </si>
   <si>
-    <t xml:space="preserve">Net Profit (as reported)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Net Profit Margin</t>
+    <t xml:space="preserve">Net Profit</t>
   </si>
   <si>
     <t xml:space="preserve">Basic EPS (CHF)</t>
   </si>
   <si>
-    <t xml:space="preserve">Cash Generated from Operations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">n/a*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free Cash Flow (as reported)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FCF Margin (FCF / Sales)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Implied CapEx + Other Investing Items (OCF − FCF)**</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Net Debt (year-end)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">* Profit Before Tax here is a simplified bridge (UTOP − Net Financial Expenses only) and excludes restructuring/other trading and non-trading items that sit between UTOP and Nestlé's reported Trading/Operating Profit. This sheet intentionally keeps the P&amp;L simplified (per project scope: Income Statement + Free Cash Flow, no detailed Balance Sheet) — it will not tie exactly to Nestlé's full consolidated income statement.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">** FY2022's 'Cash generated from operations' was disclosed on a different basis ('before changes in working capital') and is not comparable to the FY2021/2023/2024 figures, so it is left blank (n/a) rather than mixing bases silently.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FY2021 Net Financial Expenses and Tax Rate are back-calculated from a disclosed year-on-year % change (exact figures sit in Nestlé's full Financial Statements 2021 PDF, not the condensed press release) — flagged in cell comments.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All other blue cells are exact figures as reported in Nestlé's official full-year results press releases (see cell comments for exact source/quote).</t>
+    <t xml:space="preserve">Free Cash Flow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FCF Margin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">* Profit Before Tax here follows a simplified bridge (UTOP − Net Financial Expenses only), excluding restructuring/other trading items — the Budget will not tie to a full consolidated income statement, by design (see Income_Statement and Cash_Flow_Statement notes).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Column B ("FY2024 Actual") links directly to the Income_Statement and Cash_Flow_Statement sheets — it is not retyped.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Column C ("FY2025 Budget") is entirely driven by the yellow assumption cells in Assumptions_FY2025 — change any assumption there and this whole sheet recalculates.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This is a Budget built from Nestlé's own FY2025 guidance as disclosed on 13-Feb-2025, BEFORE FY2025 actual results were known — it deliberately does not use hindsight. Step 4 of this project (Variance Analysis) will compare this Budget against Nestlé's actual FY2025 results once published.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0;\(#,##0\);\-"/>
     <numFmt numFmtId="166" formatCode="0.0%;\(0.0%\);\-"/>
     <numFmt numFmtId="167" formatCode="0.00;\(0.00\);\-"/>
+    <numFmt numFmtId="168" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -738,6 +726,13 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Cambria"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
@@ -833,21 +828,28 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF008000"/>
-      <name val="Cambria"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Cambria"/>
+      <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
+      <name val="Cambria"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Cambria"/>
       <family val="0"/>
       <charset val="1"/>
@@ -861,12 +863,29 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
+      <b val="true"/>
+      <i val="true"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF444444"/>
+      <name val="Cambria"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF008000"/>
+      <name val="Cambria"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -876,13 +895,25 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1F4B44"/>
-        <bgColor rgb="FF003366"/>
+        <bgColor rgb="FF444444"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9E2E0"/>
-        <bgColor rgb="FFCCFFCC"/>
+        <bgColor rgb="FFEDEDE8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEDEDE8"/>
+        <bgColor rgb="FFD9E2E0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -935,20 +966,20 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="47">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -960,115 +991,167 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="17" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="18" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="23" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="24" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="22" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="22" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1101,7 +1184,7 @@
       <rgbColor rgb="FF6B675C"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFFFCC"/>
+      <rgbColor rgb="FFEDEDE8"/>
       <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
@@ -1131,14 +1214,14 @@
       <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF666666"/>
       <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FF1F4B44"/>
       <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF003300"/>
       <rgbColor rgb="FF333300"/>
       <rgbColor rgb="FF993300"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
-      <rgbColor rgb="FF1F4B44"/>
+      <rgbColor rgb="FF444444"/>
     </indexedColors>
   </colors>
 </styleSheet>
@@ -1324,7 +1407,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A23"/>
+  <dimension ref="A1:A26"/>
   <sheetFormatPr defaultColWidth="8.71484375" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="255.71"/>
@@ -1366,66 +1449,81 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
+    <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="12" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="s">
+    <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5" t="s">
         <v>8</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="5" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="5" t="s">
+    <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="3" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="17" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
     <row r="18" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="3" t="s">
-        <v>13</v>
+      <c r="A18" s="6" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="4" t="s">
+      <c r="A19" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="4" t="s">
+    <row r="20" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="1" t="s">
+    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="4" t="s">
         <v>18</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="7" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -1447,938 +1545,938 @@
   <dimension ref="A1:Z15"/>
   <sheetFormatPr defaultColWidth="8.71484375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="2" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="8" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="2" style="8" width="13"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-      <c r="R1" s="6"/>
-      <c r="S1" s="6"/>
-      <c r="T1" s="6"/>
-      <c r="U1" s="6"/>
-      <c r="V1" s="6"/>
-      <c r="W1" s="6"/>
-      <c r="X1" s="6"/>
-      <c r="Y1" s="6"/>
-      <c r="Z1" s="6"/>
+      <c r="A1" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="9"/>
+      <c r="Q1" s="9"/>
+      <c r="R1" s="9"/>
+      <c r="S1" s="9"/>
+      <c r="T1" s="9"/>
+      <c r="U1" s="9"/>
+      <c r="V1" s="9"/>
+      <c r="W1" s="9"/>
+      <c r="X1" s="9"/>
+      <c r="Y1" s="9"/>
+      <c r="Z1" s="9"/>
     </row>
     <row r="3" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" s="7" t="s">
+      <c r="A3" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="B3" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="C3" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="D3" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="E3" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="F3" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="G3" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="K3" s="7" t="s">
+      <c r="H3" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="L3" s="7" t="s">
+      <c r="I3" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="M3" s="7" t="s">
+      <c r="J3" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="N3" s="7" t="s">
+      <c r="K3" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="O3" s="7" t="s">
+      <c r="L3" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="P3" s="7" t="s">
+      <c r="M3" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="Q3" s="7" t="s">
+      <c r="N3" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="R3" s="7" t="s">
+      <c r="O3" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="S3" s="7" t="s">
+      <c r="P3" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="T3" s="7" t="s">
+      <c r="Q3" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="U3" s="7" t="s">
+      <c r="R3" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="V3" s="7" t="s">
+      <c r="S3" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="W3" s="7" t="s">
+      <c r="T3" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="X3" s="7" t="s">
+      <c r="U3" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="Y3" s="7" t="s">
+      <c r="V3" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="Z3" s="7" t="s">
+      <c r="W3" s="10" t="s">
         <v>45</v>
       </c>
+      <c r="X3" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y3" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z3" s="10" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="9" t="n">
+      <c r="A4" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="B4" s="12" t="n">
         <v>23693</v>
       </c>
-      <c r="C4" s="9" t="n">
+      <c r="C4" s="12" t="n">
         <v>26328</v>
       </c>
-      <c r="D4" s="9" t="n">
+      <c r="D4" s="12" t="n">
         <v>25995</v>
       </c>
-      <c r="E4" s="9" t="n">
+      <c r="E4" s="12" t="n">
         <v>25336</v>
       </c>
-      <c r="F4" s="10" t="n">
+      <c r="F4" s="13" t="n">
         <f aca="false">IFERROR(C4/B4-1,"")</f>
         <v>0.111214282699531</v>
       </c>
-      <c r="G4" s="10" t="n">
+      <c r="G4" s="13" t="n">
         <f aca="false">IFERROR(D4/C4-1,"")</f>
         <v>-0.0126481312670921</v>
       </c>
-      <c r="H4" s="10" t="n">
+      <c r="H4" s="13" t="n">
         <f aca="false">IFERROR(E4/D4-1,"")</f>
         <v>-0.025351029044047</v>
       </c>
-      <c r="I4" s="9" t="n">
+      <c r="I4" s="12" t="n">
         <v>4804</v>
       </c>
-      <c r="J4" s="9" t="n">
+      <c r="J4" s="12" t="n">
         <v>5528</v>
       </c>
-      <c r="K4" s="9" t="n">
+      <c r="K4" s="12" t="n">
         <v>5768</v>
       </c>
-      <c r="L4" s="9" t="n">
+      <c r="L4" s="12" t="n">
         <v>5640</v>
       </c>
-      <c r="M4" s="10" t="n">
+      <c r="M4" s="13" t="n">
         <f aca="false">IFERROR(I4/B4,"")</f>
         <v>0.202760308952011</v>
       </c>
-      <c r="N4" s="10" t="n">
+      <c r="N4" s="13" t="n">
         <f aca="false">IFERROR(J4/C4,"")</f>
         <v>0.209966575508964</v>
       </c>
-      <c r="O4" s="10" t="n">
+      <c r="O4" s="13" t="n">
         <f aca="false">IFERROR(K4/D4,"")</f>
         <v>0.221888824773995</v>
       </c>
-      <c r="P4" s="10" t="n">
+      <c r="P4" s="13" t="n">
         <f aca="false">IFERROR(L4/E4,"")</f>
         <v>0.222608146510894</v>
       </c>
-      <c r="Q4" s="11" t="n">
+      <c r="Q4" s="14" t="n">
         <v>-0.013</v>
       </c>
-      <c r="R4" s="11" t="n">
+      <c r="R4" s="14" t="n">
         <v>0.116</v>
       </c>
-      <c r="S4" s="11" t="n">
+      <c r="S4" s="14" t="n">
         <v>0.103</v>
       </c>
-      <c r="T4" s="11" t="n">
+      <c r="T4" s="14" t="n">
         <v>-0.038</v>
       </c>
-      <c r="U4" s="11" t="n">
+      <c r="U4" s="14" t="n">
         <v>0.047</v>
       </c>
-      <c r="V4" s="11" t="n">
+      <c r="V4" s="14" t="n">
         <v>-0.008</v>
       </c>
-      <c r="W4" s="11" t="n">
+      <c r="W4" s="14" t="n">
         <v>0.004</v>
       </c>
-      <c r="X4" s="11" t="n">
+      <c r="X4" s="14" t="n">
         <v>-0.005</v>
       </c>
-      <c r="Y4" s="11" t="n">
+      <c r="Y4" s="14" t="n">
         <v>-0.001</v>
       </c>
-      <c r="Z4" s="11" t="n">
+      <c r="Z4" s="14" t="n">
         <v>-0.02</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="9" t="n">
+      <c r="A5" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="B5" s="12" t="n">
         <v>18794</v>
       </c>
-      <c r="C5" s="9" t="n">
+      <c r="C5" s="12" t="n">
         <v>19128</v>
       </c>
-      <c r="D5" s="9" t="n">
+      <c r="D5" s="12" t="n">
         <v>19098</v>
       </c>
-      <c r="E5" s="9" t="n">
+      <c r="E5" s="12" t="n">
         <v>18910</v>
       </c>
-      <c r="F5" s="10" t="n">
+      <c r="F5" s="13" t="n">
         <f aca="false">IFERROR(C5/B5-1,"")</f>
         <v>0.0177716292433756</v>
       </c>
-      <c r="G5" s="10" t="n">
+      <c r="G5" s="13" t="n">
         <f aca="false">IFERROR(D5/C5-1,"")</f>
         <v>-0.00156838143036386</v>
       </c>
-      <c r="H5" s="10" t="n">
+      <c r="H5" s="13" t="n">
         <f aca="false">IFERROR(E5/D5-1,"")</f>
         <v>-0.00984396271860932</v>
       </c>
-      <c r="I5" s="9" t="n">
+      <c r="I5" s="12" t="n">
         <v>3439</v>
       </c>
-      <c r="J5" s="9" t="n">
+      <c r="J5" s="12" t="n">
         <v>3138</v>
       </c>
-      <c r="K5" s="9" t="n">
+      <c r="K5" s="12" t="n">
         <v>3127</v>
       </c>
-      <c r="L5" s="9" t="n">
+      <c r="L5" s="12" t="n">
         <v>3192</v>
       </c>
-      <c r="M5" s="10" t="n">
+      <c r="M5" s="13" t="n">
         <f aca="false">IFERROR(I5/B5,"")</f>
         <v>0.182983931041822</v>
       </c>
-      <c r="N5" s="10" t="n">
+      <c r="N5" s="13" t="n">
         <f aca="false">IFERROR(J5/C5,"")</f>
         <v>0.16405269761606</v>
       </c>
-      <c r="O5" s="10" t="n">
+      <c r="O5" s="13" t="n">
         <f aca="false">IFERROR(K5/D5,"")</f>
         <v>0.163734422452613</v>
       </c>
-      <c r="P5" s="10" t="n">
+      <c r="P5" s="13" t="n">
         <f aca="false">IFERROR(L5/E5,"")</f>
         <v>0.168799576943416</v>
       </c>
-      <c r="Q5" s="11" t="n">
+      <c r="Q5" s="14" t="n">
         <v>0.009</v>
       </c>
-      <c r="R5" s="11" t="n">
+      <c r="R5" s="14" t="n">
         <v>0.064</v>
       </c>
-      <c r="S5" s="11" t="n">
+      <c r="S5" s="14" t="n">
         <v>0.072</v>
       </c>
-      <c r="T5" s="11" t="n">
+      <c r="T5" s="14" t="n">
         <v>0.021</v>
       </c>
-      <c r="U5" s="11" t="n">
+      <c r="U5" s="14" t="n">
         <v>-0.076</v>
       </c>
-      <c r="V5" s="11" t="n">
+      <c r="V5" s="14" t="n">
         <v>0.008</v>
       </c>
-      <c r="W5" s="11" t="n">
+      <c r="W5" s="14" t="n">
         <v>0.025</v>
       </c>
-      <c r="X5" s="11" t="n">
+      <c r="X5" s="14" t="n">
         <v>0.033</v>
       </c>
-      <c r="Y5" s="11" t="n">
+      <c r="Y5" s="14" t="n">
         <v>-0.019</v>
       </c>
-      <c r="Z5" s="11" t="n">
+      <c r="Z5" s="14" t="n">
         <v>-0.025</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="B6" s="9" t="n">
+      <c r="A6" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="B6" s="12" t="n">
         <v>17894</v>
       </c>
-      <c r="C6" s="9" t="n">
+      <c r="C6" s="12" t="n">
         <v>18484</v>
       </c>
-      <c r="D6" s="9" t="n">
+      <c r="D6" s="12" t="n">
         <v>17519</v>
       </c>
-      <c r="E6" s="9" t="n">
+      <c r="E6" s="12" t="n">
         <v>16793</v>
       </c>
-      <c r="F6" s="10" t="n">
+      <c r="F6" s="13" t="n">
         <f aca="false">IFERROR(C6/B6-1,"")</f>
         <v>0.0329719459036548</v>
       </c>
-      <c r="G6" s="10" t="n">
+      <c r="G6" s="13" t="n">
         <f aca="false">IFERROR(D6/C6-1,"")</f>
         <v>-0.0522073144341052</v>
       </c>
-      <c r="H6" s="10" t="n">
+      <c r="H6" s="13" t="n">
         <f aca="false">IFERROR(E6/D6-1,"")</f>
         <v>-0.0414407215023689</v>
       </c>
-      <c r="I6" s="9" t="n">
+      <c r="I6" s="12" t="n">
         <v>4288</v>
       </c>
-      <c r="J6" s="9" t="n">
+      <c r="J6" s="12" t="n">
         <v>4237</v>
       </c>
-      <c r="K6" s="9" t="n">
+      <c r="K6" s="12" t="n">
         <v>4109</v>
       </c>
-      <c r="L6" s="9" t="n">
+      <c r="L6" s="12" t="n">
         <v>3916</v>
       </c>
-      <c r="M6" s="10" t="n">
+      <c r="M6" s="13" t="n">
         <f aca="false">IFERROR(I6/B6,"")</f>
         <v>0.239633396669275</v>
       </c>
-      <c r="N6" s="10" t="n">
+      <c r="N6" s="13" t="n">
         <f aca="false">IFERROR(J6/C6,"")</f>
         <v>0.229225275914304</v>
       </c>
-      <c r="O6" s="10" t="n">
+      <c r="O6" s="13" t="n">
         <f aca="false">IFERROR(K6/D6,"")</f>
         <v>0.23454535076203</v>
       </c>
-      <c r="P6" s="10" t="n">
+      <c r="P6" s="13" t="n">
         <f aca="false">IFERROR(L6/E6,"")</f>
         <v>0.233192401595903</v>
       </c>
-      <c r="Q6" s="11" t="n">
+      <c r="Q6" s="14" t="n">
         <v>0.001</v>
       </c>
-      <c r="R6" s="11" t="n">
+      <c r="R6" s="14" t="n">
         <v>0.081</v>
       </c>
-      <c r="S6" s="11" t="n">
+      <c r="S6" s="14" t="n">
         <v>0.082</v>
       </c>
-      <c r="T6" s="11" t="n">
+      <c r="T6" s="14" t="n">
         <v>-0.001</v>
       </c>
-      <c r="U6" s="11" t="n">
+      <c r="U6" s="14" t="n">
         <v>-0.049</v>
       </c>
-      <c r="V6" s="11" t="n">
+      <c r="V6" s="14" t="n">
         <v>0.006</v>
       </c>
-      <c r="W6" s="11" t="n">
+      <c r="W6" s="14" t="n">
         <v>0.028</v>
       </c>
-      <c r="X6" s="11" t="n">
+      <c r="X6" s="14" t="n">
         <v>0.034</v>
       </c>
-      <c r="Y6" s="11" t="n">
+      <c r="Y6" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="Z6" s="11" t="n">
+      <c r="Z6" s="14" t="n">
         <v>-0.075</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="B7" s="9" t="n">
+      <c r="A7" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" s="12" t="n">
         <v>10086</v>
       </c>
-      <c r="C7" s="9" t="n">
+      <c r="C7" s="12" t="n">
         <v>11819</v>
       </c>
-      <c r="D7" s="9" t="n">
+      <c r="D7" s="12" t="n">
         <v>12196</v>
       </c>
-      <c r="E7" s="9" t="n">
+      <c r="E7" s="12" t="n">
         <v>11933</v>
       </c>
-      <c r="F7" s="10" t="n">
+      <c r="F7" s="13" t="n">
         <f aca="false">IFERROR(C7/B7-1,"")</f>
         <v>0.171822327979377</v>
       </c>
-      <c r="G7" s="10" t="n">
+      <c r="G7" s="13" t="n">
         <f aca="false">IFERROR(D7/C7-1,"")</f>
         <v>0.0318977916913445</v>
       </c>
-      <c r="H7" s="10" t="n">
+      <c r="H7" s="13" t="n">
         <f aca="false">IFERROR(E7/D7-1,"")</f>
         <v>-0.0215644473597901</v>
       </c>
-      <c r="I7" s="9" t="n">
+      <c r="I7" s="12" t="n">
         <v>2208</v>
       </c>
-      <c r="J7" s="9" t="n">
+      <c r="J7" s="12" t="n">
         <v>2501</v>
       </c>
-      <c r="K7" s="9" t="n">
+      <c r="K7" s="12" t="n">
         <v>2520</v>
       </c>
-      <c r="L7" s="9" t="n">
+      <c r="L7" s="12" t="n">
         <v>2429</v>
       </c>
-      <c r="M7" s="10" t="n">
+      <c r="M7" s="13" t="n">
         <f aca="false">IFERROR(I7/B7,"")</f>
         <v>0.218917311124331</v>
       </c>
-      <c r="N7" s="10" t="n">
+      <c r="N7" s="13" t="n">
         <f aca="false">IFERROR(J7/C7,"")</f>
         <v>0.211608427108892</v>
       </c>
-      <c r="O7" s="10" t="n">
+      <c r="O7" s="13" t="n">
         <f aca="false">IFERROR(K7/D7,"")</f>
         <v>0.206625122991145</v>
       </c>
-      <c r="P7" s="10" t="n">
+      <c r="P7" s="13" t="n">
         <f aca="false">IFERROR(L7/E7,"")</f>
         <v>0.203553171876309</v>
       </c>
-      <c r="Q7" s="11" t="n">
+      <c r="Q7" s="14" t="n">
         <v>0.015</v>
       </c>
-      <c r="R7" s="11" t="n">
+      <c r="R7" s="14" t="n">
         <v>0.116</v>
       </c>
-      <c r="S7" s="11" t="n">
+      <c r="S7" s="14" t="n">
         <v>0.131</v>
       </c>
-      <c r="T7" s="11" t="n">
+      <c r="T7" s="14" t="n">
         <v>0.001</v>
       </c>
-      <c r="U7" s="11" t="n">
+      <c r="U7" s="14" t="n">
         <v>0.04</v>
       </c>
-      <c r="V7" s="11" t="n">
+      <c r="V7" s="14" t="n">
         <v>-0.003</v>
       </c>
-      <c r="W7" s="11" t="n">
+      <c r="W7" s="14" t="n">
         <v>0.027</v>
       </c>
-      <c r="X7" s="11" t="n">
+      <c r="X7" s="14" t="n">
         <v>0.025</v>
       </c>
-      <c r="Y7" s="11" t="n">
+      <c r="Y7" s="14" t="n">
         <v>0.004</v>
       </c>
-      <c r="Z7" s="11" t="n">
+      <c r="Z7" s="14" t="n">
         <v>-0.049</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="B8" s="9" t="n">
+      <c r="A8" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="B8" s="12" t="n">
         <v>5175</v>
       </c>
-      <c r="C8" s="9" t="n">
+      <c r="C8" s="12" t="n">
         <v>5351</v>
       </c>
-      <c r="D8" s="9" t="n">
+      <c r="D8" s="12" t="n">
         <v>5037</v>
       </c>
-      <c r="E8" s="9" t="n">
+      <c r="E8" s="12" t="n">
         <v>4973</v>
       </c>
-      <c r="F8" s="10" t="n">
+      <c r="F8" s="13" t="n">
         <f aca="false">IFERROR(C8/B8-1,"")</f>
         <v>0.0340096618357488</v>
       </c>
-      <c r="G8" s="10" t="n">
+      <c r="G8" s="13" t="n">
         <f aca="false">IFERROR(D8/C8-1,"")</f>
         <v>-0.0586806204447767</v>
       </c>
-      <c r="H8" s="10" t="n">
+      <c r="H8" s="13" t="n">
         <f aca="false">IFERROR(E8/D8-1,"")</f>
         <v>-0.0127059757792337</v>
       </c>
-      <c r="I8" s="9" t="n">
+      <c r="I8" s="12" t="n">
         <v>700</v>
       </c>
-      <c r="J8" s="9" t="n">
+      <c r="J8" s="12" t="n">
         <v>862</v>
       </c>
-      <c r="K8" s="9" t="n">
+      <c r="K8" s="12" t="n">
         <v>832</v>
       </c>
-      <c r="L8" s="9" t="n">
+      <c r="L8" s="12" t="n">
         <v>803</v>
       </c>
-      <c r="M8" s="10" t="n">
+      <c r="M8" s="13" t="n">
         <f aca="false">IFERROR(I8/B8,"")</f>
         <v>0.135265700483092</v>
       </c>
-      <c r="N8" s="10" t="n">
+      <c r="N8" s="13" t="n">
         <f aca="false">IFERROR(J8/C8,"")</f>
         <v>0.16109138478789</v>
       </c>
-      <c r="O8" s="10" t="n">
+      <c r="O8" s="13" t="n">
         <f aca="false">IFERROR(K8/D8,"")</f>
         <v>0.165177685130038</v>
       </c>
-      <c r="P8" s="10" t="n">
+      <c r="P8" s="13" t="n">
         <f aca="false">IFERROR(L8/E8,"")</f>
         <v>0.161471948522019</v>
       </c>
-      <c r="Q8" s="11" t="n">
+      <c r="Q8" s="14" t="n">
         <v>0.01</v>
       </c>
-      <c r="R8" s="11" t="n">
+      <c r="R8" s="14" t="n">
         <v>0.025</v>
       </c>
-      <c r="S8" s="11" t="n">
+      <c r="S8" s="14" t="n">
         <v>0.035</v>
       </c>
-      <c r="T8" s="11" t="n">
+      <c r="T8" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="U8" s="11" t="n">
+      <c r="U8" s="14" t="n">
         <v>-0.001</v>
       </c>
-      <c r="V8" s="11" t="n">
+      <c r="V8" s="14" t="n">
         <v>0.043</v>
       </c>
-      <c r="W8" s="11" t="n">
+      <c r="W8" s="14" t="n">
         <v>-0.021</v>
       </c>
-      <c r="X8" s="11" t="n">
+      <c r="X8" s="14" t="n">
         <v>0.021</v>
       </c>
-      <c r="Y8" s="11" t="n">
+      <c r="Y8" s="14" t="n">
         <v>0.001</v>
       </c>
-      <c r="Z8" s="11" t="n">
+      <c r="Z8" s="14" t="n">
         <v>-0.035</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="B9" s="9" t="n">
+      <c r="A9" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="B9" s="12" t="n">
         <v>4822</v>
       </c>
-      <c r="C9" s="9" t="n">
+      <c r="C9" s="12" t="n">
         <v>6602</v>
       </c>
-      <c r="D9" s="9" t="n">
+      <c r="D9" s="12" t="n">
         <v>6498</v>
       </c>
-      <c r="E9" s="9" t="n">
+      <c r="E9" s="12" t="n">
         <v>6739</v>
       </c>
-      <c r="F9" s="10" t="n">
+      <c r="F9" s="13" t="n">
         <f aca="false">IFERROR(C9/B9-1,"")</f>
         <v>0.369141435089175</v>
       </c>
-      <c r="G9" s="10" t="n">
+      <c r="G9" s="13" t="n">
         <f aca="false">IFERROR(D9/C9-1,"")</f>
         <v>-0.0157528021811573</v>
       </c>
-      <c r="H9" s="10" t="n">
+      <c r="H9" s="13" t="n">
         <f aca="false">IFERROR(E9/D9-1,"")</f>
         <v>0.0370883348722684</v>
       </c>
-      <c r="I9" s="9" t="n">
+      <c r="I9" s="12" t="n">
         <v>654</v>
       </c>
-      <c r="J9" s="9" t="n">
+      <c r="J9" s="12" t="n">
         <v>899</v>
       </c>
-      <c r="K9" s="9" t="n">
+      <c r="K9" s="12" t="n">
         <v>777</v>
       </c>
-      <c r="L9" s="9" t="n">
+      <c r="L9" s="12" t="n">
         <v>943</v>
       </c>
-      <c r="M9" s="10" t="n">
+      <c r="M9" s="13" t="n">
         <f aca="false">IFERROR(I9/B9,"")</f>
         <v>0.135628369970966</v>
       </c>
-      <c r="N9" s="10" t="n">
+      <c r="N9" s="13" t="n">
         <f aca="false">IFERROR(J9/C9,"")</f>
         <v>0.136170857315965</v>
       </c>
-      <c r="O9" s="10" t="n">
+      <c r="O9" s="13" t="n">
         <f aca="false">IFERROR(K9/D9,"")</f>
         <v>0.119575253924284</v>
       </c>
-      <c r="P9" s="10" t="n">
+      <c r="P9" s="13" t="n">
         <f aca="false">IFERROR(L9/E9,"")</f>
         <v>0.139931740614334</v>
       </c>
-      <c r="Q9" s="11" t="n">
+      <c r="Q9" s="14" t="n">
         <v>0.006</v>
       </c>
-      <c r="R9" s="11" t="n">
+      <c r="R9" s="14" t="n">
         <v>0.034</v>
       </c>
-      <c r="S9" s="11" t="n">
+      <c r="S9" s="14" t="n">
         <v>0.04</v>
       </c>
-      <c r="T9" s="11" t="n">
+      <c r="T9" s="14" t="n">
         <v>0.315</v>
       </c>
-      <c r="U9" s="11" t="n">
+      <c r="U9" s="14" t="n">
         <v>0.015</v>
       </c>
-      <c r="V9" s="11" t="n">
+      <c r="V9" s="14" t="n">
         <v>0.055</v>
       </c>
-      <c r="W9" s="11" t="n">
+      <c r="W9" s="14" t="n">
         <v>0.007</v>
       </c>
-      <c r="X9" s="11" t="n">
+      <c r="X9" s="14" t="n">
         <v>0.062</v>
       </c>
-      <c r="Y9" s="11" t="n">
+      <c r="Y9" s="14" t="n">
         <v>0.002</v>
       </c>
-      <c r="Z9" s="11" t="n">
+      <c r="Z9" s="14" t="n">
         <v>-0.028</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="B10" s="9" t="n">
+      <c r="A10" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="B10" s="12" t="n">
         <v>6418</v>
       </c>
-      <c r="C10" s="9" t="n">
+      <c r="C10" s="12" t="n">
         <v>6448</v>
       </c>
-      <c r="D10" s="9" t="n">
+      <c r="D10" s="12" t="n">
         <v>6372</v>
       </c>
-      <c r="E10" s="9" t="n">
+      <c r="E10" s="12" t="n">
         <v>6378</v>
       </c>
-      <c r="F10" s="10" t="n">
+      <c r="F10" s="13" t="n">
         <f aca="false">IFERROR(C10/B10-1,"")</f>
         <v>0.00467435338111555</v>
       </c>
-      <c r="G10" s="10" t="n">
+      <c r="G10" s="13" t="n">
         <f aca="false">IFERROR(D10/C10-1,"")</f>
         <v>-0.0117866004962779</v>
       </c>
-      <c r="H10" s="10" t="n">
+      <c r="H10" s="13" t="n">
         <f aca="false">IFERROR(E10/D10-1,"")</f>
         <v>0.000941619585687281</v>
       </c>
-      <c r="I10" s="9" t="n">
+      <c r="I10" s="12" t="n">
         <v>1475</v>
       </c>
-      <c r="J10" s="9" t="n">
+      <c r="J10" s="12" t="n">
         <v>1388</v>
       </c>
-      <c r="K10" s="9" t="n">
+      <c r="K10" s="12" t="n">
         <v>1291</v>
       </c>
-      <c r="L10" s="9" t="n">
+      <c r="L10" s="12" t="n">
         <v>1278</v>
       </c>
-      <c r="M10" s="10" t="n">
+      <c r="M10" s="13" t="n">
         <f aca="false">IFERROR(I10/B10,"")</f>
         <v>0.229822374571518</v>
       </c>
-      <c r="N10" s="10" t="n">
+      <c r="N10" s="13" t="n">
         <f aca="false">IFERROR(J10/C10,"")</f>
         <v>0.215260545905707</v>
       </c>
-      <c r="O10" s="10" t="n">
+      <c r="O10" s="13" t="n">
         <f aca="false">IFERROR(K10/D10,"")</f>
         <v>0.202605147520402</v>
       </c>
-      <c r="P10" s="10" t="n">
+      <c r="P10" s="13" t="n">
         <f aca="false">IFERROR(L10/E10,"")</f>
         <v>0.200376293508937</v>
       </c>
-      <c r="Q10" s="11" t="n">
+      <c r="Q10" s="14" t="n">
         <v>-0.017</v>
       </c>
-      <c r="R10" s="11" t="n">
+      <c r="R10" s="14" t="n">
         <v>0.052</v>
       </c>
-      <c r="S10" s="11" t="n">
+      <c r="S10" s="14" t="n">
         <v>0.035</v>
       </c>
-      <c r="T10" s="11" t="n">
+      <c r="T10" s="14" t="n">
         <v>-0.003</v>
       </c>
-      <c r="U10" s="11" t="n">
+      <c r="U10" s="14" t="n">
         <v>-0.027</v>
       </c>
-      <c r="V10" s="11" t="n">
+      <c r="V10" s="14" t="n">
         <v>0.016</v>
       </c>
-      <c r="W10" s="11" t="n">
+      <c r="W10" s="14" t="n">
         <v>0.006</v>
       </c>
-      <c r="X10" s="11" t="n">
+      <c r="X10" s="14" t="n">
         <v>0.022</v>
       </c>
-      <c r="Y10" s="11" t="n">
+      <c r="Y10" s="14" t="n">
         <v>0.002</v>
       </c>
-      <c r="Z10" s="11" t="n">
+      <c r="Z10" s="14" t="n">
         <v>-0.024</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="B11" s="9" t="n">
+      <c r="A11" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="B11" s="12" t="n">
         <v>206</v>
       </c>
-      <c r="C11" s="9" t="n">
+      <c r="C11" s="12" t="n">
         <v>264</v>
       </c>
-      <c r="D11" s="9" t="n">
+      <c r="D11" s="12" t="n">
         <v>283</v>
       </c>
-      <c r="E11" s="9" t="n">
+      <c r="E11" s="12" t="n">
         <v>292</v>
       </c>
-      <c r="F11" s="10" t="n">
+      <c r="F11" s="13" t="n">
         <f aca="false">IFERROR(C11/B11-1,"")</f>
         <v>0.281553398058253</v>
       </c>
-      <c r="G11" s="10" t="n">
+      <c r="G11" s="13" t="n">
         <f aca="false">IFERROR(D11/C11-1,"")</f>
         <v>0.071969696969697</v>
       </c>
-      <c r="H11" s="10" t="n">
+      <c r="H11" s="13" t="n">
         <f aca="false">IFERROR(E11/D11-1,"")</f>
         <v>0.0318021201413428</v>
       </c>
-      <c r="I11" s="9" t="n">
+      <c r="I11" s="12" t="n">
         <v>-32</v>
       </c>
-      <c r="J11" s="9" t="n">
+      <c r="J11" s="12" t="n">
         <v>-17</v>
       </c>
-      <c r="K11" s="9" t="n">
+      <c r="K11" s="12" t="n">
         <v>-12</v>
       </c>
-      <c r="L11" s="9" t="n">
+      <c r="L11" s="12" t="n">
         <v>-13</v>
       </c>
-      <c r="M11" s="10" t="n">
+      <c r="M11" s="13" t="n">
         <f aca="false">IFERROR(I11/B11,"")</f>
         <v>-0.155339805825243</v>
       </c>
-      <c r="N11" s="10" t="n">
+      <c r="N11" s="13" t="n">
         <f aca="false">IFERROR(J11/C11,"")</f>
         <v>-0.0643939393939394</v>
       </c>
-      <c r="O11" s="10" t="n">
+      <c r="O11" s="13" t="n">
         <f aca="false">IFERROR(K11/D11,"")</f>
         <v>-0.0424028268551237</v>
       </c>
-      <c r="P11" s="10" t="n">
+      <c r="P11" s="13" t="n">
         <f aca="false">IFERROR(L11/E11,"")</f>
         <v>-0.0445205479452055</v>
       </c>
-      <c r="Q11" s="11" t="n">
+      <c r="Q11" s="14" t="n">
         <v>0.252</v>
       </c>
-      <c r="R11" s="11" t="n">
+      <c r="R11" s="14" t="n">
         <v>0.032</v>
       </c>
-      <c r="S11" s="11" t="n">
+      <c r="S11" s="14" t="n">
         <v>0.284</v>
       </c>
-      <c r="T11" s="11" t="n">
+      <c r="T11" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="U11" s="11" t="n">
+      <c r="U11" s="14" t="n">
         <v>-0.001</v>
       </c>
-      <c r="V11" s="11" t="n">
+      <c r="V11" s="14" t="n">
         <v>0.053</v>
       </c>
-      <c r="W11" s="11" t="n">
+      <c r="W11" s="14" t="n">
         <v>0.013</v>
       </c>
-      <c r="X11" s="11" t="n">
+      <c r="X11" s="14" t="n">
         <v>0.066</v>
       </c>
-      <c r="Y11" s="11" t="n">
+      <c r="Y11" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="Z11" s="11" t="n">
+      <c r="Z11" s="14" t="n">
         <v>-0.027</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="B12" s="13" t="n">
+      <c r="A12" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="B12" s="16" t="n">
         <f aca="false">SUM(B4:B11)</f>
         <v>87088</v>
       </c>
-      <c r="C12" s="13" t="n">
+      <c r="C12" s="16" t="n">
         <f aca="false">SUM(C4:C11)</f>
         <v>94424</v>
       </c>
-      <c r="D12" s="13" t="n">
+      <c r="D12" s="16" t="n">
         <f aca="false">SUM(D4:D11)</f>
         <v>92998</v>
       </c>
-      <c r="E12" s="13" t="n">
+      <c r="E12" s="16" t="n">
         <f aca="false">SUM(E4:E11)</f>
         <v>91354</v>
       </c>
-      <c r="F12" s="14" t="n">
+      <c r="F12" s="17" t="n">
         <f aca="false">IFERROR(C12/B12-1,"")</f>
         <v>0.0842366342090759</v>
       </c>
-      <c r="G12" s="14" t="n">
+      <c r="G12" s="17" t="n">
         <f aca="false">IFERROR(D12/C12-1,"")</f>
         <v>-0.0151020926882995</v>
       </c>
-      <c r="H12" s="14" t="n">
+      <c r="H12" s="17" t="n">
         <f aca="false">IFERROR(E12/D12-1,"")</f>
         <v>-0.0176777995225704</v>
       </c>
-      <c r="I12" s="15" t="n">
+      <c r="I12" s="18" t="n">
         <v>15119</v>
       </c>
-      <c r="J12" s="15" t="n">
+      <c r="J12" s="18" t="n">
         <v>16103</v>
       </c>
-      <c r="K12" s="15" t="n">
+      <c r="K12" s="18" t="n">
         <v>16053</v>
       </c>
-      <c r="L12" s="15" t="n">
+      <c r="L12" s="18" t="n">
         <v>15704</v>
       </c>
-      <c r="M12" s="14" t="n">
+      <c r="M12" s="17" t="n">
         <f aca="false">IFERROR(I12/B12,"")</f>
         <v>0.173606007716333</v>
       </c>
-      <c r="N12" s="14" t="n">
+      <c r="N12" s="17" t="n">
         <f aca="false">IFERROR(J12/C12,"")</f>
         <v>0.170539269677201</v>
       </c>
-      <c r="O12" s="14" t="n">
+      <c r="O12" s="17" t="n">
         <f aca="false">IFERROR(K12/D12,"")</f>
         <v>0.172616615411084</v>
       </c>
-      <c r="P12" s="14" t="n">
+      <c r="P12" s="17" t="n">
         <f aca="false">IFERROR(L12/E12,"")</f>
         <v>0.171902708146332</v>
       </c>
-      <c r="Q12" s="16" t="n">
+      <c r="Q12" s="19" t="n">
         <v>0.001</v>
       </c>
-      <c r="R12" s="16" t="n">
+      <c r="R12" s="19" t="n">
         <v>0.082</v>
       </c>
-      <c r="S12" s="16" t="n">
+      <c r="S12" s="19" t="n">
         <v>0.083</v>
       </c>
-      <c r="T12" s="16" t="n">
+      <c r="T12" s="19" t="n">
         <v>0.011</v>
       </c>
-      <c r="U12" s="16" t="n">
+      <c r="U12" s="19" t="n">
         <v>-0.009</v>
       </c>
-      <c r="V12" s="16" t="n">
+      <c r="V12" s="19" t="n">
         <v>0.008</v>
       </c>
-      <c r="W12" s="16" t="n">
+      <c r="W12" s="19" t="n">
         <v>0.015</v>
       </c>
-      <c r="X12" s="16" t="n">
+      <c r="X12" s="19" t="n">
         <v>0.022</v>
       </c>
-      <c r="Y12" s="16" t="n">
+      <c r="Y12" s="19" t="n">
         <v>-0.003</v>
       </c>
-      <c r="Z12" s="16" t="n">
+      <c r="Z12" s="19" t="n">
         <v>-0.037</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="B14" s="17"/>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="17"/>
-      <c r="G14" s="17"/>
-      <c r="H14" s="17"/>
-      <c r="I14" s="17"/>
-      <c r="J14" s="17"/>
+      <c r="A14" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="B14" s="20"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="20"/>
+      <c r="G14" s="20"/>
+      <c r="H14" s="20"/>
+      <c r="I14" s="20"/>
+      <c r="J14" s="20"/>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="18" t="s">
-        <v>56</v>
-      </c>
-      <c r="B15" s="18"/>
-      <c r="C15" s="18"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="18"/>
-      <c r="G15" s="18"/>
-      <c r="H15" s="18"/>
-      <c r="I15" s="18"/>
-      <c r="J15" s="18"/>
-      <c r="K15" s="18"/>
-      <c r="L15" s="18"/>
-      <c r="M15" s="18"/>
-      <c r="N15" s="18"/>
+      <c r="A15" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="B15" s="21"/>
+      <c r="C15" s="21"/>
+      <c r="D15" s="21"/>
+      <c r="E15" s="21"/>
+      <c r="F15" s="21"/>
+      <c r="G15" s="21"/>
+      <c r="H15" s="21"/>
+      <c r="I15" s="21"/>
+      <c r="J15" s="21"/>
+      <c r="K15" s="21"/>
+      <c r="L15" s="21"/>
+      <c r="M15" s="21"/>
+      <c r="N15" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -2404,727 +2502,727 @@
   <dimension ref="A1:V14"/>
   <sheetFormatPr defaultColWidth="8.71484375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="2" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="8" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="2" style="8" width="13"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-      <c r="R1" s="6"/>
-      <c r="S1" s="6"/>
-      <c r="T1" s="6"/>
-      <c r="U1" s="6"/>
-      <c r="V1" s="6"/>
+      <c r="A1" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="9"/>
+      <c r="Q1" s="9"/>
+      <c r="R1" s="9"/>
+      <c r="S1" s="9"/>
+      <c r="T1" s="9"/>
+      <c r="U1" s="9"/>
+      <c r="V1" s="9"/>
     </row>
     <row r="3" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E3" s="7" t="s">
+      <c r="A3" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="B3" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="C3" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="D3" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="E3" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="F3" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="G3" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="K3" s="7" t="s">
+      <c r="H3" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="L3" s="7" t="s">
+      <c r="I3" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="M3" s="7" t="s">
+      <c r="J3" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="N3" s="7" t="s">
+      <c r="K3" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="O3" s="7" t="s">
+      <c r="L3" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="P3" s="7" t="s">
+      <c r="M3" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="Q3" s="7" t="s">
+      <c r="N3" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="R3" s="7" t="s">
+      <c r="O3" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="S3" s="7" t="s">
+      <c r="P3" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="T3" s="7" t="s">
+      <c r="Q3" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="R3" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="S3" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="U3" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="V3" s="7" t="s">
-        <v>43</v>
+      <c r="T3" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="U3" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="V3" s="10" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="B4" s="9" t="n">
+      <c r="A4" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="B4" s="12" t="n">
         <v>23975</v>
       </c>
-      <c r="C4" s="9" t="n">
+      <c r="C4" s="12" t="n">
         <v>25218</v>
       </c>
-      <c r="D4" s="9" t="n">
+      <c r="D4" s="12" t="n">
         <v>24786</v>
       </c>
-      <c r="E4" s="9" t="n">
+      <c r="E4" s="12" t="n">
         <v>24598</v>
       </c>
-      <c r="F4" s="10" t="n">
+      <c r="F4" s="13" t="n">
         <f aca="false">IFERROR(C4/B4-1,"")</f>
         <v>0.0518456725755996</v>
       </c>
-      <c r="G4" s="10" t="n">
+      <c r="G4" s="13" t="n">
         <f aca="false">IFERROR(D4/C4-1,"")</f>
         <v>-0.0171306209850107</v>
       </c>
-      <c r="H4" s="10" t="n">
+      <c r="H4" s="13" t="n">
         <f aca="false">IFERROR(E4/D4-1,"")</f>
         <v>-0.0075849269749052</v>
       </c>
-      <c r="I4" s="9" t="n">
+      <c r="I4" s="12" t="n">
         <v>5631</v>
       </c>
-      <c r="J4" s="9" t="n">
+      <c r="J4" s="12" t="n">
         <v>5593</v>
       </c>
-      <c r="K4" s="9" t="n">
+      <c r="K4" s="12" t="n">
         <v>5130</v>
       </c>
-      <c r="L4" s="9" t="n">
+      <c r="L4" s="12" t="n">
         <v>4920</v>
       </c>
-      <c r="M4" s="10" t="n">
+      <c r="M4" s="13" t="n">
         <f aca="false">IFERROR(I4/B4,"")</f>
         <v>0.234869655891554</v>
       </c>
-      <c r="N4" s="10" t="n">
+      <c r="N4" s="13" t="n">
         <f aca="false">IFERROR(J4/C4,"")</f>
         <v>0.221786025854548</v>
       </c>
-      <c r="O4" s="10" t="n">
+      <c r="O4" s="13" t="n">
         <f aca="false">IFERROR(K4/D4,"")</f>
         <v>0.206971677559913</v>
       </c>
-      <c r="P4" s="10" t="n">
+      <c r="P4" s="13" t="n">
         <f aca="false">IFERROR(L4/E4,"")</f>
         <v>0.200016261484674</v>
       </c>
-      <c r="Q4" s="11" t="n">
+      <c r="Q4" s="14" t="n">
         <v>0.002</v>
       </c>
-      <c r="R4" s="11" t="n">
+      <c r="R4" s="14" t="n">
         <v>0.078</v>
       </c>
-      <c r="S4" s="11" t="n">
+      <c r="S4" s="14" t="n">
         <v>0.08</v>
       </c>
-      <c r="T4" s="11" t="n">
+      <c r="T4" s="14" t="n">
         <v>0.016</v>
       </c>
-      <c r="U4" s="11" t="n">
+      <c r="U4" s="14" t="n">
         <v>0.017</v>
       </c>
-      <c r="V4" s="11" t="n">
+      <c r="V4" s="14" t="n">
         <v>0.033</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="B5" s="9" t="n">
+      <c r="A5" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="B5" s="12" t="n">
         <v>4040</v>
       </c>
-      <c r="C5" s="9" t="n">
+      <c r="C5" s="12" t="n">
         <v>3536</v>
       </c>
-      <c r="D5" s="9" t="n">
+      <c r="D5" s="12" t="n">
         <v>3320</v>
       </c>
-      <c r="E5" s="9" t="n">
+      <c r="E5" s="12" t="n">
         <v>3180</v>
       </c>
-      <c r="F5" s="10" t="n">
+      <c r="F5" s="13" t="n">
         <f aca="false">IFERROR(C5/B5-1,"")</f>
         <v>-0.124752475247525</v>
       </c>
-      <c r="G5" s="10" t="n">
+      <c r="G5" s="13" t="n">
         <f aca="false">IFERROR(D5/C5-1,"")</f>
         <v>-0.0610859728506787</v>
       </c>
-      <c r="H5" s="10" t="n">
+      <c r="H5" s="13" t="n">
         <f aca="false">IFERROR(E5/D5-1,"")</f>
         <v>-0.0421686746987952</v>
       </c>
-      <c r="I5" s="9" t="n">
+      <c r="I5" s="12" t="n">
         <v>364</v>
       </c>
-      <c r="J5" s="9" t="n">
+      <c r="J5" s="12" t="n">
         <v>277</v>
       </c>
-      <c r="K5" s="9" t="n">
+      <c r="K5" s="12" t="n">
         <v>351</v>
       </c>
-      <c r="L5" s="9" t="n">
+      <c r="L5" s="12" t="n">
         <v>297</v>
       </c>
-      <c r="M5" s="10" t="n">
+      <c r="M5" s="13" t="n">
         <f aca="false">IFERROR(I5/B5,"")</f>
         <v>0.0900990099009901</v>
       </c>
-      <c r="N5" s="10" t="n">
+      <c r="N5" s="13" t="n">
         <f aca="false">IFERROR(J5/C5,"")</f>
         <v>0.0783371040723982</v>
       </c>
-      <c r="O5" s="10" t="n">
+      <c r="O5" s="13" t="n">
         <f aca="false">IFERROR(K5/D5,"")</f>
         <v>0.105722891566265</v>
       </c>
-      <c r="P5" s="10" t="n">
+      <c r="P5" s="13" t="n">
         <f aca="false">IFERROR(L5/E5,"")</f>
         <v>0.0933962264150943</v>
       </c>
-      <c r="Q5" s="11" t="n">
+      <c r="Q5" s="14" t="n">
         <v>0.022</v>
       </c>
-      <c r="R5" s="11" t="n">
+      <c r="R5" s="14" t="n">
         <v>0.089</v>
       </c>
-      <c r="S5" s="11" t="n">
+      <c r="S5" s="14" t="n">
         <v>0.11</v>
       </c>
-      <c r="T5" s="11" t="n">
+      <c r="T5" s="14" t="n">
         <v>-0.01</v>
       </c>
-      <c r="U5" s="11" t="n">
+      <c r="U5" s="14" t="n">
         <v>0.032</v>
       </c>
-      <c r="V5" s="11" t="n">
+      <c r="V5" s="14" t="n">
         <v>0.023</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="B6" s="9" t="n">
+      <c r="A6" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="B6" s="12" t="n">
         <v>10700</v>
       </c>
-      <c r="C6" s="9" t="n">
+      <c r="C6" s="12" t="n">
         <v>11289</v>
       </c>
-      <c r="D6" s="9" t="n">
+      <c r="D6" s="12" t="n">
         <v>10981</v>
       </c>
-      <c r="E6" s="9" t="n">
+      <c r="E6" s="12" t="n">
         <v>10397</v>
       </c>
-      <c r="F6" s="10" t="n">
+      <c r="F6" s="13" t="n">
         <f aca="false">IFERROR(C6/B6-1,"")</f>
         <v>0.0550467289719627</v>
       </c>
-      <c r="G6" s="10" t="n">
+      <c r="G6" s="13" t="n">
         <f aca="false">IFERROR(D6/C6-1,"")</f>
         <v>-0.0272831960315352</v>
       </c>
-      <c r="H6" s="10" t="n">
+      <c r="H6" s="13" t="n">
         <f aca="false">IFERROR(E6/D6-1,"")</f>
         <v>-0.0531827702395046</v>
       </c>
-      <c r="I6" s="9" t="n">
+      <c r="I6" s="12" t="n">
         <v>2707</v>
       </c>
-      <c r="J6" s="9" t="n">
+      <c r="J6" s="12" t="n">
         <v>2568</v>
       </c>
-      <c r="K6" s="9" t="n">
+      <c r="K6" s="12" t="n">
         <v>2688</v>
       </c>
-      <c r="L6" s="9" t="n">
+      <c r="L6" s="12" t="n">
         <v>2442</v>
       </c>
-      <c r="M6" s="10" t="n">
+      <c r="M6" s="13" t="n">
         <f aca="false">IFERROR(I6/B6,"")</f>
         <v>0.252990654205607</v>
       </c>
-      <c r="N6" s="10" t="n">
+      <c r="N6" s="13" t="n">
         <f aca="false">IFERROR(J6/C6,"")</f>
         <v>0.227478076003189</v>
       </c>
-      <c r="O6" s="10" t="n">
+      <c r="O6" s="13" t="n">
         <f aca="false">IFERROR(K6/D6,"")</f>
         <v>0.244786449321555</v>
       </c>
-      <c r="P6" s="10" t="n">
+      <c r="P6" s="13" t="n">
         <f aca="false">IFERROR(L6/E6,"")</f>
         <v>0.234875444839858</v>
       </c>
-      <c r="Q6" s="11" t="n">
+      <c r="Q6" s="14" t="n">
         <v>-0.043</v>
       </c>
-      <c r="R6" s="11" t="n">
+      <c r="R6" s="14" t="n">
         <v>0.096</v>
       </c>
-      <c r="S6" s="11" t="n">
+      <c r="S6" s="14" t="n">
         <v>0.054</v>
       </c>
-      <c r="T6" s="11" t="n">
+      <c r="T6" s="14" t="n">
         <v>-0.007</v>
       </c>
-      <c r="U6" s="11" t="n">
+      <c r="U6" s="14" t="n">
         <v>0.001</v>
       </c>
-      <c r="V6" s="11" t="n">
+      <c r="V6" s="14" t="n">
         <v>-0.006</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="B7" s="9" t="n">
+      <c r="A7" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="B7" s="12" t="n">
         <v>13157</v>
       </c>
-      <c r="C7" s="9" t="n">
+      <c r="C7" s="12" t="n">
         <v>15678</v>
       </c>
-      <c r="D7" s="9" t="n">
+      <c r="D7" s="12" t="n">
         <v>15278</v>
       </c>
-      <c r="E7" s="9" t="n">
+      <c r="E7" s="12" t="n">
         <v>15137</v>
       </c>
-      <c r="F7" s="10" t="n">
+      <c r="F7" s="13" t="n">
         <f aca="false">IFERROR(C7/B7-1,"")</f>
         <v>0.191609029414</v>
       </c>
-      <c r="G7" s="10" t="n">
+      <c r="G7" s="13" t="n">
         <f aca="false">IFERROR(D7/C7-1,"")</f>
         <v>-0.0255134583492792</v>
       </c>
-      <c r="H7" s="10" t="n">
+      <c r="H7" s="13" t="n">
         <f aca="false">IFERROR(E7/D7-1,"")</f>
         <v>-0.00922895666972112</v>
       </c>
-      <c r="I7" s="9" t="n">
+      <c r="I7" s="12" t="n">
         <v>2307</v>
       </c>
-      <c r="J7" s="9" t="n">
+      <c r="J7" s="12" t="n">
         <v>2990</v>
       </c>
-      <c r="K7" s="9" t="n">
+      <c r="K7" s="12" t="n">
         <v>2831</v>
       </c>
-      <c r="L7" s="9" t="n">
+      <c r="L7" s="12" t="n">
         <v>3006</v>
       </c>
-      <c r="M7" s="10" t="n">
+      <c r="M7" s="13" t="n">
         <f aca="false">IFERROR(I7/B7,"")</f>
         <v>0.17534392338679</v>
       </c>
-      <c r="N7" s="10" t="n">
+      <c r="N7" s="13" t="n">
         <f aca="false">IFERROR(J7/C7,"")</f>
         <v>0.190713101160862</v>
       </c>
-      <c r="O7" s="10" t="n">
+      <c r="O7" s="13" t="n">
         <f aca="false">IFERROR(K7/D7,"")</f>
         <v>0.185299122921848</v>
       </c>
-      <c r="P7" s="10" t="n">
+      <c r="P7" s="13" t="n">
         <f aca="false">IFERROR(L7/E7,"")</f>
         <v>0.198586245623307</v>
       </c>
-      <c r="Q7" s="11" t="n">
+      <c r="Q7" s="14" t="n">
         <v>0.017</v>
       </c>
-      <c r="R7" s="11" t="n">
+      <c r="R7" s="14" t="n">
         <v>0.057</v>
       </c>
-      <c r="S7" s="11" t="n">
+      <c r="S7" s="14" t="n">
         <v>0.074</v>
       </c>
-      <c r="T7" s="11" t="n">
+      <c r="T7" s="14" t="n">
         <v>0.019</v>
       </c>
-      <c r="U7" s="11" t="n">
+      <c r="U7" s="14" t="n">
         <v>0.009</v>
       </c>
-      <c r="V7" s="11" t="n">
+      <c r="V7" s="14" t="n">
         <v>0.028</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="B8" s="9" t="n">
+      <c r="A8" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="B8" s="12" t="n">
         <v>12146</v>
       </c>
-      <c r="C8" s="9" t="n">
+      <c r="C8" s="12" t="n">
         <v>12484</v>
       </c>
-      <c r="D8" s="9" t="n">
+      <c r="D8" s="12" t="n">
         <v>11666</v>
       </c>
-      <c r="E8" s="9" t="n">
+      <c r="E8" s="12" t="n">
         <v>10711</v>
       </c>
-      <c r="F8" s="10" t="n">
+      <c r="F8" s="13" t="n">
         <f aca="false">IFERROR(C8/B8-1,"")</f>
         <v>0.0278280915527747</v>
       </c>
-      <c r="G8" s="10" t="n">
+      <c r="G8" s="13" t="n">
         <f aca="false">IFERROR(D8/C8-1,"")</f>
         <v>-0.0655238705543095</v>
       </c>
-      <c r="H8" s="10" t="n">
+      <c r="H8" s="13" t="n">
         <f aca="false">IFERROR(E8/D8-1,"")</f>
         <v>-0.0818618206754672</v>
       </c>
-      <c r="I8" s="9" t="n">
+      <c r="I8" s="12" t="n">
         <v>2040</v>
       </c>
-      <c r="J8" s="9" t="n">
+      <c r="J8" s="12" t="n">
         <v>2038</v>
       </c>
-      <c r="K8" s="9" t="n">
+      <c r="K8" s="12" t="n">
         <v>2136</v>
       </c>
-      <c r="L8" s="9" t="n">
+      <c r="L8" s="12" t="n">
         <v>2137</v>
       </c>
-      <c r="M8" s="10" t="n">
+      <c r="M8" s="13" t="n">
         <f aca="false">IFERROR(I8/B8,"")</f>
         <v>0.167956528898403</v>
       </c>
-      <c r="N8" s="10" t="n">
+      <c r="N8" s="13" t="n">
         <f aca="false">IFERROR(J8/C8,"")</f>
         <v>0.163248958667094</v>
       </c>
-      <c r="O8" s="10" t="n">
+      <c r="O8" s="13" t="n">
         <f aca="false">IFERROR(K8/D8,"")</f>
         <v>0.183096176924396</v>
       </c>
-      <c r="P8" s="10" t="n">
+      <c r="P8" s="13" t="n">
         <f aca="false">IFERROR(L8/E8,"")</f>
         <v>0.199514517785454</v>
       </c>
-      <c r="Q8" s="11" t="n">
+      <c r="Q8" s="14" t="n">
         <v>-0.069</v>
       </c>
-      <c r="R8" s="11" t="n">
+      <c r="R8" s="14" t="n">
         <v>0.1</v>
       </c>
-      <c r="S8" s="11" t="n">
+      <c r="S8" s="14" t="n">
         <v>0.031</v>
       </c>
-      <c r="T8" s="11" t="n">
+      <c r="T8" s="14" t="n">
         <v>-0.022</v>
       </c>
-      <c r="U8" s="11" t="n">
+      <c r="U8" s="14" t="n">
         <v>0.005</v>
       </c>
-      <c r="V8" s="11" t="n">
+      <c r="V8" s="14" t="n">
         <v>-0.017</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="B9" s="9" t="n">
+      <c r="A9" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="B9" s="12" t="n">
         <v>7514</v>
       </c>
-      <c r="C9" s="9" t="n">
+      <c r="C9" s="12" t="n">
         <v>8118</v>
       </c>
-      <c r="D9" s="9" t="n">
+      <c r="D9" s="12" t="n">
         <v>8107</v>
       </c>
-      <c r="E9" s="9" t="n">
+      <c r="E9" s="12" t="n">
         <v>8449</v>
       </c>
-      <c r="F9" s="10" t="n">
+      <c r="F9" s="13" t="n">
         <f aca="false">IFERROR(C9/B9-1,"")</f>
         <v>0.0803832845355337</v>
       </c>
-      <c r="G9" s="10" t="n">
+      <c r="G9" s="13" t="n">
         <f aca="false">IFERROR(D9/C9-1,"")</f>
         <v>-0.00135501355013545</v>
       </c>
-      <c r="H9" s="10" t="n">
+      <c r="H9" s="13" t="n">
         <f aca="false">IFERROR(E9/D9-1,"")</f>
         <v>0.0421857653879363</v>
       </c>
-      <c r="I9" s="9" t="n">
+      <c r="I9" s="12" t="n">
         <v>1205</v>
       </c>
-      <c r="J9" s="9" t="n">
+      <c r="J9" s="12" t="n">
         <v>1364</v>
       </c>
-      <c r="K9" s="9" t="n">
+      <c r="K9" s="12" t="n">
         <v>1364</v>
       </c>
-      <c r="L9" s="9" t="n">
+      <c r="L9" s="12" t="n">
         <v>1299</v>
       </c>
-      <c r="M9" s="10" t="n">
+      <c r="M9" s="13" t="n">
         <f aca="false">IFERROR(I9/B9,"")</f>
         <v>0.160367314346553</v>
       </c>
-      <c r="N9" s="10" t="n">
+      <c r="N9" s="13" t="n">
         <f aca="false">IFERROR(J9/C9,"")</f>
         <v>0.168021680216802</v>
       </c>
-      <c r="O9" s="10" t="n">
+      <c r="O9" s="13" t="n">
         <f aca="false">IFERROR(K9/D9,"")</f>
         <v>0.168249660786974</v>
       </c>
-      <c r="P9" s="10" t="n">
+      <c r="P9" s="13" t="n">
         <f aca="false">IFERROR(L9/E9,"")</f>
         <v>0.153746005444431</v>
       </c>
-      <c r="Q9" s="11" t="n">
+      <c r="Q9" s="14" t="n">
         <v>0.048</v>
       </c>
-      <c r="R9" s="11" t="n">
+      <c r="R9" s="14" t="n">
         <v>0.047</v>
       </c>
-      <c r="S9" s="11" t="n">
+      <c r="S9" s="14" t="n">
         <v>0.094</v>
       </c>
-      <c r="T9" s="11" t="n">
+      <c r="T9" s="14" t="n">
         <v>-0.002</v>
       </c>
-      <c r="U9" s="11" t="n">
+      <c r="U9" s="14" t="n">
         <v>0.064</v>
       </c>
-      <c r="V9" s="11" t="n">
+      <c r="V9" s="14" t="n">
         <v>0.062</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="B10" s="9" t="n">
+      <c r="A10" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="B10" s="12" t="n">
         <v>15556</v>
       </c>
-      <c r="C10" s="9" t="n">
+      <c r="C10" s="12" t="n">
         <v>18101</v>
       </c>
-      <c r="D10" s="9" t="n">
+      <c r="D10" s="12" t="n">
         <v>18860</v>
       </c>
-      <c r="E10" s="9" t="n">
+      <c r="E10" s="12" t="n">
         <v>18882</v>
       </c>
-      <c r="F10" s="10" t="n">
+      <c r="F10" s="13" t="n">
         <f aca="false">IFERROR(C10/B10-1,"")</f>
         <v>0.1636024685009</v>
       </c>
-      <c r="G10" s="10" t="n">
+      <c r="G10" s="13" t="n">
         <f aca="false">IFERROR(D10/C10-1,"")</f>
         <v>0.0419313850063532</v>
       </c>
-      <c r="H10" s="10" t="n">
+      <c r="H10" s="13" t="n">
         <f aca="false">IFERROR(E10/D10-1,"")</f>
         <v>0.00116648992576884</v>
       </c>
-      <c r="I10" s="9" t="n">
+      <c r="I10" s="12" t="n">
         <v>3282</v>
       </c>
-      <c r="J10" s="9" t="n">
+      <c r="J10" s="12" t="n">
         <v>3706</v>
       </c>
-      <c r="K10" s="9" t="n">
+      <c r="K10" s="12" t="n">
         <v>3912</v>
       </c>
-      <c r="L10" s="9" t="n">
+      <c r="L10" s="12" t="n">
         <v>4087</v>
       </c>
-      <c r="M10" s="10" t="n">
+      <c r="M10" s="13" t="n">
         <f aca="false">IFERROR(I10/B10,"")</f>
         <v>0.210979686294677</v>
       </c>
-      <c r="N10" s="10" t="n">
+      <c r="N10" s="13" t="n">
         <f aca="false">IFERROR(J10/C10,"")</f>
         <v>0.204740069609414</v>
       </c>
-      <c r="O10" s="10" t="n">
+      <c r="O10" s="13" t="n">
         <f aca="false">IFERROR(K10/D10,"")</f>
         <v>0.207423117709438</v>
       </c>
-      <c r="P10" s="10" t="n">
+      <c r="P10" s="13" t="n">
         <f aca="false">IFERROR(L10/E10,"")</f>
         <v>0.216449528651626</v>
       </c>
-      <c r="Q10" s="11" t="n">
+      <c r="Q10" s="14" t="n">
         <v>0.043</v>
       </c>
-      <c r="R10" s="11" t="n">
+      <c r="R10" s="14" t="n">
         <v>0.102</v>
       </c>
-      <c r="S10" s="11" t="n">
+      <c r="S10" s="14" t="n">
         <v>0.145</v>
       </c>
-      <c r="T10" s="11" t="n">
+      <c r="T10" s="14" t="n">
         <v>0.021</v>
       </c>
-      <c r="U10" s="11" t="n">
+      <c r="U10" s="14" t="n">
         <v>0.006</v>
       </c>
-      <c r="V10" s="11" t="n">
+      <c r="V10" s="14" t="n">
         <v>0.027</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="B11" s="13" t="n">
+      <c r="A11" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="B11" s="16" t="n">
         <f aca="false">SUM(B4:B10)</f>
         <v>87088</v>
       </c>
-      <c r="C11" s="13" t="n">
+      <c r="C11" s="16" t="n">
         <f aca="false">SUM(C4:C10)</f>
         <v>94424</v>
       </c>
-      <c r="D11" s="13" t="n">
+      <c r="D11" s="16" t="n">
         <f aca="false">SUM(D4:D10)</f>
         <v>92998</v>
       </c>
-      <c r="E11" s="13" t="n">
+      <c r="E11" s="16" t="n">
         <f aca="false">SUM(E4:E10)</f>
         <v>91354</v>
       </c>
-      <c r="F11" s="14" t="n">
+      <c r="F11" s="17" t="n">
         <f aca="false">IFERROR(C11/B11-1,"")</f>
         <v>0.0842366342090759</v>
       </c>
-      <c r="G11" s="14" t="n">
+      <c r="G11" s="17" t="n">
         <f aca="false">IFERROR(D11/C11-1,"")</f>
         <v>-0.0151020926882995</v>
       </c>
-      <c r="H11" s="14" t="n">
+      <c r="H11" s="17" t="n">
         <f aca="false">IFERROR(E11/D11-1,"")</f>
         <v>-0.0176777995225704</v>
       </c>
-      <c r="I11" s="15" t="n">
+      <c r="I11" s="18" t="n">
         <v>15119</v>
       </c>
-      <c r="J11" s="15" t="n">
+      <c r="J11" s="18" t="n">
         <v>16103</v>
       </c>
-      <c r="K11" s="15" t="n">
+      <c r="K11" s="18" t="n">
         <v>16053</v>
       </c>
-      <c r="L11" s="15" t="n">
+      <c r="L11" s="18" t="n">
         <v>15704</v>
       </c>
-      <c r="M11" s="14" t="n">
+      <c r="M11" s="17" t="n">
         <f aca="false">IFERROR(I11/B11,"")</f>
         <v>0.173606007716333</v>
       </c>
-      <c r="N11" s="14" t="n">
+      <c r="N11" s="17" t="n">
         <f aca="false">IFERROR(J11/C11,"")</f>
         <v>0.170539269677201</v>
       </c>
-      <c r="O11" s="14" t="n">
+      <c r="O11" s="17" t="n">
         <f aca="false">IFERROR(K11/D11,"")</f>
         <v>0.172616615411084</v>
       </c>
-      <c r="P11" s="14" t="n">
+      <c r="P11" s="17" t="n">
         <f aca="false">IFERROR(L11/E11,"")</f>
         <v>0.171902708146332</v>
       </c>
-      <c r="Q11" s="19"/>
-      <c r="R11" s="19"/>
-      <c r="S11" s="19"/>
-      <c r="T11" s="19"/>
-      <c r="U11" s="19"/>
-      <c r="V11" s="19"/>
+      <c r="Q11" s="22"/>
+      <c r="R11" s="22"/>
+      <c r="S11" s="22"/>
+      <c r="T11" s="22"/>
+      <c r="U11" s="22"/>
+      <c r="V11" s="22"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="B13" s="17"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
-      <c r="G13" s="17"/>
-      <c r="H13" s="17"/>
-      <c r="I13" s="17"/>
-      <c r="J13" s="17"/>
+      <c r="A13" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="B13" s="20"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="20"/>
+      <c r="G13" s="20"/>
+      <c r="H13" s="20"/>
+      <c r="I13" s="20"/>
+      <c r="J13" s="20"/>
     </row>
     <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="18" t="s">
-        <v>67</v>
-      </c>
-      <c r="B14" s="18"/>
-      <c r="C14" s="18"/>
-      <c r="D14" s="18"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="18"/>
-      <c r="G14" s="18"/>
-      <c r="H14" s="18"/>
-      <c r="I14" s="18"/>
-      <c r="J14" s="18"/>
-      <c r="K14" s="18"/>
-      <c r="L14" s="18"/>
-      <c r="M14" s="18"/>
-      <c r="N14" s="18"/>
+      <c r="A14" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="B14" s="21"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="21"/>
+      <c r="G14" s="21"/>
+      <c r="H14" s="21"/>
+      <c r="I14" s="21"/>
+      <c r="J14" s="21"/>
+      <c r="K14" s="21"/>
+      <c r="L14" s="21"/>
+      <c r="M14" s="21"/>
+      <c r="N14" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -3150,585 +3248,585 @@
   <dimension ref="A1:N15"/>
   <sheetFormatPr defaultColWidth="8.71484375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="2" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="8" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="2" style="8" width="15"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
+      <c r="A1" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="17" t="s">
-        <v>69</v>
-      </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="17"/>
-      <c r="J2" s="17"/>
-      <c r="K2" s="17"/>
-      <c r="L2" s="17"/>
-      <c r="M2" s="17"/>
-      <c r="N2" s="17"/>
+      <c r="A2" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="20"/>
     </row>
     <row r="4" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="C4" s="7" t="s">
+      <c r="A4" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="G4" s="7" t="s">
+      <c r="B4" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="C4" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="I4" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="J4" s="7" t="s">
+      <c r="E4" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="K4" s="7" t="s">
+      <c r="F4" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="L4" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="M4" s="7" t="s">
+      <c r="H4" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="N4" s="7" t="s">
+      <c r="I4" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="J4" s="10" t="s">
         <v>78</v>
       </c>
+      <c r="K4" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="L4" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="M4" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="N4" s="10" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="B5" s="9" t="n">
+      <c r="A5" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="B5" s="12" t="n">
         <v>12553</v>
       </c>
-      <c r="C5" s="20" t="n">
+      <c r="C5" s="23" t="n">
         <f aca="false">Segment_Data!D4</f>
         <v>25995</v>
       </c>
-      <c r="D5" s="21" t="n">
+      <c r="D5" s="24" t="n">
         <f aca="false">C5-B5</f>
         <v>13442</v>
       </c>
-      <c r="E5" s="9" t="n">
+      <c r="E5" s="12" t="n">
         <v>12234</v>
       </c>
-      <c r="F5" s="20" t="n">
+      <c r="F5" s="23" t="n">
         <f aca="false">Segment_Data!E4</f>
         <v>25336</v>
       </c>
-      <c r="G5" s="21" t="n">
+      <c r="G5" s="24" t="n">
         <f aca="false">F5-E5</f>
         <v>13102</v>
       </c>
-      <c r="H5" s="9" t="n">
+      <c r="H5" s="12" t="n">
         <v>2713</v>
       </c>
-      <c r="I5" s="20" t="n">
+      <c r="I5" s="23" t="n">
         <f aca="false">Segment_Data!K4</f>
         <v>5768</v>
       </c>
-      <c r="J5" s="21" t="n">
+      <c r="J5" s="24" t="n">
         <f aca="false">I5-H5</f>
         <v>3055</v>
       </c>
-      <c r="K5" s="9" t="n">
+      <c r="K5" s="12" t="n">
         <v>2662</v>
       </c>
-      <c r="L5" s="20" t="n">
+      <c r="L5" s="23" t="n">
         <f aca="false">Segment_Data!L4</f>
         <v>5640</v>
       </c>
-      <c r="M5" s="21" t="n">
+      <c r="M5" s="24" t="n">
         <f aca="false">L5-K5</f>
         <v>2978</v>
       </c>
-      <c r="N5" s="10" t="n">
+      <c r="N5" s="13" t="n">
         <f aca="false">IFERROR(G5/D5-1,"")</f>
         <v>-0.0252938550810892</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="B6" s="9" t="n">
+      <c r="A6" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="B6" s="12" t="n">
         <v>9467</v>
       </c>
-      <c r="C6" s="20" t="n">
+      <c r="C6" s="23" t="n">
         <f aca="false">Segment_Data!D5</f>
         <v>19098</v>
       </c>
-      <c r="D6" s="21" t="n">
+      <c r="D6" s="24" t="n">
         <f aca="false">C6-B6</f>
         <v>9631</v>
       </c>
-      <c r="E6" s="9" t="n">
+      <c r="E6" s="12" t="n">
         <v>9283</v>
       </c>
-      <c r="F6" s="20" t="n">
+      <c r="F6" s="23" t="n">
         <f aca="false">Segment_Data!E5</f>
         <v>18910</v>
       </c>
-      <c r="G6" s="21" t="n">
+      <c r="G6" s="24" t="n">
         <f aca="false">F6-E6</f>
         <v>9627</v>
       </c>
-      <c r="H6" s="9" t="n">
+      <c r="H6" s="12" t="n">
         <v>1570</v>
       </c>
-      <c r="I6" s="20" t="n">
+      <c r="I6" s="23" t="n">
         <f aca="false">Segment_Data!K5</f>
         <v>3127</v>
       </c>
-      <c r="J6" s="21" t="n">
+      <c r="J6" s="24" t="n">
         <f aca="false">I6-H6</f>
         <v>1557</v>
       </c>
-      <c r="K6" s="9" t="n">
+      <c r="K6" s="12" t="n">
         <v>1644</v>
       </c>
-      <c r="L6" s="20" t="n">
+      <c r="L6" s="23" t="n">
         <f aca="false">Segment_Data!L5</f>
         <v>3192</v>
       </c>
-      <c r="M6" s="21" t="n">
+      <c r="M6" s="24" t="n">
         <f aca="false">L6-K6</f>
         <v>1548</v>
       </c>
-      <c r="N6" s="10" t="n">
+      <c r="N6" s="13" t="n">
         <f aca="false">IFERROR(G6/D6-1,"")</f>
         <v>-0.00041532551136958</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="B7" s="9" t="n">
+      <c r="A7" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="B7" s="12" t="n">
         <v>9060</v>
       </c>
-      <c r="C7" s="20" t="n">
+      <c r="C7" s="23" t="n">
         <f aca="false">Segment_Data!D6</f>
         <v>17519</v>
       </c>
-      <c r="D7" s="21" t="n">
+      <c r="D7" s="24" t="n">
         <f aca="false">C7-B7</f>
         <v>8459</v>
       </c>
-      <c r="E7" s="9" t="n">
+      <c r="E7" s="12" t="n">
         <v>8441</v>
       </c>
-      <c r="F7" s="20" t="n">
+      <c r="F7" s="23" t="n">
         <f aca="false">Segment_Data!E6</f>
         <v>16793</v>
       </c>
-      <c r="G7" s="21" t="n">
+      <c r="G7" s="24" t="n">
         <f aca="false">F7-E7</f>
         <v>8352</v>
       </c>
-      <c r="H7" s="9" t="n">
+      <c r="H7" s="12" t="n">
         <v>2068</v>
       </c>
-      <c r="I7" s="20" t="n">
+      <c r="I7" s="23" t="n">
         <f aca="false">Segment_Data!K6</f>
         <v>4109</v>
       </c>
-      <c r="J7" s="21" t="n">
+      <c r="J7" s="24" t="n">
         <f aca="false">I7-H7</f>
         <v>2041</v>
       </c>
-      <c r="K7" s="9" t="n">
+      <c r="K7" s="12" t="n">
         <v>2006</v>
       </c>
-      <c r="L7" s="20" t="n">
+      <c r="L7" s="23" t="n">
         <f aca="false">Segment_Data!L6</f>
         <v>3916</v>
       </c>
-      <c r="M7" s="21" t="n">
+      <c r="M7" s="24" t="n">
         <f aca="false">L7-K7</f>
         <v>1910</v>
       </c>
-      <c r="N7" s="10" t="n">
+      <c r="N7" s="13" t="n">
         <f aca="false">IFERROR(G7/D7-1,"")</f>
         <v>-0.0126492493202506</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="B8" s="9" t="n">
+      <c r="A8" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="B8" s="12" t="n">
         <v>6082</v>
       </c>
-      <c r="C8" s="20" t="n">
+      <c r="C8" s="23" t="n">
         <f aca="false">Segment_Data!D7</f>
         <v>12196</v>
       </c>
-      <c r="D8" s="21" t="n">
+      <c r="D8" s="24" t="n">
         <f aca="false">C8-B8</f>
         <v>6114</v>
       </c>
-      <c r="E8" s="9" t="n">
+      <c r="E8" s="12" t="n">
         <v>6166</v>
       </c>
-      <c r="F8" s="20" t="n">
+      <c r="F8" s="23" t="n">
         <f aca="false">Segment_Data!E7</f>
         <v>11933</v>
       </c>
-      <c r="G8" s="21" t="n">
+      <c r="G8" s="24" t="n">
         <f aca="false">F8-E8</f>
         <v>5767</v>
       </c>
-      <c r="H8" s="9" t="n">
+      <c r="H8" s="12" t="n">
         <v>1202</v>
       </c>
-      <c r="I8" s="20" t="n">
+      <c r="I8" s="23" t="n">
         <f aca="false">Segment_Data!K7</f>
         <v>2520</v>
       </c>
-      <c r="J8" s="21" t="n">
+      <c r="J8" s="24" t="n">
         <f aca="false">I8-H8</f>
         <v>1318</v>
       </c>
-      <c r="K8" s="9" t="n">
+      <c r="K8" s="12" t="n">
         <v>1219</v>
       </c>
-      <c r="L8" s="20" t="n">
+      <c r="L8" s="23" t="n">
         <f aca="false">Segment_Data!L7</f>
         <v>2429</v>
       </c>
-      <c r="M8" s="21" t="n">
+      <c r="M8" s="24" t="n">
         <f aca="false">L8-K8</f>
         <v>1210</v>
       </c>
-      <c r="N8" s="10" t="n">
+      <c r="N8" s="13" t="n">
         <f aca="false">IFERROR(G8/D8-1,"")</f>
         <v>-0.0567549885508669</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="B9" s="9" t="n">
+      <c r="A9" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" s="12" t="n">
         <v>2548</v>
       </c>
-      <c r="C9" s="20" t="n">
+      <c r="C9" s="23" t="n">
         <f aca="false">Segment_Data!D8</f>
         <v>5037</v>
       </c>
-      <c r="D9" s="21" t="n">
+      <c r="D9" s="24" t="n">
         <f aca="false">C9-B9</f>
         <v>2489</v>
       </c>
-      <c r="E9" s="9" t="n">
+      <c r="E9" s="12" t="n">
         <v>2440</v>
       </c>
-      <c r="F9" s="20" t="n">
+      <c r="F9" s="23" t="n">
         <f aca="false">Segment_Data!E8</f>
         <v>4973</v>
       </c>
-      <c r="G9" s="21" t="n">
+      <c r="G9" s="24" t="n">
         <f aca="false">F9-E9</f>
         <v>2533</v>
       </c>
-      <c r="H9" s="9" t="n">
+      <c r="H9" s="12" t="n">
         <v>422</v>
       </c>
-      <c r="I9" s="20" t="n">
+      <c r="I9" s="23" t="n">
         <f aca="false">Segment_Data!K8</f>
         <v>832</v>
       </c>
-      <c r="J9" s="21" t="n">
+      <c r="J9" s="24" t="n">
         <f aca="false">I9-H9</f>
         <v>410</v>
       </c>
-      <c r="K9" s="9" t="n">
+      <c r="K9" s="12" t="n">
         <v>386</v>
       </c>
-      <c r="L9" s="20" t="n">
+      <c r="L9" s="23" t="n">
         <f aca="false">Segment_Data!L8</f>
         <v>803</v>
       </c>
-      <c r="M9" s="21" t="n">
+      <c r="M9" s="24" t="n">
         <f aca="false">L9-K9</f>
         <v>417</v>
       </c>
-      <c r="N9" s="10" t="n">
+      <c r="N9" s="13" t="n">
         <f aca="false">IFERROR(G9/D9-1,"")</f>
         <v>0.0176777822418641</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="B10" s="9" t="n">
+      <c r="A10" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="B10" s="12" t="n">
         <v>3318</v>
       </c>
-      <c r="C10" s="20" t="n">
+      <c r="C10" s="23" t="n">
         <f aca="false">Segment_Data!D9</f>
         <v>6498</v>
       </c>
-      <c r="D10" s="21" t="n">
+      <c r="D10" s="24" t="n">
         <f aca="false">C10-B10</f>
         <v>3180</v>
       </c>
-      <c r="E10" s="9" t="n">
+      <c r="E10" s="12" t="n">
         <v>3239</v>
       </c>
-      <c r="F10" s="20" t="n">
+      <c r="F10" s="23" t="n">
         <f aca="false">Segment_Data!E9</f>
         <v>6739</v>
       </c>
-      <c r="G10" s="21" t="n">
+      <c r="G10" s="24" t="n">
         <f aca="false">F10-E10</f>
         <v>3500</v>
       </c>
-      <c r="H10" s="9" t="n">
+      <c r="H10" s="12" t="n">
         <v>432</v>
       </c>
-      <c r="I10" s="20" t="n">
+      <c r="I10" s="23" t="n">
         <f aca="false">Segment_Data!K9</f>
         <v>777</v>
       </c>
-      <c r="J10" s="21" t="n">
+      <c r="J10" s="24" t="n">
         <f aca="false">I10-H10</f>
         <v>345</v>
       </c>
-      <c r="K10" s="9" t="n">
+      <c r="K10" s="12" t="n">
         <v>433</v>
       </c>
-      <c r="L10" s="20" t="n">
+      <c r="L10" s="23" t="n">
         <f aca="false">Segment_Data!L9</f>
         <v>943</v>
       </c>
-      <c r="M10" s="21" t="n">
+      <c r="M10" s="24" t="n">
         <f aca="false">L10-K10</f>
         <v>510</v>
       </c>
-      <c r="N10" s="10" t="n">
+      <c r="N10" s="13" t="n">
         <f aca="false">IFERROR(G10/D10-1,"")</f>
         <v>0.10062893081761</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="B11" s="9" t="n">
+      <c r="A11" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="B11" s="12" t="n">
         <v>3128</v>
       </c>
-      <c r="C11" s="20" t="n">
+      <c r="C11" s="23" t="n">
         <f aca="false">Segment_Data!D10</f>
         <v>6372</v>
       </c>
-      <c r="D11" s="21" t="n">
+      <c r="D11" s="24" t="n">
         <f aca="false">C11-B11</f>
         <v>3244</v>
       </c>
-      <c r="E11" s="9" t="n">
+      <c r="E11" s="12" t="n">
         <v>3096</v>
       </c>
-      <c r="F11" s="20" t="n">
+      <c r="F11" s="23" t="n">
         <f aca="false">Segment_Data!E10</f>
         <v>6378</v>
       </c>
-      <c r="G11" s="21" t="n">
+      <c r="G11" s="24" t="n">
         <f aca="false">F11-E11</f>
         <v>3282</v>
       </c>
-      <c r="H11" s="9" t="n">
+      <c r="H11" s="12" t="n">
         <v>678</v>
       </c>
-      <c r="I11" s="20" t="n">
+      <c r="I11" s="23" t="n">
         <f aca="false">Segment_Data!K10</f>
         <v>1291</v>
       </c>
-      <c r="J11" s="21" t="n">
+      <c r="J11" s="24" t="n">
         <f aca="false">I11-H11</f>
         <v>613</v>
       </c>
-      <c r="K11" s="9" t="n">
+      <c r="K11" s="12" t="n">
         <v>667</v>
       </c>
-      <c r="L11" s="20" t="n">
+      <c r="L11" s="23" t="n">
         <f aca="false">Segment_Data!L10</f>
         <v>1278</v>
       </c>
-      <c r="M11" s="21" t="n">
+      <c r="M11" s="24" t="n">
         <f aca="false">L11-K11</f>
         <v>611</v>
       </c>
-      <c r="N11" s="10" t="n">
+      <c r="N11" s="13" t="n">
         <f aca="false">IFERROR(G11/D11-1,"")</f>
         <v>0.0117139334155363</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="B12" s="9" t="n">
+      <c r="A12" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="B12" s="12" t="n">
         <v>137</v>
       </c>
-      <c r="C12" s="20" t="n">
+      <c r="C12" s="23" t="n">
         <f aca="false">Segment_Data!D11</f>
         <v>283</v>
       </c>
-      <c r="D12" s="21" t="n">
+      <c r="D12" s="24" t="n">
         <f aca="false">C12-B12</f>
         <v>146</v>
       </c>
-      <c r="E12" s="9" t="n">
+      <c r="E12" s="12" t="n">
         <v>146</v>
       </c>
-      <c r="F12" s="20" t="n">
+      <c r="F12" s="23" t="n">
         <f aca="false">Segment_Data!E11</f>
         <v>292</v>
       </c>
-      <c r="G12" s="21" t="n">
+      <c r="G12" s="24" t="n">
         <f aca="false">F12-E12</f>
         <v>146</v>
       </c>
-      <c r="H12" s="9" t="n">
+      <c r="H12" s="12" t="n">
         <v>-17</v>
       </c>
-      <c r="I12" s="20" t="n">
+      <c r="I12" s="23" t="n">
         <f aca="false">Segment_Data!K11</f>
         <v>-12</v>
       </c>
-      <c r="J12" s="21" t="n">
+      <c r="J12" s="24" t="n">
         <f aca="false">I12-H12</f>
         <v>5</v>
       </c>
-      <c r="K12" s="9" t="n">
+      <c r="K12" s="12" t="n">
         <v>-5</v>
       </c>
-      <c r="L12" s="20" t="n">
+      <c r="L12" s="23" t="n">
         <f aca="false">Segment_Data!L11</f>
         <v>-13</v>
       </c>
-      <c r="M12" s="21" t="n">
+      <c r="M12" s="24" t="n">
         <f aca="false">L12-K12</f>
         <v>-8</v>
       </c>
-      <c r="N12" s="10" t="n">
+      <c r="N12" s="13" t="n">
         <f aca="false">IFERROR(G12/D12-1,"")</f>
         <v>0</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="B13" s="13" t="n">
+      <c r="A13" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="B13" s="16" t="n">
         <f aca="false">SUM(B5:B12)</f>
         <v>46293</v>
       </c>
-      <c r="C13" s="13" t="n">
+      <c r="C13" s="16" t="n">
         <f aca="false">SUM(C5:C12)</f>
         <v>92998</v>
       </c>
-      <c r="D13" s="13" t="n">
+      <c r="D13" s="16" t="n">
         <f aca="false">SUM(D5:D12)</f>
         <v>46705</v>
       </c>
-      <c r="E13" s="13" t="n">
+      <c r="E13" s="16" t="n">
         <f aca="false">SUM(E5:E12)</f>
         <v>45045</v>
       </c>
-      <c r="F13" s="13" t="n">
+      <c r="F13" s="16" t="n">
         <f aca="false">SUM(F5:F12)</f>
         <v>91354</v>
       </c>
-      <c r="G13" s="13" t="n">
+      <c r="G13" s="16" t="n">
         <f aca="false">SUM(G5:G12)</f>
         <v>46309</v>
       </c>
-      <c r="H13" s="15" t="n">
+      <c r="H13" s="18" t="n">
         <v>3798</v>
       </c>
-      <c r="I13" s="22" t="n">
+      <c r="I13" s="25" t="n">
         <f aca="false">Segment_Data!K12</f>
         <v>16053</v>
       </c>
-      <c r="J13" s="13" t="n">
+      <c r="J13" s="16" t="n">
         <f aca="false">I13-H13</f>
         <v>12255</v>
       </c>
-      <c r="K13" s="15" t="n">
+      <c r="K13" s="18" t="n">
         <v>7841</v>
       </c>
-      <c r="L13" s="22" t="n">
+      <c r="L13" s="25" t="n">
         <f aca="false">Segment_Data!L12</f>
         <v>15704</v>
       </c>
-      <c r="M13" s="13" t="n">
+      <c r="M13" s="16" t="n">
         <f aca="false">L13-K13</f>
         <v>7863</v>
       </c>
-      <c r="N13" s="14" t="n">
+      <c r="N13" s="17" t="n">
         <f aca="false">IFERROR(G13/D13-1,"")</f>
         <v>-0.008478749598544</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="18" t="s">
-        <v>79</v>
-      </c>
-      <c r="B15" s="18"/>
-      <c r="C15" s="18"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="18"/>
-      <c r="G15" s="18"/>
-      <c r="H15" s="18"/>
-      <c r="I15" s="18"/>
-      <c r="J15" s="18"/>
-      <c r="K15" s="18"/>
-      <c r="L15" s="18"/>
-      <c r="M15" s="18"/>
+      <c r="A15" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="B15" s="21"/>
+      <c r="C15" s="21"/>
+      <c r="D15" s="21"/>
+      <c r="E15" s="21"/>
+      <c r="F15" s="21"/>
+      <c r="G15" s="21"/>
+      <c r="H15" s="21"/>
+      <c r="I15" s="21"/>
+      <c r="J15" s="21"/>
+      <c r="K15" s="21"/>
+      <c r="L15" s="21"/>
+      <c r="M15" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -3751,339 +3849,594 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
-  <sheetFormatPr defaultColWidth="8.71484375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:E39"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="48"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="2" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="8" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="2" style="8" width="14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="26" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="27" t="s">
+        <v>84</v>
+      </c>
+      <c r="B3" s="27" t="s">
+        <v>85</v>
+      </c>
+      <c r="C3" s="27" t="s">
+        <v>86</v>
+      </c>
+      <c r="D3" s="27" t="s">
+        <v>87</v>
+      </c>
+      <c r="E3" s="27" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="28" t="s">
+        <v>89</v>
+      </c>
+      <c r="B4" s="29" t="n">
+        <v>87088</v>
+      </c>
+      <c r="C4" s="29" t="n">
+        <v>94424</v>
+      </c>
+      <c r="D4" s="29" t="n">
+        <v>92998</v>
+      </c>
+      <c r="E4" s="29" t="n">
+        <v>91354</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="28" t="s">
+        <v>90</v>
+      </c>
+      <c r="B5" s="29" t="n">
+        <v>382</v>
+      </c>
+      <c r="C5" s="29" t="n">
+        <v>356</v>
+      </c>
+      <c r="D5" s="29" t="n">
+        <v>353</v>
+      </c>
+      <c r="E5" s="29" t="n">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="28" t="s">
+        <v>91</v>
+      </c>
+      <c r="B6" s="29" t="n">
+        <v>-45468</v>
+      </c>
+      <c r="C6" s="29" t="n">
+        <v>-51745</v>
+      </c>
+      <c r="D6" s="29" t="n">
+        <v>-50328</v>
+      </c>
+      <c r="E6" s="29" t="n">
+        <v>-48670</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="28" t="s">
+        <v>92</v>
+      </c>
+      <c r="B7" s="29" t="n">
+        <v>-7919</v>
+      </c>
+      <c r="C7" s="29" t="n">
+        <v>-8386</v>
+      </c>
+      <c r="D7" s="29" t="n">
+        <v>-7765</v>
+      </c>
+      <c r="E7" s="29" t="n">
+        <v>-7567</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="28" t="s">
+        <v>93</v>
+      </c>
+      <c r="B8" s="29" t="n">
+        <v>-17294</v>
+      </c>
+      <c r="C8" s="29" t="n">
+        <v>-16850</v>
+      </c>
+      <c r="D8" s="29" t="n">
+        <v>-17549</v>
+      </c>
+      <c r="E8" s="29" t="n">
+        <v>-18112</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="28" t="s">
+        <v>94</v>
+      </c>
+      <c r="B9" s="29" t="n">
+        <v>-1670</v>
+      </c>
+      <c r="C9" s="29" t="n">
+        <v>-1696</v>
+      </c>
+      <c r="D9" s="29" t="n">
+        <v>-1656</v>
+      </c>
+      <c r="E9" s="29" t="n">
+        <v>-1667</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="30" t="s">
+        <v>95</v>
+      </c>
+      <c r="B10" s="31" t="n">
+        <f aca="false">SUM(B4:B9)</f>
+        <v>15119</v>
+      </c>
+      <c r="C10" s="31" t="n">
+        <f aca="false">SUM(C4:C9)</f>
+        <v>16103</v>
+      </c>
+      <c r="D10" s="31" t="n">
+        <f aca="false">SUM(D4:D9)</f>
+        <v>16053</v>
+      </c>
+      <c r="E10" s="31" t="n">
+        <f aca="false">SUM(E4:E9)</f>
+        <v>15704</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="28" t="s">
+        <v>96</v>
+      </c>
+      <c r="B11" s="29" t="n">
+        <v>171</v>
+      </c>
+      <c r="C11" s="29" t="n">
+        <v>107</v>
+      </c>
+      <c r="D11" s="29" t="n">
+        <v>132</v>
+      </c>
+      <c r="E11" s="29" t="n">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="28" t="s">
+        <v>97</v>
+      </c>
+      <c r="B12" s="29" t="n">
+        <v>-3131</v>
+      </c>
+      <c r="C12" s="29" t="n">
+        <v>-3015</v>
+      </c>
+      <c r="D12" s="29" t="n">
+        <v>-1665</v>
+      </c>
+      <c r="E12" s="29" t="n">
+        <v>-1195</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="30" t="s">
+        <v>98</v>
+      </c>
+      <c r="B13" s="31" t="n">
+        <f aca="false">B10+B11+B12</f>
+        <v>12159</v>
+      </c>
+      <c r="C13" s="31" t="n">
+        <f aca="false">C10+C11+C12</f>
+        <v>13195</v>
+      </c>
+      <c r="D13" s="31" t="n">
+        <f aca="false">D10+D11+D12</f>
+        <v>14520</v>
+      </c>
+      <c r="E13" s="31" t="n">
+        <f aca="false">E10+E11+E12</f>
+        <v>14633</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="B14" s="29" t="n">
+        <v>698</v>
+      </c>
+      <c r="C14" s="29" t="n">
+        <v>340</v>
+      </c>
+      <c r="D14" s="29" t="n">
+        <v>298</v>
+      </c>
+      <c r="E14" s="29" t="n">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="28" t="s">
+        <v>100</v>
+      </c>
+      <c r="B15" s="29" t="n">
+        <v>-1178</v>
+      </c>
+      <c r="C15" s="29" t="n">
+        <v>-1209</v>
+      </c>
+      <c r="D15" s="29" t="n">
+        <v>-755</v>
+      </c>
+      <c r="E15" s="29" t="n">
+        <v>-383</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="B16" s="31" t="n">
+        <f aca="false">B13+B14+B15</f>
+        <v>11679</v>
+      </c>
+      <c r="C16" s="31" t="n">
+        <f aca="false">C13+C14+C15</f>
+        <v>12326</v>
+      </c>
+      <c r="D16" s="31" t="n">
+        <f aca="false">D13+D14+D15</f>
+        <v>14063</v>
+      </c>
+      <c r="E16" s="31" t="n">
+        <f aca="false">E13+E14+E15</f>
+        <v>14724</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="28" t="s">
+        <v>102</v>
+      </c>
+      <c r="B17" s="29" t="n">
         <v>80</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="24" t="s">
-        <v>81</v>
-      </c>
-      <c r="B3" s="25" t="s">
-        <v>82</v>
-      </c>
-      <c r="C3" s="25" t="s">
-        <v>83</v>
-      </c>
-      <c r="D3" s="25" t="s">
-        <v>84</v>
-      </c>
-      <c r="E3" s="25" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
-        <v>86</v>
-      </c>
-      <c r="B4" s="26" t="n">
-        <f aca="false">Segment_Data!B12</f>
-        <v>87088</v>
-      </c>
-      <c r="C4" s="26" t="n">
-        <f aca="false">Segment_Data!C12</f>
-        <v>94424</v>
-      </c>
-      <c r="D4" s="26" t="n">
-        <f aca="false">Segment_Data!D12</f>
-        <v>92998</v>
-      </c>
-      <c r="E4" s="26" t="n">
-        <f aca="false">Segment_Data!E12</f>
-        <v>91354</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
-        <v>87</v>
-      </c>
-      <c r="B5" s="26" t="n">
-        <f aca="false">Segment_Data!I12</f>
-        <v>15119</v>
-      </c>
-      <c r="C5" s="26" t="n">
-        <f aca="false">Segment_Data!J12</f>
-        <v>16103</v>
-      </c>
-      <c r="D5" s="26" t="n">
-        <f aca="false">Segment_Data!K12</f>
-        <v>16053</v>
-      </c>
-      <c r="E5" s="26" t="n">
-        <f aca="false">Segment_Data!L12</f>
-        <v>15704</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
-        <v>88</v>
-      </c>
-      <c r="B6" s="27" t="n">
-        <f aca="false">IFERROR(B5/B4,"")</f>
+      <c r="C17" s="29" t="n">
+        <v>210</v>
+      </c>
+      <c r="D17" s="29" t="n">
+        <v>284</v>
+      </c>
+      <c r="E17" s="29" t="n">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="28" t="s">
+        <v>103</v>
+      </c>
+      <c r="B18" s="29" t="n">
+        <v>-953</v>
+      </c>
+      <c r="C18" s="29" t="n">
+        <v>-1250</v>
+      </c>
+      <c r="D18" s="29" t="n">
+        <v>-1644</v>
+      </c>
+      <c r="E18" s="29" t="n">
+        <v>-1843</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="32" t="s">
+        <v>104</v>
+      </c>
+      <c r="B19" s="33" t="n">
+        <f aca="false">B17+B18</f>
+        <v>-873</v>
+      </c>
+      <c r="C19" s="33" t="n">
+        <f aca="false">C17+C18</f>
+        <v>-1040</v>
+      </c>
+      <c r="D19" s="33" t="n">
+        <f aca="false">D17+D18</f>
+        <v>-1360</v>
+      </c>
+      <c r="E19" s="33" t="n">
+        <f aca="false">E17+E18</f>
+        <v>-1485</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="30" t="s">
+        <v>105</v>
+      </c>
+      <c r="B20" s="31" t="n">
+        <f aca="false">B16+B19</f>
+        <v>10806</v>
+      </c>
+      <c r="C20" s="31" t="n">
+        <f aca="false">C16+C19</f>
+        <v>11286</v>
+      </c>
+      <c r="D20" s="31" t="n">
+        <f aca="false">D16+D19</f>
+        <v>12703</v>
+      </c>
+      <c r="E20" s="31" t="n">
+        <f aca="false">E16+E19</f>
+        <v>13239</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="28" t="s">
+        <v>106</v>
+      </c>
+      <c r="B21" s="29" t="n">
+        <v>8651</v>
+      </c>
+      <c r="C21" s="29" t="n">
+        <v>1040</v>
+      </c>
+      <c r="D21" s="29" t="n">
+        <v>1120</v>
+      </c>
+      <c r="E21" s="29" t="n">
+        <v>1249</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="28" t="s">
+        <v>107</v>
+      </c>
+      <c r="B22" s="29" t="n">
+        <v>-2261</v>
+      </c>
+      <c r="C22" s="29" t="n">
+        <v>-2730</v>
+      </c>
+      <c r="D22" s="29" t="n">
+        <v>-2314</v>
+      </c>
+      <c r="E22" s="29" t="n">
+        <v>-3314</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="30" t="s">
+        <v>108</v>
+      </c>
+      <c r="B23" s="31" t="n">
+        <f aca="false">B20+B21+B22</f>
+        <v>17196</v>
+      </c>
+      <c r="C23" s="31" t="n">
+        <f aca="false">C20+C21+C22</f>
+        <v>9596</v>
+      </c>
+      <c r="D23" s="31" t="n">
+        <f aca="false">D20+D21+D22</f>
+        <v>11509</v>
+      </c>
+      <c r="E23" s="31" t="n">
+        <f aca="false">E20+E21+E22</f>
+        <v>11174</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="28" t="s">
+        <v>109</v>
+      </c>
+      <c r="B24" s="29" t="n">
+        <v>291</v>
+      </c>
+      <c r="C24" s="29" t="n">
+        <v>326</v>
+      </c>
+      <c r="D24" s="29" t="n">
+        <v>300</v>
+      </c>
+      <c r="E24" s="29" t="n">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="30" t="s">
+        <v>110</v>
+      </c>
+      <c r="B25" s="31" t="n">
+        <f aca="false">B23-B24</f>
+        <v>16905</v>
+      </c>
+      <c r="C25" s="31" t="n">
+        <f aca="false">C23-C24</f>
+        <v>9270</v>
+      </c>
+      <c r="D25" s="31" t="n">
+        <f aca="false">D23-D24</f>
+        <v>11209</v>
+      </c>
+      <c r="E25" s="31" t="n">
+        <f aca="false">E23-E24</f>
+        <v>10884</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="28" t="s">
+        <v>111</v>
+      </c>
+      <c r="B27" s="34" t="n">
+        <f aca="false">IFERROR(B10/B4,"")</f>
         <v>0.173606007716333</v>
       </c>
-      <c r="C6" s="27" t="n">
-        <f aca="false">IFERROR(C5/C4,"")</f>
+      <c r="C27" s="34" t="n">
+        <f aca="false">IFERROR(C10/C4,"")</f>
         <v>0.170539269677201</v>
       </c>
-      <c r="D6" s="27" t="n">
-        <f aca="false">IFERROR(D5/D4,"")</f>
+      <c r="D27" s="34" t="n">
+        <f aca="false">IFERROR(D10/D4,"")</f>
         <v>0.172616615411084</v>
       </c>
-      <c r="E6" s="27" t="n">
-        <f aca="false">IFERROR(E5/E4,"")</f>
+      <c r="E27" s="34" t="n">
+        <f aca="false">IFERROR(E10/E4,"")</f>
         <v>0.171902708146332</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
-        <v>89</v>
-      </c>
-      <c r="B7" s="28" t="n">
-        <v>840</v>
-      </c>
-      <c r="C7" s="28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="D7" s="28" t="n">
-        <v>1400</v>
-      </c>
-      <c r="E7" s="28" t="n">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
-        <v>90</v>
-      </c>
-      <c r="B8" s="29" t="n">
-        <f aca="false">B5-B7</f>
-        <v>14279</v>
-      </c>
-      <c r="C8" s="29" t="n">
-        <f aca="false">C5-C7</f>
-        <v>15103</v>
-      </c>
-      <c r="D8" s="29" t="n">
-        <f aca="false">D5-D7</f>
-        <v>14653</v>
-      </c>
-      <c r="E8" s="29" t="n">
-        <f aca="false">E5-E7</f>
-        <v>14204</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
-        <v>91</v>
-      </c>
-      <c r="B9" s="30" t="n">
-        <v>0.209</v>
-      </c>
-      <c r="C9" s="30" t="n">
-        <v>0.242</v>
-      </c>
-      <c r="D9" s="30" t="n">
-        <v>0.182</v>
-      </c>
-      <c r="E9" s="30" t="n">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
-        <v>92</v>
-      </c>
-      <c r="B10" s="29" t="n">
-        <f aca="false">B8*B9</f>
-        <v>2984.311</v>
-      </c>
-      <c r="C10" s="29" t="n">
-        <f aca="false">C8*C9</f>
-        <v>3654.926</v>
-      </c>
-      <c r="D10" s="29" t="n">
-        <f aca="false">D8*D9</f>
-        <v>2666.846</v>
-      </c>
-      <c r="E10" s="29" t="n">
-        <f aca="false">E8*E9</f>
-        <v>3551</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
-        <v>93</v>
-      </c>
-      <c r="B11" s="28" t="n">
-        <v>16900</v>
-      </c>
-      <c r="C11" s="28" t="n">
-        <v>9300</v>
-      </c>
-      <c r="D11" s="28" t="n">
-        <v>11209</v>
-      </c>
-      <c r="E11" s="28" t="n">
-        <v>10884</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
-        <v>94</v>
-      </c>
-      <c r="B12" s="27" t="n">
-        <f aca="false">IFERROR(B11/B4,"")</f>
-        <v>0.194056586441301</v>
-      </c>
-      <c r="C12" s="27" t="n">
-        <f aca="false">IFERROR(C11/C4,"")</f>
-        <v>0.0984919088367364</v>
-      </c>
-      <c r="D12" s="27" t="n">
-        <f aca="false">IFERROR(D11/D4,"")</f>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="28" t="s">
+        <v>112</v>
+      </c>
+      <c r="B28" s="34" t="n">
+        <f aca="false">IFERROR(B13/B4,"")</f>
+        <v>0.139617398493478</v>
+      </c>
+      <c r="C28" s="34" t="n">
+        <f aca="false">IFERROR(C13/C4,"")</f>
+        <v>0.139742014742015</v>
+      </c>
+      <c r="D28" s="34" t="n">
+        <f aca="false">IFERROR(D13/D4,"")</f>
+        <v>0.15613238994387</v>
+      </c>
+      <c r="E28" s="34" t="n">
+        <f aca="false">IFERROR(E13/E4,"")</f>
+        <v>0.160179083565033</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="28" t="s">
+        <v>113</v>
+      </c>
+      <c r="B29" s="34" t="n">
+        <f aca="false">IFERROR(B16/B4,"")</f>
+        <v>0.134105732133015</v>
+      </c>
+      <c r="C29" s="34" t="n">
+        <f aca="false">IFERROR(C16/C4,"")</f>
+        <v>0.130538846056087</v>
+      </c>
+      <c r="D29" s="34" t="n">
+        <f aca="false">IFERROR(D16/D4,"")</f>
+        <v>0.151218305770017</v>
+      </c>
+      <c r="E29" s="34" t="n">
+        <f aca="false">IFERROR(E16/E4,"")</f>
+        <v>0.161175208529457</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="28" t="s">
+        <v>114</v>
+      </c>
+      <c r="B30" s="34" t="n">
+        <f aca="false">IFERROR(B25/B4,"")</f>
+        <v>0.194113999632556</v>
+      </c>
+      <c r="C30" s="34" t="n">
+        <f aca="false">IFERROR(C25/C4,"")</f>
+        <v>0.0981741930017792</v>
+      </c>
+      <c r="D30" s="34" t="n">
+        <f aca="false">IFERROR(D25/D4,"")</f>
         <v>0.120529473752124</v>
       </c>
-      <c r="E12" s="27" t="n">
-        <f aca="false">IFERROR(E11/E4,"")</f>
+      <c r="E30" s="34" t="n">
+        <f aca="false">IFERROR(E25/E4,"")</f>
         <v>0.119140924316396</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
-        <v>95</v>
-      </c>
-      <c r="B13" s="31" t="n">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="28" t="s">
+        <v>115</v>
+      </c>
+      <c r="B31" s="34" t="n">
+        <f aca="false">IFERROR(-B22/B20,"")</f>
+        <v>0.209235609846382</v>
+      </c>
+      <c r="C31" s="34" t="n">
+        <f aca="false">IFERROR(-C22/C20,"")</f>
+        <v>0.241892610313663</v>
+      </c>
+      <c r="D31" s="34" t="n">
+        <f aca="false">IFERROR(-D22/D20,"")</f>
+        <v>0.182161694088011</v>
+      </c>
+      <c r="E31" s="34" t="n">
+        <f aca="false">IFERROR(-E22/E20,"")</f>
+        <v>0.250321021225168</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="28" t="s">
+        <v>116</v>
+      </c>
+      <c r="B33" s="35" t="n">
         <v>6.06</v>
       </c>
-      <c r="C13" s="31" t="n">
+      <c r="C33" s="35" t="n">
         <v>3.42</v>
       </c>
-      <c r="D13" s="31" t="n">
+      <c r="D33" s="35" t="n">
         <v>4.24</v>
       </c>
-      <c r="E13" s="31" t="n">
+      <c r="E33" s="35" t="n">
         <v>4.19</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
-        <v>96</v>
-      </c>
-      <c r="B15" s="28" t="n">
-        <v>16600</v>
-      </c>
-      <c r="C15" s="29" t="s">
-        <v>97</v>
-      </c>
-      <c r="D15" s="28" t="n">
-        <v>19200</v>
-      </c>
-      <c r="E15" s="28" t="n">
-        <v>19600</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
-        <v>98</v>
-      </c>
-      <c r="B16" s="28" t="n">
-        <v>8700</v>
-      </c>
-      <c r="C16" s="28" t="n">
-        <v>6600</v>
-      </c>
-      <c r="D16" s="28" t="n">
-        <v>10403</v>
-      </c>
-      <c r="E16" s="28" t="n">
-        <v>10666</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
-        <v>99</v>
-      </c>
-      <c r="B17" s="27" t="n">
-        <f aca="false">IFERROR(B16/B4,"")</f>
-        <v>0.0998989527833915</v>
-      </c>
-      <c r="C17" s="27" t="n">
-        <f aca="false">IFERROR(C16/C4,"")</f>
-        <v>0.0698974836905871</v>
-      </c>
-      <c r="D17" s="27" t="n">
-        <f aca="false">IFERROR(D16/D4,"")</f>
-        <v>0.11186262070152</v>
-      </c>
-      <c r="E17" s="27" t="n">
-        <f aca="false">IFERROR(E16/E4,"")</f>
-        <v>0.11675460297305</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
-        <v>100</v>
-      </c>
-      <c r="B18" s="29" t="n">
-        <f aca="false">B15-B16</f>
-        <v>7900</v>
-      </c>
-      <c r="C18" s="32" t="s">
-        <v>97</v>
-      </c>
-      <c r="D18" s="29" t="n">
-        <f aca="false">D15-D16</f>
-        <v>8797</v>
-      </c>
-      <c r="E18" s="29" t="n">
-        <f aca="false">E15-E16</f>
-        <v>8934</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
-        <v>101</v>
-      </c>
-      <c r="B20" s="28" t="n">
-        <v>32900</v>
-      </c>
-      <c r="C20" s="28" t="n">
-        <v>48200</v>
-      </c>
-      <c r="D20" s="28" t="n">
-        <v>49600</v>
-      </c>
-      <c r="E20" s="28" t="n">
-        <v>56000</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="33" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="33" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="33" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="33" t="s">
-        <v>105</v>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="B34" s="35" t="n">
+        <v>6.06</v>
+      </c>
+      <c r="C34" s="35" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="D34" s="35" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="E34" s="35" t="n">
+        <v>4.19</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="36" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="36" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="36" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="36" t="s">
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -4094,6 +4447,1211 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
-  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:E57"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="8" width="58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="2" style="8" width="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="26" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="27" t="s">
+        <v>84</v>
+      </c>
+      <c r="B3" s="27" t="s">
+        <v>85</v>
+      </c>
+      <c r="C3" s="27" t="s">
+        <v>86</v>
+      </c>
+      <c r="D3" s="27" t="s">
+        <v>87</v>
+      </c>
+      <c r="E3" s="27" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="37" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="32" t="s">
+        <v>124</v>
+      </c>
+      <c r="B5" s="33" t="n">
+        <f aca="false">Income_Statement!B16</f>
+        <v>11679</v>
+      </c>
+      <c r="C5" s="33" t="n">
+        <f aca="false">Income_Statement!C16</f>
+        <v>12326</v>
+      </c>
+      <c r="D5" s="33" t="n">
+        <f aca="false">Income_Statement!D16</f>
+        <v>14063</v>
+      </c>
+      <c r="E5" s="33" t="n">
+        <f aca="false">Income_Statement!E16</f>
+        <v>14724</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="B6" s="29" t="n">
+        <v>3440</v>
+      </c>
+      <c r="C6" s="29" t="n">
+        <v>3541</v>
+      </c>
+      <c r="D6" s="29" t="n">
+        <v>3458</v>
+      </c>
+      <c r="E6" s="29" t="n">
+        <v>3582</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="28" t="s">
+        <v>126</v>
+      </c>
+      <c r="B7" s="29" t="n">
+        <v>2614</v>
+      </c>
+      <c r="C7" s="29" t="n">
+        <v>2726</v>
+      </c>
+      <c r="D7" s="29" t="n">
+        <v>647</v>
+      </c>
+      <c r="E7" s="29" t="n">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="28" t="s">
+        <v>127</v>
+      </c>
+      <c r="B8" s="29" t="n">
+        <v>-235</v>
+      </c>
+      <c r="C8" s="29" t="n">
+        <v>79</v>
+      </c>
+      <c r="D8" s="29" t="n">
+        <v>221</v>
+      </c>
+      <c r="E8" s="29" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="B9" s="29" t="n">
+        <v>-253</v>
+      </c>
+      <c r="C9" s="29" t="n">
+        <v>216</v>
+      </c>
+      <c r="D9" s="29" t="n">
+        <v>82</v>
+      </c>
+      <c r="E9" s="29" t="n">
+        <v>-229</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="30" t="s">
+        <v>129</v>
+      </c>
+      <c r="B10" s="31" t="n">
+        <f aca="false">SUM(B5:B9)</f>
+        <v>17245</v>
+      </c>
+      <c r="C10" s="31" t="n">
+        <f aca="false">SUM(C5:C9)</f>
+        <v>18888</v>
+      </c>
+      <c r="D10" s="31" t="n">
+        <f aca="false">SUM(D5:D9)</f>
+        <v>18471</v>
+      </c>
+      <c r="E10" s="31" t="n">
+        <f aca="false">SUM(E5:E9)</f>
+        <v>18719</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="28" t="s">
+        <v>130</v>
+      </c>
+      <c r="B11" s="29" t="n">
+        <v>-173</v>
+      </c>
+      <c r="C11" s="29" t="n">
+        <v>-3133</v>
+      </c>
+      <c r="D11" s="29" t="n">
+        <v>1134</v>
+      </c>
+      <c r="E11" s="29" t="n">
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="28" t="s">
+        <v>131</v>
+      </c>
+      <c r="B12" s="29" t="n">
+        <v>-427</v>
+      </c>
+      <c r="C12" s="29" t="n">
+        <v>-514</v>
+      </c>
+      <c r="D12" s="29" t="n">
+        <v>-425</v>
+      </c>
+      <c r="E12" s="29" t="n">
+        <v>-334</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="30" t="s">
+        <v>132</v>
+      </c>
+      <c r="B13" s="31" t="n">
+        <f aca="false">B10+B11+B12</f>
+        <v>16645</v>
+      </c>
+      <c r="C13" s="31" t="n">
+        <f aca="false">C10+C11+C12</f>
+        <v>15241</v>
+      </c>
+      <c r="D13" s="31" t="n">
+        <f aca="false">D10+D11+D12</f>
+        <v>19180</v>
+      </c>
+      <c r="E13" s="31" t="n">
+        <f aca="false">E10+E11+E12</f>
+        <v>19593</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="28" t="s">
+        <v>133</v>
+      </c>
+      <c r="B14" s="29" t="n">
+        <v>-753</v>
+      </c>
+      <c r="C14" s="29" t="n">
+        <v>-953</v>
+      </c>
+      <c r="D14" s="29" t="n">
+        <v>-1330</v>
+      </c>
+      <c r="E14" s="29" t="n">
+        <v>-1539</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="28" t="s">
+        <v>134</v>
+      </c>
+      <c r="B15" s="29" t="n">
+        <v>43</v>
+      </c>
+      <c r="C15" s="29" t="n">
+        <v>118</v>
+      </c>
+      <c r="D15" s="29" t="n">
+        <v>193</v>
+      </c>
+      <c r="E15" s="29" t="n">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="28" t="s">
+        <v>135</v>
+      </c>
+      <c r="B16" s="29" t="n">
+        <v>-2722</v>
+      </c>
+      <c r="C16" s="29" t="n">
+        <v>-3107</v>
+      </c>
+      <c r="D16" s="29" t="n">
+        <v>-2801</v>
+      </c>
+      <c r="E16" s="29" t="n">
+        <v>-2411</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="28" t="s">
+        <v>136</v>
+      </c>
+      <c r="B17" s="29" t="n">
+        <v>651</v>
+      </c>
+      <c r="C17" s="29" t="n">
+        <v>608</v>
+      </c>
+      <c r="D17" s="29" t="n">
+        <v>699</v>
+      </c>
+      <c r="E17" s="29" t="n">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="30" t="s">
+        <v>137</v>
+      </c>
+      <c r="B18" s="31" t="n">
+        <f aca="false">B13+B14+B15+B16+B17</f>
+        <v>13864</v>
+      </c>
+      <c r="C18" s="31" t="n">
+        <f aca="false">C13+C14+C15+C16+C17</f>
+        <v>11907</v>
+      </c>
+      <c r="D18" s="31" t="n">
+        <f aca="false">D13+D14+D15+D16+D17</f>
+        <v>15941</v>
+      </c>
+      <c r="E18" s="31" t="n">
+        <f aca="false">E13+E14+E15+E16+E17</f>
+        <v>16675</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="37" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="28" t="s">
+        <v>139</v>
+      </c>
+      <c r="B21" s="29" t="n">
+        <v>-4880</v>
+      </c>
+      <c r="C21" s="29" t="n">
+        <v>-5095</v>
+      </c>
+      <c r="D21" s="29" t="n">
+        <v>-5714</v>
+      </c>
+      <c r="E21" s="29" t="n">
+        <v>-5638</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="28" t="s">
+        <v>140</v>
+      </c>
+      <c r="B22" s="29" t="n">
+        <v>-461</v>
+      </c>
+      <c r="C22" s="29" t="n">
+        <v>-266</v>
+      </c>
+      <c r="D22" s="29" t="n">
+        <v>-489</v>
+      </c>
+      <c r="E22" s="29" t="n">
+        <v>-325</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="28" t="s">
+        <v>141</v>
+      </c>
+      <c r="B23" s="29" t="n">
+        <v>-6394</v>
+      </c>
+      <c r="C23" s="29" t="n">
+        <v>-1710</v>
+      </c>
+      <c r="D23" s="29" t="n">
+        <v>-211</v>
+      </c>
+      <c r="E23" s="29" t="n">
+        <v>-809</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="28" t="s">
+        <v>142</v>
+      </c>
+      <c r="B24" s="29" t="n">
+        <v>3530</v>
+      </c>
+      <c r="C24" s="29" t="n">
+        <v>160</v>
+      </c>
+      <c r="D24" s="29" t="n">
+        <v>215</v>
+      </c>
+      <c r="E24" s="29" t="n">
+        <v>-23</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="28" t="s">
+        <v>143</v>
+      </c>
+      <c r="B25" s="29" t="n">
+        <v>-715</v>
+      </c>
+      <c r="C25" s="29" t="n">
+        <v>-918</v>
+      </c>
+      <c r="D25" s="29" t="n">
+        <v>-582</v>
+      </c>
+      <c r="E25" s="29" t="n">
+        <v>-532</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="28" t="s">
+        <v>144</v>
+      </c>
+      <c r="B26" s="29" t="n">
+        <v>9294</v>
+      </c>
+      <c r="C26" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="28" t="s">
+        <v>145</v>
+      </c>
+      <c r="B27" s="29" t="n">
+        <v>-3610</v>
+      </c>
+      <c r="C27" s="29" t="n">
+        <v>5902</v>
+      </c>
+      <c r="D27" s="29" t="n">
+        <v>-80</v>
+      </c>
+      <c r="E27" s="29" t="n">
+        <v>-1251</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="28" t="s">
+        <v>146</v>
+      </c>
+      <c r="B28" s="29" t="n">
+        <v>192</v>
+      </c>
+      <c r="C28" s="29" t="n">
+        <v>24</v>
+      </c>
+      <c r="D28" s="29" t="n">
+        <v>665</v>
+      </c>
+      <c r="E28" s="29" t="n">
+        <v>-46</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="30" t="s">
+        <v>147</v>
+      </c>
+      <c r="B29" s="31" t="n">
+        <f aca="false">SUM(B21:B28)</f>
+        <v>-3044</v>
+      </c>
+      <c r="C29" s="31" t="n">
+        <f aca="false">SUM(C21:C28)</f>
+        <v>-1903</v>
+      </c>
+      <c r="D29" s="31" t="n">
+        <f aca="false">SUM(D21:D28)</f>
+        <v>-6196</v>
+      </c>
+      <c r="E29" s="31" t="n">
+        <f aca="false">SUM(E21:E28)</f>
+        <v>-8624</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="37" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="28" t="s">
+        <v>149</v>
+      </c>
+      <c r="B32" s="29" t="n">
+        <v>-7681</v>
+      </c>
+      <c r="C32" s="29" t="n">
+        <v>-7618</v>
+      </c>
+      <c r="D32" s="29" t="n">
+        <v>-7829</v>
+      </c>
+      <c r="E32" s="29" t="n">
+        <v>-7816</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="28" t="s">
+        <v>150</v>
+      </c>
+      <c r="B33" s="29" t="n">
+        <v>-302</v>
+      </c>
+      <c r="C33" s="29" t="n">
+        <v>-284</v>
+      </c>
+      <c r="D33" s="29" t="n">
+        <v>-323</v>
+      </c>
+      <c r="E33" s="29" t="n">
+        <v>-174</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="28" t="s">
+        <v>151</v>
+      </c>
+      <c r="B34" s="29" t="n">
+        <v>-601</v>
+      </c>
+      <c r="C34" s="29" t="n">
+        <v>-605</v>
+      </c>
+      <c r="D34" s="29" t="n">
+        <v>-52</v>
+      </c>
+      <c r="E34" s="29" t="n">
+        <v>-27</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="28" t="s">
+        <v>152</v>
+      </c>
+      <c r="B35" s="29" t="n">
+        <v>-6548</v>
+      </c>
+      <c r="C35" s="29" t="n">
+        <v>-10679</v>
+      </c>
+      <c r="D35" s="29" t="n">
+        <v>-5234</v>
+      </c>
+      <c r="E35" s="29" t="n">
+        <v>-4678</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="28" t="s">
+        <v>153</v>
+      </c>
+      <c r="B36" s="29" t="n">
+        <v>11339</v>
+      </c>
+      <c r="C36" s="29" t="n">
+        <v>10936</v>
+      </c>
+      <c r="D36" s="29" t="n">
+        <v>9806</v>
+      </c>
+      <c r="E36" s="29" t="n">
+        <v>7992</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="28" t="s">
+        <v>154</v>
+      </c>
+      <c r="B37" s="29" t="n">
+        <v>-4474</v>
+      </c>
+      <c r="C37" s="29" t="n">
+        <v>-3283</v>
+      </c>
+      <c r="D37" s="29" t="n">
+        <v>-3589</v>
+      </c>
+      <c r="E37" s="29" t="n">
+        <v>-5055</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="28" t="s">
+        <v>155</v>
+      </c>
+      <c r="B38" s="29" t="n">
+        <v>-885</v>
+      </c>
+      <c r="C38" s="29" t="n">
+        <v>148</v>
+      </c>
+      <c r="D38" s="29" t="n">
+        <v>-2537</v>
+      </c>
+      <c r="E38" s="29" t="n">
+        <v>2396</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="30" t="s">
+        <v>156</v>
+      </c>
+      <c r="B39" s="31" t="n">
+        <f aca="false">SUM(B32:B38)</f>
+        <v>-9152</v>
+      </c>
+      <c r="C39" s="31" t="n">
+        <f aca="false">SUM(C32:C38)</f>
+        <v>-11385</v>
+      </c>
+      <c r="D39" s="31" t="n">
+        <f aca="false">SUM(D32:D38)</f>
+        <v>-9758</v>
+      </c>
+      <c r="E39" s="31" t="n">
+        <f aca="false">SUM(E32:E38)</f>
+        <v>-7362</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="37" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="28" t="s">
+        <v>158</v>
+      </c>
+      <c r="B42" s="29" t="n">
+        <v>89</v>
+      </c>
+      <c r="C42" s="29" t="n">
+        <v>-100</v>
+      </c>
+      <c r="D42" s="29" t="n">
+        <v>-682</v>
+      </c>
+      <c r="E42" s="29" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="30" t="s">
+        <v>159</v>
+      </c>
+      <c r="B43" s="31" t="n">
+        <f aca="false">B18+B29+B39+B42</f>
+        <v>1757</v>
+      </c>
+      <c r="C43" s="31" t="n">
+        <f aca="false">C18+C29+C39+C42</f>
+        <v>-1481</v>
+      </c>
+      <c r="D43" s="31" t="n">
+        <f aca="false">D18+D29+D39+D42</f>
+        <v>-695</v>
+      </c>
+      <c r="E43" s="31" t="n">
+        <f aca="false">E18+E29+E39+E42</f>
+        <v>742</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="28" t="s">
+        <v>160</v>
+      </c>
+      <c r="B44" s="29" t="n">
+        <v>5235</v>
+      </c>
+      <c r="C44" s="29" t="n">
+        <v>6992</v>
+      </c>
+      <c r="D44" s="29" t="n">
+        <v>5511</v>
+      </c>
+      <c r="E44" s="29" t="n">
+        <v>4816</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="B45" s="31" t="n">
+        <f aca="false">B44+B43</f>
+        <v>6992</v>
+      </c>
+      <c r="C45" s="31" t="n">
+        <f aca="false">C44+C43</f>
+        <v>5511</v>
+      </c>
+      <c r="D45" s="31" t="n">
+        <f aca="false">D44+D43</f>
+        <v>4816</v>
+      </c>
+      <c r="E45" s="31" t="n">
+        <f aca="false">E44+E43</f>
+        <v>5558</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="28" t="s">
+        <v>162</v>
+      </c>
+      <c r="B46" s="29" t="n">
+        <v>-4</v>
+      </c>
+      <c r="C46" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" s="29" t="n">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="30" t="s">
+        <v>163</v>
+      </c>
+      <c r="B47" s="31" t="n">
+        <f aca="false">B45+B46</f>
+        <v>6988</v>
+      </c>
+      <c r="C47" s="31" t="n">
+        <f aca="false">C45+C46</f>
+        <v>5511</v>
+      </c>
+      <c r="D47" s="31" t="n">
+        <f aca="false">D45+D46</f>
+        <v>4816</v>
+      </c>
+      <c r="E47" s="31" t="n">
+        <f aca="false">E45+E46</f>
+        <v>5556</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="37" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="28" t="s">
+        <v>165</v>
+      </c>
+      <c r="B50" s="29" t="n">
+        <v>8700</v>
+      </c>
+      <c r="C50" s="29" t="n">
+        <v>6600</v>
+      </c>
+      <c r="D50" s="29" t="n">
+        <v>10403</v>
+      </c>
+      <c r="E50" s="29" t="n">
+        <v>10666</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="30" t="s">
+        <v>166</v>
+      </c>
+      <c r="B51" s="31" t="n">
+        <f aca="false">B18+B21+B22</f>
+        <v>8523</v>
+      </c>
+      <c r="C51" s="31" t="n">
+        <f aca="false">C18+C21+C22</f>
+        <v>6546</v>
+      </c>
+      <c r="D51" s="31" t="n">
+        <f aca="false">D18+D21+D22</f>
+        <v>9738</v>
+      </c>
+      <c r="E51" s="31" t="n">
+        <f aca="false">E18+E21+E22</f>
+        <v>10712</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="32" t="s">
+        <v>167</v>
+      </c>
+      <c r="B52" s="38" t="n">
+        <f aca="false">IFERROR(B50/Income_Statement!B4,"")</f>
+        <v>0.0998989527833915</v>
+      </c>
+      <c r="C52" s="38" t="n">
+        <f aca="false">IFERROR(C50/Income_Statement!C4,"")</f>
+        <v>0.0698974836905871</v>
+      </c>
+      <c r="D52" s="38" t="n">
+        <f aca="false">IFERROR(D50/Income_Statement!D4,"")</f>
+        <v>0.11186262070152</v>
+      </c>
+      <c r="E52" s="38" t="n">
+        <f aca="false">IFERROR(E50/Income_Statement!E4,"")</f>
+        <v>0.11675460297305</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="36" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="36" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="36" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="36" t="s">
+        <v>171</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="8" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="8" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="8" width="95"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="26" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="27" t="s">
+        <v>173</v>
+      </c>
+      <c r="B3" s="27" t="s">
+        <v>174</v>
+      </c>
+      <c r="C3" s="27" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="28" t="s">
+        <v>176</v>
+      </c>
+      <c r="B4" s="39" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="C4" s="40" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="B5" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="40" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="B6" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="40" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="28" t="s">
+        <v>182</v>
+      </c>
+      <c r="B7" s="34" t="n">
+        <f aca="false">B4+B5+B6</f>
+        <v>0.03</v>
+      </c>
+      <c r="C7" s="40" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="28" t="s">
+        <v>184</v>
+      </c>
+      <c r="B8" s="39" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="C8" s="40" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="28" t="s">
+        <v>186</v>
+      </c>
+      <c r="B9" s="39" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="C9" s="40" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="28" t="s">
+        <v>188</v>
+      </c>
+      <c r="B10" s="39" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="C10" s="40" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="28" t="s">
+        <v>190</v>
+      </c>
+      <c r="B11" s="39" t="n">
+        <v>0.115</v>
+      </c>
+      <c r="C11" s="40" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="28" t="s">
+        <v>192</v>
+      </c>
+      <c r="B12" s="41" t="n">
+        <v>2554.7</v>
+      </c>
+      <c r="C12" s="40" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="36" t="s">
+        <v>194</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D21"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="8" width="48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="8" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="8" width="16"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="26" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="27" t="s">
+        <v>196</v>
+      </c>
+      <c r="B3" s="27" t="s">
+        <v>197</v>
+      </c>
+      <c r="C3" s="27" t="s">
+        <v>198</v>
+      </c>
+      <c r="D3" s="27" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="28" t="s">
+        <v>89</v>
+      </c>
+      <c r="B4" s="42" t="n">
+        <f aca="false">Income_Statement!E4</f>
+        <v>91354</v>
+      </c>
+      <c r="C4" s="43" t="n">
+        <f aca="false">B4*(1+Assumptions_FY2025!B7)</f>
+        <v>94094.62</v>
+      </c>
+      <c r="D4" s="34" t="n">
+        <f aca="false">IFERROR(C4/B4-1,"")</f>
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="28" t="s">
+        <v>200</v>
+      </c>
+      <c r="B5" s="42" t="n">
+        <f aca="false">Income_Statement!E10</f>
+        <v>15704</v>
+      </c>
+      <c r="C5" s="43" t="n">
+        <f aca="false">C4*Assumptions_FY2025!B8</f>
+        <v>15525.6123</v>
+      </c>
+      <c r="D5" s="34" t="n">
+        <f aca="false">IFERROR(C5/B5-1,"")</f>
+        <v>-0.0113593797758532</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="28" t="s">
+        <v>111</v>
+      </c>
+      <c r="B6" s="34" t="n">
+        <f aca="false">IFERROR(B5/B4,"")</f>
+        <v>0.171902708146332</v>
+      </c>
+      <c r="C6" s="34" t="n">
+        <f aca="false">IFERROR(C5/C4,"")</f>
+        <v>0.165</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="28" t="s">
+        <v>201</v>
+      </c>
+      <c r="B7" s="42" t="n">
+        <f aca="false">-Income_Statement!E19</f>
+        <v>1485</v>
+      </c>
+      <c r="C7" s="43" t="n">
+        <f aca="false">B7*(1+Assumptions_FY2025!B9)</f>
+        <v>1559.25</v>
+      </c>
+      <c r="D7" s="34" t="n">
+        <f aca="false">IFERROR(C7/B7-1,"")</f>
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="28" t="s">
+        <v>202</v>
+      </c>
+      <c r="B8" s="43" t="n">
+        <f aca="false">B5-B7</f>
+        <v>14219</v>
+      </c>
+      <c r="C8" s="43" t="n">
+        <f aca="false">C5-C7</f>
+        <v>13966.3623</v>
+      </c>
+      <c r="D8" s="34" t="n">
+        <f aca="false">IFERROR(C8/B8-1,"")</f>
+        <v>-0.0177676137562416</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="28" t="s">
+        <v>188</v>
+      </c>
+      <c r="B9" s="44" t="n">
+        <f aca="false">-Income_Statement!E22/Income_Statement!E20</f>
+        <v>0.250321021225168</v>
+      </c>
+      <c r="C9" s="34" t="n">
+        <f aca="false">Assumptions_FY2025!B10</f>
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="28" t="s">
+        <v>203</v>
+      </c>
+      <c r="B10" s="43" t="n">
+        <f aca="false">B8*B9</f>
+        <v>3559.31460080067</v>
+      </c>
+      <c r="C10" s="43" t="n">
+        <f aca="false">C8*C9</f>
+        <v>3351.926952</v>
+      </c>
+      <c r="D10" s="34" t="n">
+        <f aca="false">IFERROR(C10/B10-1,"")</f>
+        <v>-0.0582661753906253</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="28" t="s">
+        <v>204</v>
+      </c>
+      <c r="B11" s="42" t="n">
+        <f aca="false">Income_Statement!E25</f>
+        <v>10884</v>
+      </c>
+      <c r="C11" s="43" t="n">
+        <f aca="false">C8-C10</f>
+        <v>10614.435348</v>
+      </c>
+      <c r="D11" s="34" t="n">
+        <f aca="false">IFERROR(C11/B11-1,"")</f>
+        <v>-0.0247670573318632</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="28" t="s">
+        <v>114</v>
+      </c>
+      <c r="B12" s="34" t="n">
+        <f aca="false">IFERROR(B11/B4,"")</f>
+        <v>0.119140924316396</v>
+      </c>
+      <c r="C12" s="34" t="n">
+        <f aca="false">IFERROR(C11/C4,"")</f>
+        <v>0.11280597496435</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="28" t="s">
+        <v>205</v>
+      </c>
+      <c r="B13" s="45" t="n">
+        <f aca="false">Income_Statement!E33</f>
+        <v>4.19</v>
+      </c>
+      <c r="C13" s="46" t="n">
+        <f aca="false">IFERROR(C11/Assumptions_FY2025!B12,"")</f>
+        <v>4.15486567816182</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="28" t="s">
+        <v>206</v>
+      </c>
+      <c r="B15" s="42" t="n">
+        <f aca="false">Cash_Flow_Statement!E50</f>
+        <v>10666</v>
+      </c>
+      <c r="C15" s="43" t="n">
+        <f aca="false">C4*Assumptions_FY2025!B11</f>
+        <v>10820.8813</v>
+      </c>
+      <c r="D15" s="34" t="n">
+        <f aca="false">IFERROR(C15/B15-1,"")</f>
+        <v>0.0145210294393399</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="28" t="s">
+        <v>207</v>
+      </c>
+      <c r="B16" s="34" t="n">
+        <f aca="false">IFERROR(B15/B4,"")</f>
+        <v>0.11675460297305</v>
+      </c>
+      <c r="C16" s="34" t="n">
+        <f aca="false">IFERROR(C15/C4,"")</f>
+        <v>0.115</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="36" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="36" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="36" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="36" t="s">
+        <v>211</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/excel_model/Nestle_Data_Foundation.xlsx
+++ b/excel_model/Nestle_Data_Foundation.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="281">
   <si>
     <t xml:space="preserve">Nestlé FP&amp;A Case Study — Data Foundation</t>
   </si>
@@ -56,10 +56,10 @@
     <t xml:space="preserve">• Cash_Flow_Statement — Full consolidated Statement of Cash Flows, line by line across Operating, Investing and Financing activities plus the cash reconciliation and a Free Cash Flow memo, FY2021–FY2024, with every subtotal (Cash Generated from Operations, Operating/Investing/Financing Cash Flow) computed by formula.</t>
   </si>
   <si>
-    <t xml:space="preserve">• Assumptions_FY2025 — FY2025 budget assumptions (organic growth, FX, UTOP margin, tax rate, FCF margin, share count), each cited to Nestlé's own FY2025 guidance where available, or flagged as an explicit own-assumption where not. Yellow cells are the editable scenario levers.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Budget_FY2025_PL_CF — FY2025 Budget vs FY2024 Actual (Sales → UTOP → PBT → Net Profit, plus Free Cash Flow), fully driven by the Assumptions_FY2025 sheet. Built from guidance disclosed BEFORE FY2025 actual results were known — sets up Step 4 (Variance Analysis) of this project.</t>
+    <t xml:space="preserve">• Assumptions_FY2025 — ~40 line-item FY2025 budget drivers covering the full Income Statement and Cash Flow Statement (organic growth, FX, cost ratios, other trading/operating items, financial income/expense, associates income, tax rate, NCI, D&amp;A, impairment, working capital, capex, investing and financing lines), each cited to Nestlé's own FY2025 guidance where available, or flagged as an explicit own-assumption with rationale where not. Yellow cells are the editable levers.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Budget_FY2025_PL_CF — Full-detail FY2025 Budget vs FY2024 Actual, built at the same line-item level as Income_Statement and Cash_Flow_Statement (not a simplified bridge), fully driven by Assumptions_FY2025. Built from guidance disclosed BEFORE FY2025 actual results were known — sets up Step 3 (Variance Analysis) of this project.</t>
   </si>
   <si>
     <t xml:space="preserve">Data sources</t>
@@ -545,7 +545,7 @@
     <t xml:space="preserve">"Divestments in associates and joint ventures" (CHF 9,294m in FY2021 only) reflects the one-off partial disposal of Nestlé's L'Oréal stake — see the matching note on the Income_Statement sheet.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nestlé — FY2025 Budget Assumptions</t>
+    <t xml:space="preserve">Nestlé — FY2025 Budget Assumptions (full line-item detail, P&amp;L + Cash Flow)</t>
   </si>
   <si>
     <t xml:space="preserve">Driver</t>
@@ -557,22 +557,25 @@
     <t xml:space="preserve">Source / Rationale</t>
   </si>
   <si>
+    <t xml:space="preserve">A. INCOME STATEMENT DRIVERS</t>
+  </si>
+  <si>
     <t xml:space="preserve">Organic Sales Growth</t>
   </si>
   <si>
-    <t xml:space="preserve">Nestlé FY2025 guidance (Full-Year Results 2024 press release, 13-Feb-2025): "organic sales growth is expected to improve compared to 2024, strengthening through the year" (FY2024 organic growth was 2.2%). 3.0% is used here as an illustrative point assumption within that guided range — Nestlé did not disclose a precise FY2025 organic growth number.</t>
+    <t xml:space="preserve">Nestlé FY2025 guidance (Full-Year Results 2024 press release, 13-Feb-2025): "organic sales growth is expected to improve compared to 2024, strengthening through the year" (FY2024 organic growth was 2.2%). 3.0% is an illustrative point assumption within that guided range — Nestlé did not disclose a precise FY2025 organic growth number.</t>
   </si>
   <si>
     <t xml:space="preserve">Net M&amp;A Impact</t>
   </si>
   <si>
-    <t xml:space="preserve">No acquisition/divestment guidance was disclosed for FY2025 in the FY2024 results press release; assumed neutral (0.0%), consistent with FY2024's own -0.3% being a minor, non-recurring item.</t>
+    <t xml:space="preserve">No acquisition/divestment guidance was disclosed for FY2025; assumed neutral (0.0%), consistent with FY2024's own -0.3% being a minor, non-recurring item.</t>
   </si>
   <si>
     <t xml:space="preserve">Foreign Exchange (FX) Impact</t>
   </si>
   <si>
-    <t xml:space="preserve">FY2025 guidance states it "assumes no significant change in key macroeconomic variables" — interpreted here as a flat (0.0%) FX assumption. In practice Nestlé's FX impact has been materially negative in FY2022-FY2024 (Swiss Franc strength), so this is a simplifying assumption, not a forecast of currency markets.</t>
+    <t xml:space="preserve">FY2025 guidance "assumes no significant change in key macroeconomic variables" — interpreted as a flat (0.0%) FX assumption. This is a simplifying assumption, not a forecast of currency markets.</t>
   </si>
   <si>
     <t xml:space="preserve">→ Implied Reported Sales Growth</t>
@@ -581,40 +584,229 @@
     <t xml:space="preserve">Formula: Organic Sales Growth + Net M&amp;A Impact + FX Impact (not a separate input).</t>
   </si>
   <si>
-    <t xml:space="preserve">Underlying Trading Operating Profit (UTOP) Margin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nestlé FY2025 guidance: UTOP margin "expected to be at or above 16.0% as we invest for growth", down from FY2024's reported 17.2%, reflecting a planned step-up in advertising &amp; marketing spend (guided to reach ~9% of sales by end-2025, from 8.1% in FY2024) and the ramp-up of the Fuel for Growth cost-savings programme. 16.5% is used as a midpoint scenario within the guided "16.0%+" range.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Net Financial Expenses Growth (vs FY2024)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Own assumption (not company guidance): Nestlé's net debt rose to CHF 56.0bn at FY2024 year-end (from CHF 49.6bn a year earlier) and the company stated it does not anticipate a new share buyback programme in 2025 — implying continued elevated net financial expenses. +5.0% growth vs FY2024's CHF 1.5bn is assumed as a reasonable continuation of the FY2023→FY2024 trend (+7.1%).</t>
+    <t xml:space="preserve">Other Revenue (% of Sales)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Own assumption: held flat at the FY2024 ratio (366 / 91,354 = 0.40%) — an immaterial, stable line with no company guidance.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cost of Goods Sold (% of Sales)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Own assumption: modest improvement from FY2024's 53.3% ratio, reflecting continued procurement/input-cost savings under the "Fuel for Growth" cost-savings programme referenced in FY2025 guidance. No specific COGS-ratio guidance was disclosed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Distribution Expenses (% of Sales)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Own assumption: slight improvement from FY2024's 8.28% ratio, reflecting logistics/supply-chain efficiencies under Fuel for Growth. No specific guidance was disclosed for this line.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marketing &amp; Administration Expenses (% of Sales)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Own assumption, the key driver of the guided margin step-down: FY2025 guidance states advertising &amp; marketing spend is planned to increase toward ~9% of sales by end-2025 (from 8.1% in FY2024); this line also includes G&amp;A, which is not separately guided, so the ratio is calibrated (from FY2024's 19.83%) so that the resulting UTOP margin lands at "or above 16.0%", per guidance — see the memo row below.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Research &amp; Development Costs (% of Sales)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Own assumption: held broadly flat versus FY2024's 1.82% ratio — Nestlé has not signalled a change in R&amp;D investment intensity.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">→ Resulting UTOP Margin (memo, not an input)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Formula: 1 + Other Revenue% − COGS% − Distribution% − Marketing&amp;Admin% − R&amp;D%. Shown for reference against FY2025 guidance of "UTOP margin expected to be at or above 16.0%" (down from FY2024's 17.2%).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other Trading Items, net (% of Sales)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Own assumption: FY2023–FY2024 two-year average net ratio (-1.65% / -1.17%, avg ≈ -1.41%), reflecting continued but no-longer-escalating restructuring/one-off items as the prior large cost-reduction programme (2021–2022) winds down. Nestlé does not guide this line.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other Operating Items, net (% of Sales)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Own assumption: FY2023–FY2024 two-year average net ratio (-0.49% / +0.10%, avg ≈ -0.20%). This line is inherently one-off in nature (disposals, portfolio actions) and is not guided by the company.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Financial Income Growth (vs FY2024)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Own assumption: held flat — no treasury-yield or cash-balance guidance was disclosed for FY2025.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Net Financial Expense Growth (vs FY2024)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Own assumption (not company guidance): Nestlé's net debt rose to CHF 56.0bn at FY2024 year-end (from CHF 49.6bn a year earlier) and the company does not anticipate a new share buyback programme in 2025 — implying continued elevated net financial expenses. +5.0% growth vs FY2024's CHF 1,485m is assumed as a reasonable continuation of the FY2023→FY2024 trend (+9.2%), applied more conservatively. Financial expense is then derived as the balancing line versus the flat Financial Income assumption above.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Income from Associates &amp; JVs Growth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Own assumption: continuation of the FY2022–FY2024 recovery trend (CHF 1,040m → 1,120m → 1,249m, i.e. +7.7% then +11.5% YoY), moderated to +8.0% for FY2025. Excludes the FY2021 CHF 8,651m figure, which included the one-off L'Oréal-related gain and is not representative of a run rate.</t>
   </si>
   <si>
     <t xml:space="preserve">Effective Tax Rate</t>
   </si>
   <si>
-    <t xml:space="preserve">Own assumption: close to FY2024's reported tax rate of 25.0%, with modest normalization assumed as the one-off deferred-tax write-off that inflated the FY2024 rate is not expected to repeat. No FY2025 tax-rate guidance was disclosed by Nestlé.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free Cash Flow (FCF) Margin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Own assumption: broadly in line with FY2024's 11.7% FCF margin, reflecting continued capital discipline under the Fuel for Growth programme, offset by the margin step-down (more cash absorbed by growth investment). No explicit FY2025 FCF guidance was disclosed by Nestlé.</t>
+    <t xml:space="preserve">Own assumption: close to, but slightly below, FY2024's reported 25.0% rate, with modest normalization assumed as the one-off deferred-tax write-off that inflated the FY2024 rate is not expected to repeat. No FY2025 tax-rate guidance was disclosed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Non-Controlling Interests (% of Profit for the Year)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Own assumption: held flat at the FY2024 ratio (290 / 11,174 = 2.60%) — this line has been stable (2.5%–3.4%) across FY2021–FY2024.</t>
   </si>
   <si>
     <t xml:space="preserve">Shares Outstanding for EPS (million)</t>
   </si>
   <si>
-    <t xml:space="preserve">FY2024 weighted-average basic shares implied by reported EPS (Net Profit CHF 10,884m ÷ EPS CHF 4.19 = ~2,598m), reduced by the 43.5 million shares the Board proposed for cancellation in 2025 (per the FY2024 results press release). No new buyback programme is planned for 2025 per guidance, so the share count is held flat aside from that already-announced cancellation.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IMPORTANT: cells highlighted in yellow are the editable scenario assumptions. Change any of them and every figure in the Budget_FY2025_PL_CF sheet recalculates automatically.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nestlé Group — FY2025 Budget vs FY2024 Actual (Simplified P&amp;L + Free Cash Flow, CHF m unless % or per-share)</t>
+    <t xml:space="preserve">FY2024 weighted-average basic shares implied by reported EPS (Net Profit CHF 10,884m ÷ EPS CHF 4.19 ≈ 2,598m), reduced by the 43.5 million shares the Board proposed for cancellation in 2025. No new buyback programme is planned for 2025 per guidance, so the share count is held flat aside from that already-announced cancellation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B. CASH FLOW DRIVERS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Depreciation &amp; Amortization (% of Sales)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Own assumption: held flat at the FY2024 ratio (3,582 / 91,354 = 3.92%) — D&amp;A has been stable at 3.7%–3.9% of sales across FY2021–FY2024, tracking the asset base rather than any single-year driver.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Impairment (CHF m)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Own assumption: held flat at the FY2024 level, treated as a normalized run-rate figure. FY2021–FY2022 carried much larger impairments (CHF 2,614m / 2,726m) tied to a specific prior restructuring programme that has since wound down (FY2023: CHF 647m, FY2024: CHF 580m); no new large impairment is assumed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Net Disposal Result &amp; Other Non-Cash Items (CHF m)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Own assumption: neutral placeholder. Both lines have swung between small positive and negative values FY2021–FY2024 with no discernible trend and no company guidance — modelling anything other than zero would be spurious precision.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Working Capital &amp; Other Operating Movements (CHF m)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Own assumption: neutral placeholder. Combined working-capital and other-operating-asset/liability movements have ranged from -CHF 3,647m (FY2022) to +CHF 874m (FY2024) with no stable trend; Nestlé gives no forward guidance on working capital, so a zero net assumption is used rather than an unsupported extrapolation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interest Paid (% of Budgeted Financial Expense)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Own assumption: FY2024's historical cash-vs-accrual ratio (interest paid CHF 1,539m ÷ financial expense CHF 1,843m = 83.5%) applied to the FY2025 Budget's financial expense line.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interest Received (% of Budgeted Financial Income)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Own assumption: FY2024's historical ratio (interest &amp; dividends received CHF 273m ÷ financial income CHF 358m = 76.3%) applied to the FY2025 Budget's financial income line.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taxes Paid (% of Budgeted Tax Expense)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Own assumption: FY2024's historical cash-vs-accrual ratio (taxes paid CHF 2,411m ÷ tax expense CHF 3,314m = 72.7%) applied to the FY2025 Budget's tax expense line, reflecting normal timing differences between accrued and cash tax.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Associate Dividends Received (% of Budgeted Associate Income)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Own assumption: FY2024's historical ratio (dividends &amp; interest from associates/JVs CHF 759m ÷ income from associates &amp; JVs CHF 1,249m = 60.8%) applied to the FY2025 Budget's associate income line.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Capital Expenditure (% of Sales)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Own assumption: continuation of the rising FY2021–FY2024 capex-intensity trend (5.6% → 5.4% → 6.1% → 6.2% of sales), held at the FY2024 level — Nestlé has not disclosed specific FY2025 capex guidance.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intangible Asset Capex (% of Sales)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Own assumption: four-year average ratio (0.53% / 0.28% / 0.53% / 0.36%, avg ≈ 0.42%), rounded to 0.40% of sales.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acquisitions/Disposals of Businesses, net (CHF m)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Own assumption: no acquisitions or disposals are budgeted, consistent with no M&amp;A guidance being disclosed for FY2025 (mirrors the Net M&amp;A Impact = 0.0% sales assumption above).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Associate Investments, net (% of Sales)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Own assumption: continuation of the recent FY2023–FY2024 level (-CHF 582m / -CHF 532m, both ≈ -0.6% of sales), reflecting ongoing (but not accelerating) investment in associates/JVs such as coffee and pet care ventures.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Divestments in Associates/JVs (CHF m)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Own assumption: zero, consistent with FY2022–FY2024 (all nil). FY2021's CHF 9,294m reflected the one-off partial disposal of Nestlé's L'Oréal stake and is not expected to recur.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Treasury Investments &amp; Other Investing (CHF m)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Own assumption: neutral placeholder. Both lines are treasury-management driven, have swung between large inflows and outflows FY2021–FY2024 (e.g. treasury investments from -CHF 3,610m to +CHF 5,902m), and are not forecastable from sales or guidance.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dividend Paid to Shareholders Growth (vs FY2024)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Own assumption: Nestlé has a long-standing progressive dividend policy (per-share dividend increased for over two decades); +2.0% is assumed as a modest continuation. No specific FY2025 dividend figure was available at the time of this budget (the dividend for a given year is proposed to shareholders the following February, i.e. after this budget is built).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dividends to Non-Controlling Interests (CHF m)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Own assumption: held flat at the FY2024 level. This line has ranged CHF -174m to -323m across FY2021–FY2024 with no clear trend and no guidance.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acquisition of Non-Controlling Interests (CHF m)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Own assumption: zero. This line reflects opportunistic buy-outs of minority stakes (CHF -601m to -27m across FY2021–FY2024, declining) and is not a plannable, recurring item.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Purchase of Treasury Shares (CHF m)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Directly per FY2025 guidance: Nestlé stated it does not anticipate a new share buyback programme in 2025 (consistent with the Shares Outstanding assumption above, which holds the share count flat aside from the already-announced cancellation).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bond/Long-Term Debt Inflows (CHF m)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Own assumption: held flat at the FY2024 level, reflecting a steady-state refinancing/issuance programme — Nestlé has not disclosed a specific FY2025 debt-issuance plan.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bond/Lease/Long-Term Debt Outflows (CHF m)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Own assumption: held flat at the FY2024 level, for the same reason as the inflows line above. Net long-term debt financing therefore continues at roughly the FY2024 pace, consistent with the rising net-debt / rising net-financial-expense narrative used elsewhere in this budget.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Short-Term Debt Movement (CHF m)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Own assumption: neutral placeholder. This is the most volatile line in the financing section (CHF -885m to +2,396m across FY2021–FY2024) and is a short-term treasury management decision, not a forecastable business driver.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Currency Retranslation (CHF m)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Own assumption: zero, consistent with the flat (0.0%) FX Impact assumption used for Sales above — no currency-market forecast is being made.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IMPORTANT: cells highlighted in yellow are the editable assumptions. Change any of them and every figure in the Budget_FY2025_PL_CF sheet recalculates automatically. Rows marked "→" are memo/formula rows, not separate inputs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nestlé Group — FY2025 Budget vs FY2024 Actual, full P&amp;L + Cash Flow detail (CHF m unless % or per-share)</t>
   </si>
   <si>
     <t xml:space="preserve">Metric</t>
@@ -629,40 +821,55 @@
     <t xml:space="preserve">Budget YoY Growth</t>
   </si>
   <si>
+    <t xml:space="preserve">INCOME STATEMENT</t>
+  </si>
+  <si>
     <t xml:space="preserve">Underlying Trading Operating Profit (UTOP)</t>
   </si>
   <si>
-    <t xml:space="preserve">Net Financial Expenses</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Profit Before Tax (UTOP − Net Financial Expenses)*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Implied Tax Expense (PBT × Tax Rate)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Net Profit</t>
+    <t xml:space="preserve">Other trading items, net</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other operating items, net</t>
   </si>
   <si>
     <t xml:space="preserve">Basic EPS (CHF)</t>
   </si>
   <si>
-    <t xml:space="preserve">Free Cash Flow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FCF Margin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">* Profit Before Tax here follows a simplified bridge (UTOP − Net Financial Expenses only), excluding restructuring/other trading items — the Budget will not tie to a full consolidated income statement, by design (see Income_Statement and Cash_Flow_Statement notes).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Column B ("FY2024 Actual") links directly to the Income_Statement and Cash_Flow_Statement sheets — it is not retyped.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Column C ("FY2025 Budget") is entirely driven by the yellow assumption cells in Assumptions_FY2025 — change any assumption there and this whole sheet recalculates.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">This is a Budget built from Nestlé's own FY2025 guidance as disclosed on 13-Feb-2025, BEFORE FY2025 actual results were known — it deliberately does not use hindsight. Step 4 of this project (Variance Analysis) will compare this Budget against Nestlé's actual FY2025 results once published.</t>
+    <t xml:space="preserve">CASH FLOW STATEMENT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operating Profit (linked from Income Statement above)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Net disposal result &amp; other non-cash items</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Working capital &amp; other operating movements</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acquisition/disposal of businesses, net</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Treasury investments &amp; other investing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free Cash Flow Margin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Column B ("FY2024 Actual") links directly to the Income_Statement and Cash_Flow_Statement sheets — it is not retyped. Column C ("FY2025 Budget") is entirely driven by the assumption cells in Assumptions_FY2025 — change any assumption there and this whole sheet recalculates.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This budget is built at the same line-item level of detail as Income_Statement and Cash_Flow_Statement (full statutory P&amp;L and Cash Flow, not a simplified bridge). Lines with no forecastable business driver and no company guidance (e.g. treasury investments, short-term debt movements, non-cash disposal items) are explicitly assumed flat/neutral rather than given spurious precision — see each driver's rationale in Assumptions_FY2025.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"Other trading items, net" and "Other operating items, net" are budgeted on a combined net basis (income − expense), unlike the split presentation in Income_Statement, since FY2025 guidance does not provide separate visibility into these one-off/restructuring components.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Budgeted ending cash rises materially (CHF 5,558m -&gt; CHF 9,240m, +66%) versus FY2024 mainly because two large one-off FY2024 cash outflows are assumed not to repeat: the CHF 4,678m share buyback (per guidance, no new buyback programme is planned for 2025) and CHF 832m/1,297m of M&amp;A and treasury-investment outflows (no acquisitions are budgeted for FY2025). This is a mechanical consequence of the guidance-based assumptions above, not a hidden cash-generation improvement in the underlying business — Operating Cash Flow is actually budgeted slightly lower than FY2024 (CHF 15,666m vs CHF 16,675m).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This is a Budget built from Nestlé's own FY2025 guidance as disclosed on 13-Feb-2025, BEFORE FY2025 actual results were known — it deliberately does not use hindsight. Step 3 of this project (Variance Analysis) will compare this Budget against Nestlé's actual FY2025 results once published.</t>
   </si>
 </sst>
 </file>
@@ -676,7 +883,7 @@
     <numFmt numFmtId="167" formatCode="0.00;\(0.00\);\-"/>
     <numFmt numFmtId="168" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="32">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -871,6 +1078,13 @@
       <charset val="1"/>
     </font>
     <font>
+      <b val="true"/>
+      <sz val="12"/>
+      <name val="Cambria"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <sz val="9"/>
       <color rgb="FF444444"/>
       <name val="Cambria"/>
@@ -884,8 +1098,25 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF008000"/>
+      <name val="Cambria"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <i val="true"/>
+      <sz val="10"/>
+      <color rgb="FF1F4B44"/>
+      <name val="Cambria"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -901,12 +1132,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9E2E0"/>
-        <bgColor rgb="FFEDEDE8"/>
+        <bgColor rgb="FFD9D6C9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFEDEDE8"/>
+        <bgColor rgb="FFD9E2E0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9D6C9"/>
         <bgColor rgb="FFD9E2E0"/>
       </patternFill>
     </fill>
@@ -966,7 +1203,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="56">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1123,35 +1360,71 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="22" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="19" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="22" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="22" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="22" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="22" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="30" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="24" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1189,7 +1462,7 @@
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFD9E2E0"/>
+      <rgbColor rgb="FFD9D6C9"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -1200,7 +1473,7 @@
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFD9E2E0"/>
       <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
@@ -1459,12 +1732,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
         <v>10</v>
       </c>
@@ -5269,16 +5542,16 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C48"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="8" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="8" width="46"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="8" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="8" width="95"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="8" width="100"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="39" t="s">
         <v>172</v>
       </c>
     </row>
@@ -5293,109 +5566,465 @@
         <v>175</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="28" t="s">
+    <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="40" t="s">
         <v>176</v>
       </c>
-      <c r="B4" s="39" t="n">
+      <c r="B4" s="41"/>
+      <c r="C4" s="41"/>
+    </row>
+    <row r="5" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="B5" s="42" t="n">
         <v>0.03</v>
       </c>
-      <c r="C4" s="40" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="28" t="s">
+      <c r="C5" s="43" t="s">
         <v>178</v>
       </c>
-      <c r="B5" s="39" t="n">
+    </row>
+    <row r="6" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="B6" s="42" t="n">
         <v>0</v>
       </c>
-      <c r="C5" s="40" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="28" t="s">
+      <c r="C6" s="43" t="s">
         <v>180</v>
       </c>
-      <c r="B6" s="39" t="n">
+    </row>
+    <row r="7" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="28" t="s">
+        <v>181</v>
+      </c>
+      <c r="B7" s="42" t="n">
         <v>0</v>
       </c>
-      <c r="C6" s="40" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="28" t="s">
+      <c r="C7" s="43" t="s">
         <v>182</v>
       </c>
-      <c r="B7" s="34" t="n">
-        <f aca="false">B4+B5+B6</f>
+    </row>
+    <row r="8" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="28" t="s">
+        <v>183</v>
+      </c>
+      <c r="B8" s="34" t="n">
+        <f aca="false">Assumptions_FY2025!B5+Assumptions_FY2025!B6+Assumptions_FY2025!B7</f>
         <v>0.03</v>
       </c>
-      <c r="C7" s="40" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="28" t="s">
+      <c r="C8" s="43" t="s">
         <v>184</v>
       </c>
-      <c r="B8" s="39" t="n">
-        <v>0.165</v>
-      </c>
-      <c r="C8" s="40" t="s">
+    </row>
+    <row r="9" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="28" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="28" t="s">
+      <c r="B9" s="42" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="C9" s="43" t="s">
         <v>186</v>
       </c>
-      <c r="B9" s="39" t="n">
+    </row>
+    <row r="10" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="28" t="s">
+        <v>187</v>
+      </c>
+      <c r="B10" s="42" t="n">
+        <v>0.529</v>
+      </c>
+      <c r="C10" s="43" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="28" t="s">
+        <v>189</v>
+      </c>
+      <c r="B11" s="42" t="n">
+        <v>0.082</v>
+      </c>
+      <c r="C11" s="43" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="28" t="s">
+        <v>191</v>
+      </c>
+      <c r="B12" s="42" t="n">
+        <v>0.209</v>
+      </c>
+      <c r="C12" s="43" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="28" t="s">
+        <v>193</v>
+      </c>
+      <c r="B13" s="42" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="C13" s="43" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="28" t="s">
+        <v>195</v>
+      </c>
+      <c r="B14" s="34" t="n">
+        <f aca="false">1+Assumptions_FY2025!B9-Assumptions_FY2025!B10-Assumptions_FY2025!B11-Assumptions_FY2025!B12-Assumptions_FY2025!B13</f>
+        <v>0.166</v>
+      </c>
+      <c r="C14" s="43" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="28" t="s">
+        <v>197</v>
+      </c>
+      <c r="B15" s="42" t="n">
+        <v>-0.014</v>
+      </c>
+      <c r="C15" s="43" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="28" t="s">
+        <v>199</v>
+      </c>
+      <c r="B16" s="42" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="C16" s="43" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="28" t="s">
+        <v>201</v>
+      </c>
+      <c r="B17" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="43" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="28" t="s">
+        <v>203</v>
+      </c>
+      <c r="B18" s="42" t="n">
         <v>0.05</v>
       </c>
-      <c r="C9" s="40" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="28" t="s">
-        <v>188</v>
-      </c>
-      <c r="B10" s="39" t="n">
+      <c r="C18" s="43" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="28" t="s">
+        <v>205</v>
+      </c>
+      <c r="B19" s="42" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="C19" s="43" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="28" t="s">
+        <v>207</v>
+      </c>
+      <c r="B20" s="42" t="n">
         <v>0.24</v>
       </c>
-      <c r="C10" s="40" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="28" t="s">
-        <v>190</v>
-      </c>
-      <c r="B11" s="39" t="n">
-        <v>0.115</v>
-      </c>
-      <c r="C11" s="40" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="28" t="s">
-        <v>192</v>
-      </c>
-      <c r="B12" s="41" t="n">
+      <c r="C20" s="43" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="28" t="s">
+        <v>209</v>
+      </c>
+      <c r="B21" s="42" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="C21" s="43" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="28" t="s">
+        <v>211</v>
+      </c>
+      <c r="B22" s="44" t="n">
         <v>2554.7</v>
       </c>
-      <c r="C12" s="40" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="36" t="s">
-        <v>194</v>
+      <c r="C22" s="43" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="40" t="s">
+        <v>213</v>
+      </c>
+      <c r="B24" s="41"/>
+      <c r="C24" s="41"/>
+    </row>
+    <row r="25" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="28" t="s">
+        <v>214</v>
+      </c>
+      <c r="B25" s="42" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="C25" s="43" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="28" t="s">
+        <v>216</v>
+      </c>
+      <c r="B26" s="45" t="n">
+        <v>580</v>
+      </c>
+      <c r="C26" s="43" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="28" t="s">
+        <v>218</v>
+      </c>
+      <c r="B27" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" s="43" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="28" t="s">
+        <v>220</v>
+      </c>
+      <c r="B28" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="43" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="28" t="s">
+        <v>222</v>
+      </c>
+      <c r="B29" s="42" t="n">
+        <v>0.835</v>
+      </c>
+      <c r="C29" s="43" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="28" t="s">
+        <v>224</v>
+      </c>
+      <c r="B30" s="42" t="n">
+        <v>0.763</v>
+      </c>
+      <c r="C30" s="43" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="28" t="s">
+        <v>226</v>
+      </c>
+      <c r="B31" s="42" t="n">
+        <v>0.727</v>
+      </c>
+      <c r="C31" s="43" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="28" t="s">
+        <v>228</v>
+      </c>
+      <c r="B32" s="42" t="n">
+        <v>0.608</v>
+      </c>
+      <c r="C32" s="43" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="28" t="s">
+        <v>230</v>
+      </c>
+      <c r="B33" s="42" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="C33" s="43" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="28" t="s">
+        <v>232</v>
+      </c>
+      <c r="B34" s="42" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="C34" s="43" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="28" t="s">
+        <v>234</v>
+      </c>
+      <c r="B35" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="43" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="28" t="s">
+        <v>236</v>
+      </c>
+      <c r="B36" s="42" t="n">
+        <v>-0.006</v>
+      </c>
+      <c r="C36" s="43" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="28" t="s">
+        <v>238</v>
+      </c>
+      <c r="B37" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="43" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="28" t="s">
+        <v>240</v>
+      </c>
+      <c r="B38" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" s="43" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="28" t="s">
+        <v>242</v>
+      </c>
+      <c r="B39" s="42" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="C39" s="43" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="28" t="s">
+        <v>244</v>
+      </c>
+      <c r="B40" s="45" t="n">
+        <v>-174</v>
+      </c>
+      <c r="C40" s="43" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="28" t="s">
+        <v>246</v>
+      </c>
+      <c r="B41" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="43" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="28" t="s">
+        <v>248</v>
+      </c>
+      <c r="B42" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="43" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="28" t="s">
+        <v>250</v>
+      </c>
+      <c r="B43" s="45" t="n">
+        <v>7992</v>
+      </c>
+      <c r="C43" s="43" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="28" t="s">
+        <v>252</v>
+      </c>
+      <c r="B44" s="45" t="n">
+        <v>-5055</v>
+      </c>
+      <c r="C44" s="43" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="28" t="s">
+        <v>254</v>
+      </c>
+      <c r="B45" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="43" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="28" t="s">
+        <v>256</v>
+      </c>
+      <c r="B46" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="43" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="36" t="s">
+        <v>258</v>
       </c>
     </row>
   </sheetData>
@@ -5414,235 +6043,1072 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D82"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="8" width="48"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="8" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="8" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="8" width="58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="8" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="8" width="16"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="26" t="s">
-        <v>195</v>
+      <c r="A1" s="39" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="27" t="s">
-        <v>196</v>
+        <v>260</v>
       </c>
       <c r="B3" s="27" t="s">
-        <v>197</v>
+        <v>261</v>
       </c>
       <c r="C3" s="27" t="s">
-        <v>198</v>
+        <v>262</v>
       </c>
       <c r="D3" s="27" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="28" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="27" t="s">
+        <v>264</v>
+      </c>
+      <c r="B4" s="46"/>
+      <c r="C4" s="46"/>
+      <c r="D4" s="46"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="28" t="s">
         <v>89</v>
       </c>
-      <c r="B4" s="42" t="n">
+      <c r="B5" s="47" t="n">
         <f aca="false">Income_Statement!E4</f>
         <v>91354</v>
       </c>
-      <c r="C4" s="43" t="n">
-        <f aca="false">B4*(1+Assumptions_FY2025!B7)</f>
+      <c r="C5" s="47" t="n">
+        <f aca="false">B5*(1+Assumptions_FY2025!B8)</f>
         <v>94094.62</v>
       </c>
-      <c r="D4" s="34" t="n">
-        <f aca="false">IFERROR(C4/B4-1,"")</f>
+      <c r="D5" s="34" t="n">
+        <f aca="false">IFERROR(C5/B5-1,"")</f>
         <v>0.03</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="28" t="s">
-        <v>200</v>
-      </c>
-      <c r="B5" s="42" t="n">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="28" t="s">
+        <v>90</v>
+      </c>
+      <c r="B6" s="47" t="n">
+        <f aca="false">Income_Statement!E5</f>
+        <v>366</v>
+      </c>
+      <c r="C6" s="47" t="n">
+        <f aca="false">C5*Assumptions_FY2025!B9</f>
+        <v>376.37848</v>
+      </c>
+      <c r="D6" s="34" t="n">
+        <f aca="false">IFERROR(C6/B6-1,"")</f>
+        <v>0.0283565027322403</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="28" t="s">
+        <v>91</v>
+      </c>
+      <c r="B7" s="47" t="n">
+        <f aca="false">Income_Statement!E6</f>
+        <v>-48670</v>
+      </c>
+      <c r="C7" s="47" t="n">
+        <f aca="false">-C5*Assumptions_FY2025!B10</f>
+        <v>-49776.05398</v>
+      </c>
+      <c r="D7" s="34" t="n">
+        <f aca="false">IFERROR(C7/B7-1,"")</f>
+        <v>0.0227255800287651</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="28" t="s">
+        <v>92</v>
+      </c>
+      <c r="B8" s="47" t="n">
+        <f aca="false">Income_Statement!E7</f>
+        <v>-7567</v>
+      </c>
+      <c r="C8" s="47" t="n">
+        <f aca="false">-C5*Assumptions_FY2025!B11</f>
+        <v>-7715.75884</v>
+      </c>
+      <c r="D8" s="34" t="n">
+        <f aca="false">IFERROR(C8/B8-1,"")</f>
+        <v>0.0196588925597991</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="28" t="s">
+        <v>93</v>
+      </c>
+      <c r="B9" s="47" t="n">
+        <f aca="false">Income_Statement!E8</f>
+        <v>-18112</v>
+      </c>
+      <c r="C9" s="47" t="n">
+        <f aca="false">-C5*Assumptions_FY2025!B12</f>
+        <v>-19665.77558</v>
+      </c>
+      <c r="D9" s="34" t="n">
+        <f aca="false">IFERROR(C9/B9-1,"")</f>
+        <v>0.0857870792844522</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="28" t="s">
+        <v>94</v>
+      </c>
+      <c r="B10" s="47" t="n">
+        <f aca="false">Income_Statement!E9</f>
+        <v>-1667</v>
+      </c>
+      <c r="C10" s="47" t="n">
+        <f aca="false">-C5*Assumptions_FY2025!B13</f>
+        <v>-1693.70316</v>
+      </c>
+      <c r="D10" s="34" t="n">
+        <f aca="false">IFERROR(C10/B10-1,"")</f>
+        <v>0.0160186922615475</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="48" t="s">
+        <v>265</v>
+      </c>
+      <c r="B11" s="49" t="n">
         <f aca="false">Income_Statement!E10</f>
         <v>15704</v>
       </c>
-      <c r="C5" s="43" t="n">
-        <f aca="false">C4*Assumptions_FY2025!B8</f>
-        <v>15525.6123</v>
-      </c>
-      <c r="D5" s="34" t="n">
-        <f aca="false">IFERROR(C5/B5-1,"")</f>
-        <v>-0.0113593797758532</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="28" t="s">
-        <v>111</v>
-      </c>
-      <c r="B6" s="34" t="n">
-        <f aca="false">IFERROR(B5/B4,"")</f>
-        <v>0.171902708146332</v>
-      </c>
-      <c r="C6" s="34" t="n">
-        <f aca="false">IFERROR(C5/C4,"")</f>
-        <v>0.165</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="28" t="s">
-        <v>201</v>
-      </c>
-      <c r="B7" s="42" t="n">
-        <f aca="false">-Income_Statement!E19</f>
-        <v>1485</v>
-      </c>
-      <c r="C7" s="43" t="n">
-        <f aca="false">B7*(1+Assumptions_FY2025!B9)</f>
-        <v>1559.25</v>
-      </c>
-      <c r="D7" s="34" t="n">
-        <f aca="false">IFERROR(C7/B7-1,"")</f>
+      <c r="C11" s="31" t="n">
+        <f aca="false">SUM(C5:C10)</f>
+        <v>15619.70692</v>
+      </c>
+      <c r="D11" s="50" t="n">
+        <f aca="false">IFERROR(C11/B11-1,"")</f>
+        <v>-0.00536761844116129</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="28" t="s">
+        <v>266</v>
+      </c>
+      <c r="B12" s="47" t="n">
+        <f aca="false">Income_Statement!E11+Income_Statement!E12</f>
+        <v>-1071</v>
+      </c>
+      <c r="C12" s="47" t="n">
+        <f aca="false">C5*Assumptions_FY2025!B15</f>
+        <v>-1317.32468</v>
+      </c>
+      <c r="D12" s="34" t="n">
+        <f aca="false">IFERROR(C12/B12-1,"")</f>
+        <v>0.229995032679738</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="48" t="s">
+        <v>98</v>
+      </c>
+      <c r="B13" s="49" t="n">
+        <f aca="false">Income_Statement!E13</f>
+        <v>14633</v>
+      </c>
+      <c r="C13" s="31" t="n">
+        <f aca="false">C11+C12</f>
+        <v>14302.38224</v>
+      </c>
+      <c r="D13" s="50" t="n">
+        <f aca="false">IFERROR(C13/B13-1,"")</f>
+        <v>-0.0225939834620377</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="28" t="s">
+        <v>267</v>
+      </c>
+      <c r="B14" s="47" t="n">
+        <f aca="false">Income_Statement!E14+Income_Statement!E15</f>
+        <v>91</v>
+      </c>
+      <c r="C14" s="47" t="n">
+        <f aca="false">C5*Assumptions_FY2025!B16</f>
+        <v>-188.18924</v>
+      </c>
+      <c r="D14" s="34" t="n">
+        <f aca="false">IFERROR(C14/B14-1,"")</f>
+        <v>-3.06801362637363</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="48" t="s">
+        <v>101</v>
+      </c>
+      <c r="B15" s="49" t="n">
+        <f aca="false">Income_Statement!E16</f>
+        <v>14724</v>
+      </c>
+      <c r="C15" s="31" t="n">
+        <f aca="false">C13+C14</f>
+        <v>14114.193</v>
+      </c>
+      <c r="D15" s="50" t="n">
+        <f aca="false">IFERROR(C15/B15-1,"")</f>
+        <v>-0.0414158516707415</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="28" t="s">
+        <v>102</v>
+      </c>
+      <c r="B16" s="47" t="n">
+        <f aca="false">Income_Statement!E17</f>
+        <v>358</v>
+      </c>
+      <c r="C16" s="47" t="n">
+        <f aca="false">B16*(1+Assumptions_FY2025!B17)</f>
+        <v>358</v>
+      </c>
+      <c r="D16" s="34" t="n">
+        <f aca="false">IFERROR(C16/B16-1,"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="28" t="s">
+        <v>103</v>
+      </c>
+      <c r="B17" s="47" t="n">
+        <f aca="false">Income_Statement!E18</f>
+        <v>-1843</v>
+      </c>
+      <c r="C17" s="47" t="n">
+        <f aca="false">(Income_Statement!E19*(1+Assumptions_FY2025!B18))-C16</f>
+        <v>-1917.25</v>
+      </c>
+      <c r="D17" s="34" t="n">
+        <f aca="false">IFERROR(C17/B17-1,"")</f>
+        <v>0.0402875746066196</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="48" t="s">
+        <v>104</v>
+      </c>
+      <c r="B18" s="49" t="n">
+        <f aca="false">Income_Statement!E19</f>
+        <v>-1485</v>
+      </c>
+      <c r="C18" s="31" t="n">
+        <f aca="false">C16+C17</f>
+        <v>-1559.25</v>
+      </c>
+      <c r="D18" s="50" t="n">
+        <f aca="false">IFERROR(C18/B18-1,"")</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="28" t="s">
-        <v>202</v>
-      </c>
-      <c r="B8" s="43" t="n">
-        <f aca="false">B5-B7</f>
-        <v>14219</v>
-      </c>
-      <c r="C8" s="43" t="n">
-        <f aca="false">C5-C7</f>
-        <v>13966.3623</v>
-      </c>
-      <c r="D8" s="34" t="n">
-        <f aca="false">IFERROR(C8/B8-1,"")</f>
-        <v>-0.0177676137562416</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="28" t="s">
-        <v>188</v>
-      </c>
-      <c r="B9" s="44" t="n">
-        <f aca="false">-Income_Statement!E22/Income_Statement!E20</f>
-        <v>0.250321021225168</v>
-      </c>
-      <c r="C9" s="34" t="n">
-        <f aca="false">Assumptions_FY2025!B10</f>
-        <v>0.24</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="28" t="s">
-        <v>203</v>
-      </c>
-      <c r="B10" s="43" t="n">
-        <f aca="false">B8*B9</f>
-        <v>3559.31460080067</v>
-      </c>
-      <c r="C10" s="43" t="n">
-        <f aca="false">C8*C9</f>
-        <v>3351.926952</v>
-      </c>
-      <c r="D10" s="34" t="n">
-        <f aca="false">IFERROR(C10/B10-1,"")</f>
-        <v>-0.0582661753906253</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="28" t="s">
-        <v>204</v>
-      </c>
-      <c r="B11" s="42" t="n">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="48" t="s">
+        <v>105</v>
+      </c>
+      <c r="B19" s="49" t="n">
+        <f aca="false">Income_Statement!E20</f>
+        <v>13239</v>
+      </c>
+      <c r="C19" s="31" t="n">
+        <f aca="false">C15+C18</f>
+        <v>12554.943</v>
+      </c>
+      <c r="D19" s="50" t="n">
+        <f aca="false">IFERROR(C19/B19-1,"")</f>
+        <v>-0.0516698391117152</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="28" t="s">
+        <v>106</v>
+      </c>
+      <c r="B20" s="47" t="n">
+        <f aca="false">Income_Statement!E21</f>
+        <v>1249</v>
+      </c>
+      <c r="C20" s="47" t="n">
+        <f aca="false">B20*(1+Assumptions_FY2025!B19)</f>
+        <v>1348.92</v>
+      </c>
+      <c r="D20" s="34" t="n">
+        <f aca="false">IFERROR(C20/B20-1,"")</f>
+        <v>0.0800000000000001</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="28" t="s">
+        <v>107</v>
+      </c>
+      <c r="B21" s="47" t="n">
+        <f aca="false">Income_Statement!E22</f>
+        <v>-3314</v>
+      </c>
+      <c r="C21" s="47" t="n">
+        <f aca="false">-C19*Assumptions_FY2025!B20</f>
+        <v>-3013.18632</v>
+      </c>
+      <c r="D21" s="34" t="n">
+        <f aca="false">IFERROR(C21/B21-1,"")</f>
+        <v>-0.0907705733252865</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="48" t="s">
+        <v>108</v>
+      </c>
+      <c r="B22" s="49" t="n">
+        <f aca="false">Income_Statement!E23</f>
+        <v>11174</v>
+      </c>
+      <c r="C22" s="31" t="n">
+        <f aca="false">C19+C20+C21</f>
+        <v>10890.67668</v>
+      </c>
+      <c r="D22" s="50" t="n">
+        <f aca="false">IFERROR(C22/B22-1,"")</f>
+        <v>-0.0253555861822085</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="28" t="s">
+        <v>109</v>
+      </c>
+      <c r="B23" s="47" t="n">
+        <f aca="false">Income_Statement!E24</f>
+        <v>290</v>
+      </c>
+      <c r="C23" s="47" t="n">
+        <f aca="false">C22*Assumptions_FY2025!B21</f>
+        <v>283.15759368</v>
+      </c>
+      <c r="D23" s="34" t="n">
+        <f aca="false">IFERROR(C23/B23-1,"")</f>
+        <v>-0.023594504551724</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="48" t="s">
+        <v>110</v>
+      </c>
+      <c r="B24" s="49" t="n">
         <f aca="false">Income_Statement!E25</f>
         <v>10884</v>
       </c>
-      <c r="C11" s="43" t="n">
-        <f aca="false">C8-C10</f>
-        <v>10614.435348</v>
-      </c>
-      <c r="D11" s="34" t="n">
-        <f aca="false">IFERROR(C11/B11-1,"")</f>
-        <v>-0.0247670573318632</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="28" t="s">
+      <c r="C24" s="31" t="n">
+        <f aca="false">C22-C23</f>
+        <v>10607.51908632</v>
+      </c>
+      <c r="D24" s="50" t="n">
+        <f aca="false">IFERROR(C24/B24-1,"")</f>
+        <v>-0.0254025095259094</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="28" t="s">
+        <v>111</v>
+      </c>
+      <c r="B26" s="51" t="n">
+        <f aca="false">IFERROR(B11/B5,"")</f>
+        <v>0.171902708146332</v>
+      </c>
+      <c r="C26" s="34" t="n">
+        <f aca="false">IFERROR(C11/C5,"")</f>
+        <v>0.166</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="28" t="s">
+        <v>112</v>
+      </c>
+      <c r="B27" s="51" t="n">
+        <f aca="false">IFERROR(B13/B5,"")</f>
+        <v>0.160179083565033</v>
+      </c>
+      <c r="C27" s="34" t="n">
+        <f aca="false">IFERROR(C13/C5,"")</f>
+        <v>0.152</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="28" t="s">
+        <v>113</v>
+      </c>
+      <c r="B28" s="51" t="n">
+        <f aca="false">IFERROR(B15/B5,"")</f>
+        <v>0.161175208529457</v>
+      </c>
+      <c r="C28" s="34" t="n">
+        <f aca="false">IFERROR(C15/C5,"")</f>
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="28" t="s">
         <v>114</v>
       </c>
-      <c r="B12" s="34" t="n">
-        <f aca="false">IFERROR(B11/B4,"")</f>
+      <c r="B29" s="51" t="n">
+        <f aca="false">IFERROR(B24/B5,"")</f>
         <v>0.119140924316396</v>
       </c>
-      <c r="C12" s="34" t="n">
-        <f aca="false">IFERROR(C11/C4,"")</f>
-        <v>0.11280597496435</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="28" t="s">
-        <v>205</v>
-      </c>
-      <c r="B13" s="45" t="n">
+      <c r="C29" s="34" t="n">
+        <f aca="false">IFERROR(C24/C5,"")</f>
+        <v>0.112732471700507</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="28" t="s">
+        <v>207</v>
+      </c>
+      <c r="B30" s="51" t="n">
+        <f aca="false">IFERROR(-B21/B19,"")</f>
+        <v>0.250321021225168</v>
+      </c>
+      <c r="C30" s="34" t="n">
+        <f aca="false">IFERROR(-C21/C19,"")</f>
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="28" t="s">
+        <v>268</v>
+      </c>
+      <c r="B32" s="52" t="n">
         <f aca="false">Income_Statement!E33</f>
         <v>4.19</v>
       </c>
-      <c r="C13" s="46" t="n">
-        <f aca="false">IFERROR(C11/Assumptions_FY2025!B12,"")</f>
-        <v>4.15486567816182</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="28" t="s">
-        <v>206</v>
-      </c>
-      <c r="B15" s="42" t="n">
-        <f aca="false">Cash_Flow_Statement!E50</f>
-        <v>10666</v>
-      </c>
-      <c r="C15" s="43" t="n">
-        <f aca="false">C4*Assumptions_FY2025!B11</f>
-        <v>10820.8813</v>
-      </c>
-      <c r="D15" s="34" t="n">
-        <f aca="false">IFERROR(C15/B15-1,"")</f>
-        <v>0.0145210294393399</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="28" t="s">
-        <v>207</v>
-      </c>
-      <c r="B16" s="34" t="n">
-        <f aca="false">IFERROR(B15/B4,"")</f>
-        <v>0.11675460297305</v>
-      </c>
-      <c r="C16" s="34" t="n">
-        <f aca="false">IFERROR(C15/C4,"")</f>
-        <v>0.115</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="36" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="36" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="36" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="36" t="s">
-        <v>211</v>
+      <c r="C32" s="53" t="n">
+        <f aca="false">IFERROR(C24/Assumptions_FY2025!B22,"")</f>
+        <v>4.15215840854895</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="27" t="s">
+        <v>269</v>
+      </c>
+      <c r="B34" s="46"/>
+      <c r="C34" s="46"/>
+      <c r="D34" s="46"/>
+    </row>
+    <row r="35" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="54" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="28" t="s">
+        <v>270</v>
+      </c>
+      <c r="B36" s="47" t="n">
+        <f aca="false">Cash_Flow_Statement!E5</f>
+        <v>14724</v>
+      </c>
+      <c r="C36" s="55" t="n">
+        <f aca="false">C15</f>
+        <v>14114.193</v>
+      </c>
+      <c r="D36" s="34" t="n">
+        <f aca="false">IFERROR(C36/B36-1,"")</f>
+        <v>-0.0414158516707415</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="B37" s="47" t="n">
+        <f aca="false">Cash_Flow_Statement!E6</f>
+        <v>3582</v>
+      </c>
+      <c r="C37" s="47" t="n">
+        <f aca="false">C5*Assumptions_FY2025!B25</f>
+        <v>3669.69018</v>
+      </c>
+      <c r="D37" s="34" t="n">
+        <f aca="false">IFERROR(C37/B37-1,"")</f>
+        <v>0.0244807872696817</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="28" t="s">
+        <v>126</v>
+      </c>
+      <c r="B38" s="47" t="n">
+        <f aca="false">Cash_Flow_Statement!E7</f>
+        <v>580</v>
+      </c>
+      <c r="C38" s="47" t="n">
+        <f aca="false">Assumptions_FY2025!B26</f>
+        <v>580</v>
+      </c>
+      <c r="D38" s="34" t="n">
+        <f aca="false">IFERROR(C38/B38-1,"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="28" t="s">
+        <v>271</v>
+      </c>
+      <c r="B39" s="47" t="n">
+        <f aca="false">Cash_Flow_Statement!E8+Cash_Flow_Statement!E9</f>
+        <v>-167</v>
+      </c>
+      <c r="C39" s="47" t="n">
+        <f aca="false">Assumptions_FY2025!B27</f>
+        <v>0</v>
+      </c>
+      <c r="D39" s="34" t="n">
+        <f aca="false">IFERROR(C39/B39-1,"")</f>
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="48" t="s">
+        <v>129</v>
+      </c>
+      <c r="B40" s="49" t="n">
+        <f aca="false">Cash_Flow_Statement!E10</f>
+        <v>18719</v>
+      </c>
+      <c r="C40" s="31" t="n">
+        <f aca="false">SUM(C36:C39)</f>
+        <v>18363.88318</v>
+      </c>
+      <c r="D40" s="50" t="n">
+        <f aca="false">IFERROR(C40/B40-1,"")</f>
+        <v>-0.0189709290026174</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="28" t="s">
+        <v>272</v>
+      </c>
+      <c r="B41" s="47" t="n">
+        <f aca="false">Cash_Flow_Statement!E11+Cash_Flow_Statement!E12</f>
+        <v>874</v>
+      </c>
+      <c r="C41" s="47" t="n">
+        <f aca="false">Assumptions_FY2025!B28</f>
+        <v>0</v>
+      </c>
+      <c r="D41" s="34" t="n">
+        <f aca="false">IFERROR(C41/B41-1,"")</f>
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="48" t="s">
+        <v>132</v>
+      </c>
+      <c r="B42" s="49" t="n">
+        <f aca="false">Cash_Flow_Statement!E13</f>
+        <v>19593</v>
+      </c>
+      <c r="C42" s="31" t="n">
+        <f aca="false">C40+C41</f>
+        <v>18363.88318</v>
+      </c>
+      <c r="D42" s="50" t="n">
+        <f aca="false">IFERROR(C42/B42-1,"")</f>
+        <v>-0.0627324462818352</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="28" t="s">
+        <v>133</v>
+      </c>
+      <c r="B43" s="47" t="n">
+        <f aca="false">Cash_Flow_Statement!E14</f>
+        <v>-1539</v>
+      </c>
+      <c r="C43" s="47" t="n">
+        <f aca="false">C17*Assumptions_FY2025!B29</f>
+        <v>-1600.90375</v>
+      </c>
+      <c r="D43" s="34" t="n">
+        <f aca="false">IFERROR(C43/B43-1,"")</f>
+        <v>0.0402233593242365</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="28" t="s">
+        <v>134</v>
+      </c>
+      <c r="B44" s="47" t="n">
+        <f aca="false">Cash_Flow_Statement!E15</f>
+        <v>273</v>
+      </c>
+      <c r="C44" s="47" t="n">
+        <f aca="false">C16*Assumptions_FY2025!B30</f>
+        <v>273.154</v>
+      </c>
+      <c r="D44" s="34" t="n">
+        <f aca="false">IFERROR(C44/B44-1,"")</f>
+        <v>0.000564102564102553</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="28" t="s">
+        <v>135</v>
+      </c>
+      <c r="B45" s="47" t="n">
+        <f aca="false">Cash_Flow_Statement!E16</f>
+        <v>-2411</v>
+      </c>
+      <c r="C45" s="47" t="n">
+        <f aca="false">C21*Assumptions_FY2025!B31</f>
+        <v>-2190.58645464</v>
+      </c>
+      <c r="D45" s="34" t="n">
+        <f aca="false">IFERROR(C45/B45-1,"")</f>
+        <v>-0.0914199690418912</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="28" t="s">
+        <v>136</v>
+      </c>
+      <c r="B46" s="47" t="n">
+        <f aca="false">Cash_Flow_Statement!E17</f>
+        <v>759</v>
+      </c>
+      <c r="C46" s="47" t="n">
+        <f aca="false">C20*Assumptions_FY2025!B32</f>
+        <v>820.14336</v>
+      </c>
+      <c r="D46" s="34" t="n">
+        <f aca="false">IFERROR(C46/B46-1,"")</f>
+        <v>0.0805577865612648</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="48" t="s">
+        <v>137</v>
+      </c>
+      <c r="B47" s="49" t="n">
+        <f aca="false">Cash_Flow_Statement!E18</f>
+        <v>16675</v>
+      </c>
+      <c r="C47" s="31" t="n">
+        <f aca="false">C42+C43+C44+C45+C46</f>
+        <v>15665.69033536</v>
+      </c>
+      <c r="D47" s="50" t="n">
+        <f aca="false">IFERROR(C47/B47-1,"")</f>
+        <v>-0.0605283157205396</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="54" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="28" t="s">
+        <v>139</v>
+      </c>
+      <c r="B50" s="47" t="n">
+        <f aca="false">Cash_Flow_Statement!E21</f>
+        <v>-5638</v>
+      </c>
+      <c r="C50" s="47" t="n">
+        <f aca="false">-C5*Assumptions_FY2025!B33</f>
+        <v>-5833.86644</v>
+      </c>
+      <c r="D50" s="34" t="n">
+        <f aca="false">IFERROR(C50/B50-1,"")</f>
+        <v>0.0347404114934373</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="28" t="s">
+        <v>140</v>
+      </c>
+      <c r="B51" s="47" t="n">
+        <f aca="false">Cash_Flow_Statement!E22</f>
+        <v>-325</v>
+      </c>
+      <c r="C51" s="47" t="n">
+        <f aca="false">-C5*Assumptions_FY2025!B34</f>
+        <v>-376.37848</v>
+      </c>
+      <c r="D51" s="34" t="n">
+        <f aca="false">IFERROR(C51/B51-1,"")</f>
+        <v>0.158087630769231</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="28" t="s">
+        <v>273</v>
+      </c>
+      <c r="B52" s="47" t="n">
+        <f aca="false">Cash_Flow_Statement!E23+Cash_Flow_Statement!E24</f>
+        <v>-832</v>
+      </c>
+      <c r="C52" s="47" t="n">
+        <f aca="false">Assumptions_FY2025!B35</f>
+        <v>0</v>
+      </c>
+      <c r="D52" s="34" t="n">
+        <f aca="false">IFERROR(C52/B52-1,"")</f>
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="28" t="s">
+        <v>143</v>
+      </c>
+      <c r="B53" s="47" t="n">
+        <f aca="false">Cash_Flow_Statement!E25</f>
+        <v>-532</v>
+      </c>
+      <c r="C53" s="47" t="n">
+        <f aca="false">C5*Assumptions_FY2025!B36</f>
+        <v>-564.56772</v>
+      </c>
+      <c r="D53" s="34" t="n">
+        <f aca="false">IFERROR(C53/B53-1,"")</f>
+        <v>0.0612175187969926</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="28" t="s">
+        <v>144</v>
+      </c>
+      <c r="B54" s="47" t="n">
+        <f aca="false">Cash_Flow_Statement!E26</f>
+        <v>0</v>
+      </c>
+      <c r="C54" s="47" t="n">
+        <f aca="false">Assumptions_FY2025!B37</f>
+        <v>0</v>
+      </c>
+      <c r="D54" s="34" t="str">
+        <f aca="false">IFERROR(C54/B54-1,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="28" t="s">
+        <v>274</v>
+      </c>
+      <c r="B55" s="47" t="n">
+        <f aca="false">Cash_Flow_Statement!E27+Cash_Flow_Statement!E28</f>
+        <v>-1297</v>
+      </c>
+      <c r="C55" s="47" t="n">
+        <f aca="false">Assumptions_FY2025!B38</f>
+        <v>0</v>
+      </c>
+      <c r="D55" s="34" t="n">
+        <f aca="false">IFERROR(C55/B55-1,"")</f>
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="48" t="s">
+        <v>147</v>
+      </c>
+      <c r="B56" s="49" t="n">
+        <f aca="false">Cash_Flow_Statement!E29</f>
+        <v>-8624</v>
+      </c>
+      <c r="C56" s="31" t="n">
+        <f aca="false">SUM(C50:C55)</f>
+        <v>-6774.81264</v>
+      </c>
+      <c r="D56" s="50" t="n">
+        <f aca="false">IFERROR(C56/B56-1,"")</f>
+        <v>-0.214423395176252</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="54" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="28" t="s">
+        <v>149</v>
+      </c>
+      <c r="B59" s="47" t="n">
+        <f aca="false">Cash_Flow_Statement!E32</f>
+        <v>-7816</v>
+      </c>
+      <c r="C59" s="47" t="n">
+        <f aca="false">B59*(1+Assumptions_FY2025!B39)</f>
+        <v>-7972.32</v>
+      </c>
+      <c r="D59" s="34" t="n">
+        <f aca="false">IFERROR(C59/B59-1,"")</f>
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="28" t="s">
+        <v>150</v>
+      </c>
+      <c r="B60" s="47" t="n">
+        <f aca="false">Cash_Flow_Statement!E33</f>
+        <v>-174</v>
+      </c>
+      <c r="C60" s="47" t="n">
+        <f aca="false">Assumptions_FY2025!B40</f>
+        <v>-174</v>
+      </c>
+      <c r="D60" s="34" t="n">
+        <f aca="false">IFERROR(C60/B60-1,"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="28" t="s">
+        <v>151</v>
+      </c>
+      <c r="B61" s="47" t="n">
+        <f aca="false">Cash_Flow_Statement!E34</f>
+        <v>-27</v>
+      </c>
+      <c r="C61" s="47" t="n">
+        <f aca="false">Assumptions_FY2025!B41</f>
+        <v>0</v>
+      </c>
+      <c r="D61" s="34" t="n">
+        <f aca="false">IFERROR(C61/B61-1,"")</f>
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="28" t="s">
+        <v>152</v>
+      </c>
+      <c r="B62" s="47" t="n">
+        <f aca="false">Cash_Flow_Statement!E35</f>
+        <v>-4678</v>
+      </c>
+      <c r="C62" s="47" t="n">
+        <f aca="false">Assumptions_FY2025!B42</f>
+        <v>0</v>
+      </c>
+      <c r="D62" s="34" t="n">
+        <f aca="false">IFERROR(C62/B62-1,"")</f>
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="28" t="s">
+        <v>153</v>
+      </c>
+      <c r="B63" s="47" t="n">
+        <f aca="false">Cash_Flow_Statement!E36</f>
+        <v>7992</v>
+      </c>
+      <c r="C63" s="47" t="n">
+        <f aca="false">Assumptions_FY2025!B43</f>
+        <v>7992</v>
+      </c>
+      <c r="D63" s="34" t="n">
+        <f aca="false">IFERROR(C63/B63-1,"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="28" t="s">
+        <v>154</v>
+      </c>
+      <c r="B64" s="47" t="n">
+        <f aca="false">Cash_Flow_Statement!E37</f>
+        <v>-5055</v>
+      </c>
+      <c r="C64" s="47" t="n">
+        <f aca="false">Assumptions_FY2025!B44</f>
+        <v>-5055</v>
+      </c>
+      <c r="D64" s="34" t="n">
+        <f aca="false">IFERROR(C64/B64-1,"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="28" t="s">
+        <v>155</v>
+      </c>
+      <c r="B65" s="47" t="n">
+        <f aca="false">Cash_Flow_Statement!E38</f>
+        <v>2396</v>
+      </c>
+      <c r="C65" s="47" t="n">
+        <f aca="false">Assumptions_FY2025!B45</f>
+        <v>0</v>
+      </c>
+      <c r="D65" s="34" t="n">
+        <f aca="false">IFERROR(C65/B65-1,"")</f>
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="48" t="s">
+        <v>156</v>
+      </c>
+      <c r="B66" s="49" t="n">
+        <f aca="false">Cash_Flow_Statement!E39</f>
+        <v>-7362</v>
+      </c>
+      <c r="C66" s="31" t="n">
+        <f aca="false">SUM(C59:C65)</f>
+        <v>-5209.32</v>
+      </c>
+      <c r="D66" s="50" t="n">
+        <f aca="false">IFERROR(C66/B66-1,"")</f>
+        <v>-0.29240423797881</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="54" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A69" s="28" t="s">
+        <v>158</v>
+      </c>
+      <c r="B69" s="47" t="n">
+        <f aca="false">Cash_Flow_Statement!E42</f>
+        <v>53</v>
+      </c>
+      <c r="C69" s="47" t="n">
+        <f aca="false">Assumptions_FY2025!B46</f>
+        <v>0</v>
+      </c>
+      <c r="D69" s="34" t="n">
+        <f aca="false">IFERROR(C69/B69-1,"")</f>
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A70" s="48" t="s">
+        <v>159</v>
+      </c>
+      <c r="B70" s="49" t="n">
+        <f aca="false">Cash_Flow_Statement!E43</f>
+        <v>742</v>
+      </c>
+      <c r="C70" s="31" t="n">
+        <f aca="false">C47+C56+C66+C69</f>
+        <v>3681.55769536</v>
+      </c>
+      <c r="D70" s="50" t="n">
+        <f aca="false">IFERROR(C70/B70-1,"")</f>
+        <v>3.96166805304582</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A71" s="28" t="s">
+        <v>160</v>
+      </c>
+      <c r="B71" s="47" t="n">
+        <f aca="false">Cash_Flow_Statement!E44</f>
+        <v>4816</v>
+      </c>
+      <c r="C71" s="47" t="n">
+        <f aca="false">Cash_Flow_Statement!E45</f>
+        <v>5558</v>
+      </c>
+      <c r="D71" s="34" t="n">
+        <f aca="false">IFERROR(C71/B71-1,"")</f>
+        <v>0.154069767441861</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A72" s="48" t="s">
+        <v>161</v>
+      </c>
+      <c r="B72" s="49" t="n">
+        <f aca="false">Cash_Flow_Statement!E45</f>
+        <v>5558</v>
+      </c>
+      <c r="C72" s="31" t="n">
+        <f aca="false">C70+C71</f>
+        <v>9239.55769536</v>
+      </c>
+      <c r="D72" s="50" t="n">
+        <f aca="false">IFERROR(C72/B72-1,"")</f>
+        <v>0.662388934033825</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A74" s="54" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A75" s="48" t="s">
+        <v>166</v>
+      </c>
+      <c r="B75" s="49" t="n">
+        <f aca="false">Cash_Flow_Statement!E51</f>
+        <v>10712</v>
+      </c>
+      <c r="C75" s="31" t="n">
+        <f aca="false">C47+C50+C51</f>
+        <v>9455.44541536</v>
+      </c>
+      <c r="D75" s="50" t="n">
+        <f aca="false">IFERROR(C75/B75-1,"")</f>
+        <v>-0.117303452636296</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A76" s="28" t="s">
+        <v>275</v>
+      </c>
+      <c r="B76" s="51" t="n">
+        <f aca="false">IFERROR(B75/B5,"")</f>
+        <v>0.117258138669352</v>
+      </c>
+      <c r="C76" s="34" t="n">
+        <f aca="false">IFERROR(C75/C5,"")</f>
+        <v>0.100488693353138</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A78" s="36" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A79" s="36" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A80" s="36" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A81" s="36" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A82" s="36" t="s">
+        <v>280</v>
       </c>
     </row>
   </sheetData>

--- a/excel_model/Nestle_Data_Foundation.xlsx
+++ b/excel_model/Nestle_Data_Foundation.xlsx
@@ -9,13 +9,13 @@
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Segment_Data" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="Category_Data" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="Income_Statement" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="Cash_Flow_Statement" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="Assumptions_FY2025" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="Budget_FY2025_PL_CF" sheetId="7" state="visible" r:id="rId9"/>
-    <sheet name="Overview_Analysis" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="1. Segment_Data" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="1. Category_Data" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="1. Income_Statement" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="1. Cash_Flow_Statement" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="1. Overview_Analysis" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="2. Assumptions_FY2025" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="2. Budget_FY2025_PL_CF" sheetId="8" state="visible" r:id="rId10"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -41,25 +41,25 @@
     <t xml:space="preserve">Sheets in this workbook</t>
   </si>
   <si>
-    <t xml:space="preserve">• Segment_Data — Sales &amp; Underlying Trading Operating Profit (UTOP) by reporting segment (5 geographic Zones + Nespresso + Nestlé Health Science + Other Businesses), FY2021–FY2024, with the organic growth bridge (RIG / Pricing / Net M&amp;A / FX) for FY2022 and FY2024.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Category_Data — Sales &amp; UTOP by product category (7 categories: Powdered &amp; liquid beverages, Water, Milk products &amp; ice cream, Nutrition &amp; Health Science, Prepared dishes &amp; cooking aids, Confectionery, PetCare), FY2021–FY2024.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Income_Statement — Full consolidated Income Statement, line by line (Sales, Other revenue, COGS, Distribution expenses, Marketing &amp; admin expenses, R&amp;D costs, Other trading/operating income &amp; expenses, Financial income/expense, Income from associates &amp; JVs, Taxes, NCI), FY2021–FY2024, with every subtotal (UTOP, Trading Operating Profit, Operating Profit, PBT, Profit for the Year, Net Profit) computed by formula from the disclosed line items above it — never hardcoded.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Cash_Flow_Statement — Full consolidated Statement of Cash Flows, line by line across Operating, Investing and Financing activities plus the cash reconciliation and a Free Cash Flow memo, FY2021–FY2024, with every subtotal (Cash Generated from Operations, Operating/Investing/Financing Cash Flow) computed by formula.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Assumptions_FY2025 — ~40 line-item FY2025 budget drivers covering the full Income Statement and Cash Flow Statement (organic growth, FX, cost ratios, other trading/operating items, financial income/expense, associates income, tax rate, NCI, D&amp;A, impairment, working capital, capex, investing and financing lines), each cited to Nestlé's own FY2025 guidance where available, or flagged as an explicit own-assumption with rationale where not. Yellow cells are the editable levers.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Budget_FY2025_PL_CF — Full-detail FY2025 Budget vs FY2024 Actual, built at the same line-item level as Income_Statement and Cash_Flow_Statement, fully driven by Assumptions_FY2025. Built from guidance disclosed BEFORE FY2025 actual results were known — sets up Step 3 (Variance Analysis) of this project.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Overview_Analysis — two additional views built entirely by formula from Segment_Data, Income_Statement and Budget_FY2025_PL_CF: a Group-level Sales Growth Bridge (RIG / Pricing / Net M&amp;A / FX) for FY2022, FY2024 and the FY2025 Budget, and a Cost Structure &amp; Margin trend as % of Sales, FY2021–FY2024 Actual plus FY2025 Budget. Each includes a long-format summary table.</t>
+    <t xml:space="preserve">• 1. Segment_Data — Sales &amp; Underlying Trading Operating Profit (UTOP) by reporting segment (5 geographic Zones + Nespresso + Nestlé Health Science + Other Businesses), FY2021–FY2024, with the organic growth bridge (RIG / Pricing / Net M&amp;A / FX) for FY2022 and FY2024.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• 1. Category_Data — Sales &amp; UTOP by product category (7 categories: Powdered &amp; liquid beverages, Water, Milk products &amp; ice cream, Nutrition &amp; Health Science, Prepared dishes &amp; cooking aids, Confectionery, PetCare), FY2021–FY2024.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• 1. Income_Statement — Full consolidated Income Statement, line by line (Sales, Other revenue, COGS, Distribution expenses, Marketing &amp; admin expenses, R&amp;D costs, Other trading/operating income &amp; expenses, Financial income/expense, Income from associates &amp; JVs, Taxes, NCI), FY2021–FY2024, with every subtotal (UTOP, Trading Operating Profit, Operating Profit, PBT, Profit for the Year, Net Profit) computed by formula from the disclosed line items above it — never hardcoded.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• 1. Cash_Flow_Statement — Full consolidated Statement of Cash Flows, line by line across Operating, Investing and Financing activities plus the cash reconciliation and a Free Cash Flow memo, FY2021–FY2024, with every subtotal (Cash Generated from Operations, Operating/Investing/Financing Cash Flow) computed by formula.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• 2. Assumptions_FY2025 — ~40 line-item FY2025 budget drivers covering the full Income Statement and Cash Flow Statement (organic growth, FX, cost ratios, other trading/operating items, financial income/expense, associates income, tax rate, NCI, D&amp;A, impairment, working capital, capex, investing and financing lines), each cited to Nestlé's own FY2025 guidance where available, or flagged as an explicit own-assumption with rationale where not. Yellow cells are the editable levers.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• 2. Budget_FY2025_PL_CF — Full-detail FY2025 Budget vs FY2024 Actual, built at the same line-item level as 1. Income_Statement and 1. Cash_Flow_Statement, fully driven by 2. Assumptions_FY2025. Built from guidance disclosed BEFORE FY2025 actual results were known — sets up Step 3 (Variance Analysis) of this project.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• 1. Overview_Analysis — two additional views built entirely by formula from 1. Segment_Data, 1. Income_Statement and 2. Budget_FY2025_PL_CF: a Group-level Sales Growth Bridge (RIG / Pricing / Net M&amp;A / FX) for FY2022, FY2024 and the FY2025 Budget, and a Cost Structure &amp; Margin trend as % of Sales, FY2021–FY2024 Actual plus FY2025 Budget. Each includes a long-format summary table.</t>
   </si>
   <si>
     <t xml:space="preserve">Data sources</t>
@@ -89,7 +89,7 @@
     <t xml:space="preserve">• All monetary figures are in CHF million unless stated otherwise. Blue cells = hardcoded inputs sourced from the press releases above. Black cells = formulas (margins, YoY growth, H2 derivation).</t>
   </si>
   <si>
-    <t xml:space="preserve">• Income_Statement / Cash_Flow_Statement sheets: sourced from Nestlé's full Financial Statements documents (not the condensed press releases used for Segment_Data/Category_Data) for full line-item detail. FY2022's 'Cash generated from operations' section reflects the "Decrease/(increase) in working capital" and "Variation of other operating assets and liabilities" lines as disclosed that year. The 'Free Cash Flow (derived)' row will not tie exactly to Nestlé's own reported FCF figure — this is flagged on the Cash_Flow_Statement sheet, not hidden.</t>
+    <t xml:space="preserve">• 1. Income_Statement / 1. Cash_Flow_Statement sheets: sourced from Nestlé's full Financial Statements documents (not the condensed press releases used for 1. Segment_Data/1. Category_Data) for full line-item detail. FY2022's 'Cash generated from operations' section reflects the "Decrease/(increase) in working capital" and "Variation of other operating assets and liabilities" lines as disclosed that year. The 'Free Cash Flow (derived)' row will not tie exactly to Nestlé's own reported FCF figure — this is flagged on the 1. Cash_Flow_Statement sheet, not hidden.</t>
   </si>
   <si>
     <t xml:space="preserve">Nestlé — Segment Sales &amp; Profitability, FY2021–FY2024 (CHF m unless %)</t>
@@ -506,6 +506,102 @@
     <t xml:space="preserve">"Divestments in associates and joint ventures" (CHF 9,294m in FY2021 only) reflects the one-off partial disposal of Nestlé's L'Oréal stake — see the matching note on the Income_Statement sheet.</t>
   </si>
   <si>
+    <t xml:space="preserve">Nestlé Group — Overview Analysis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two additional views of the same underlying data in Segment_Data, Income_Statement and Budget_FY2025_PL_CF: how sales growth breaks down by driver, and how the cost/margin structure is shifting over time — complementing the geography (Segment_Data) and product (Category_Data) views elsewhere in this workbook.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A. GROUP SALES GROWTH BRIDGE (RIG / Pricing / Net M&amp;A / FX)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Component</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FY2025 Budget</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real Internal Growth (RIG) — volume/mix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pricing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Organic Growth (RIG + Pricing)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Net M&amp;A Impact</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Foreign Exchange (FX) Impact</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reported Sales Growth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check vs Segment_Data reported YoY (should match Reported Sales Growth above):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Segment_Data FY Sales YoY (Total Group)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Note: FY2021 and FY2023 are not shown because Nestlé did not disclose a full RIG/Pricing/Net M&amp;A/FX bridge for the Group total in those years' press releases (only FY2022 and FY2024 bridges were published at Group level). The FY2025 Budget column does not split Organic Growth into RIG vs Pricing because FY2025 guidance was not given at that level of granularity — see Assumptions_FY2025. Small rounding differences (a few basis points) between "Reported Sales Growth" here and the Segment_Data check row reflect Nestlé's own bridge components being disclosed rounded to one decimal place, not a formula error.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Summary (long format)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RIG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Net M&amp;A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Organic Growth (RIG+Pricing combined)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B. GROUP COST STRUCTURE &amp; MARGIN TREND (% of Sales)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metric</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cost of Goods Sold (% of Sales)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Distribution Expenses (% of Sales)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marketing &amp; Administration Expenses (% of Sales)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Research &amp; Development Costs (% of Sales)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other Trading Items, net (% of Sales)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other Operating Items, net (% of Sales)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Net Financial Expense (% of Sales)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Effective Tax Rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Note: ratios are computed by formula directly from Income_Statement and Budget_FY2025_PL_CF — nothing here is a separately sourced or hardcoded figure. "Other trading/operating items, net" are shown combined (income + expense) to match the Budget's presentation.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Nestlé — FY2025 Budget Assumptions (full line-item detail, P&amp;L + Cash Flow)</t>
   </si>
   <si>
@@ -527,15 +623,9 @@
     <t xml:space="preserve">Nestlé FY2025 guidance (Full-Year Results 2024 press release, 13-Feb-2025): "organic sales growth is expected to improve compared to 2024, strengthening through the year" (FY2024 organic growth was 2.2%). 3.0% is an illustrative point assumption within that guided range — Nestlé did not disclose a precise FY2025 organic growth number.</t>
   </si>
   <si>
-    <t xml:space="preserve">Net M&amp;A Impact</t>
-  </si>
-  <si>
     <t xml:space="preserve">No acquisition/divestment guidance was disclosed for FY2025; assumed neutral (0.0%), consistent with FY2024's own -0.3% being a minor, non-recurring item.</t>
   </si>
   <si>
-    <t xml:space="preserve">Foreign Exchange (FX) Impact</t>
-  </si>
-  <si>
     <t xml:space="preserve">FY2025 guidance "assumes no significant change in key macroeconomic variables" — interpreted as a flat (0.0%) FX assumption. This is a simplifying assumption, not a forecast of currency markets.</t>
   </si>
   <si>
@@ -551,27 +641,15 @@
     <t xml:space="preserve">Own assumption: held flat at the FY2024 ratio (366 / 91,354 = 0.40%) — an immaterial, stable line with no company guidance.</t>
   </si>
   <si>
-    <t xml:space="preserve">Cost of Goods Sold (% of Sales)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Own assumption: modest improvement from FY2024's 53.3% ratio, reflecting continued procurement/input-cost savings under the "Fuel for Growth" cost-savings programme referenced in FY2025 guidance. No specific COGS-ratio guidance was disclosed.</t>
   </si>
   <si>
-    <t xml:space="preserve">Distribution Expenses (% of Sales)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Own assumption: slight improvement from FY2024's 8.28% ratio, reflecting logistics/supply-chain efficiencies under Fuel for Growth. No specific guidance was disclosed for this line.</t>
   </si>
   <si>
-    <t xml:space="preserve">Marketing &amp; Administration Expenses (% of Sales)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Own assumption, the key driver of the guided margin step-down: FY2025 guidance states advertising &amp; marketing spend is planned to increase toward ~9% of sales by end-2025 (from 8.1% in FY2024); this line also includes G&amp;A, which is not separately guided, so the ratio is calibrated (from FY2024's 19.83%) so that the resulting UTOP margin lands at "or above 16.0%", per guidance — see the memo row below.</t>
   </si>
   <si>
-    <t xml:space="preserve">Research &amp; Development Costs (% of Sales)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Own assumption: held broadly flat versus FY2024's 1.82% ratio — Nestlé has not signalled a change in R&amp;D investment intensity.</t>
   </si>
   <si>
@@ -581,15 +659,9 @@
     <t xml:space="preserve">Formula: 1 + Other Revenue% − COGS% − Distribution% − Marketing&amp;Admin% − R&amp;D%. Shown for reference against FY2025 guidance of "UTOP margin expected to be at or above 16.0%" (down from FY2024's 17.2%).</t>
   </si>
   <si>
-    <t xml:space="preserve">Other Trading Items, net (% of Sales)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Own assumption: FY2023–FY2024 two-year average net ratio (-1.65% / -1.17%, avg ≈ -1.41%), reflecting continued but no-longer-escalating restructuring/one-off items as the prior large cost-reduction programme (2021–2022) winds down. Nestlé does not guide this line.</t>
   </si>
   <si>
-    <t xml:space="preserve">Other Operating Items, net (% of Sales)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Own assumption: FY2023–FY2024 two-year average net ratio (-0.49% / +0.10%, avg ≈ -0.20%). This line is inherently one-off in nature (disposals, portfolio actions) and is not guided by the company.</t>
   </si>
   <si>
@@ -611,9 +683,6 @@
     <t xml:space="preserve">Own assumption: continuation of the FY2022–FY2024 recovery trend (CHF 1,040m → 1,120m → 1,249m, i.e. +7.7% then +11.5% YoY), moderated to +8.0% for FY2025. Excludes the FY2021 CHF 8,651m figure, which included the one-off L'Oréal-related gain and is not representative of a run rate.</t>
   </si>
   <si>
-    <t xml:space="preserve">Effective Tax Rate</t>
-  </si>
-  <si>
     <t xml:space="preserve">Own assumption: close to, but slightly below, FY2024's reported 25.0% rate, with modest normalization assumed as the one-off deferred-tax write-off that inflated the FY2024 rate is not expected to repeat. No FY2025 tax-rate guidance was disclosed.</t>
   </si>
   <si>
@@ -770,15 +839,9 @@
     <t xml:space="preserve">Nestlé Group — FY2025 Budget vs FY2024 Actual, full P&amp;L + Cash Flow detail (CHF m unless % or per-share)</t>
   </si>
   <si>
-    <t xml:space="preserve">Metric</t>
-  </si>
-  <si>
     <t xml:space="preserve">FY2024 Actual</t>
   </si>
   <si>
-    <t xml:space="preserve">FY2025 Budget</t>
-  </si>
-  <si>
     <t xml:space="preserve">Budget YoY Growth</t>
   </si>
   <si>
@@ -831,69 +894,6 @@
   </si>
   <si>
     <t xml:space="preserve">This is a Budget built from Nestlé's own FY2025 guidance as disclosed on 13-Feb-2025, BEFORE FY2025 actual results were known — it deliberately does not use hindsight. Step 3 of this project (Variance Analysis) will compare this Budget against Nestlé's actual FY2025 results once published.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nestlé Group — Overview Analysis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Two additional views of the same underlying data in Segment_Data, Income_Statement and Budget_FY2025_PL_CF: how sales growth breaks down by driver, and how the cost/margin structure is shifting over time — complementing the geography (Segment_Data) and product (Category_Data) views elsewhere in this workbook.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A. GROUP SALES GROWTH BRIDGE (RIG / Pricing / Net M&amp;A / FX)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Component</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Real Internal Growth (RIG) — volume/mix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pricing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Organic Growth (RIG + Pricing)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reported Sales Growth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check vs Segment_Data reported YoY (should match Reported Sales Growth above):</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Segment_Data FY Sales YoY (Total Group)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Note: FY2021 and FY2023 are not shown because Nestlé did not disclose a full RIG/Pricing/Net M&amp;A/FX bridge for the Group total in those years' press releases (only FY2022 and FY2024 bridges were published at Group level). The FY2025 Budget column does not split Organic Growth into RIG vs Pricing because FY2025 guidance was not given at that level of granularity — see Assumptions_FY2025. Small rounding differences (a few basis points) between "Reported Sales Growth" here and the Segment_Data check row reflect Nestlé's own bridge components being disclosed rounded to one decimal place, not a formula error.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Summary (long format)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Year</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RIG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Net M&amp;A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Organic Growth (RIG+Pricing combined)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B. GROUP COST STRUCTURE &amp; MARGIN TREND (% of Sales)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Net Financial Expense (% of Sales)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Note: ratios are computed by formula directly from Income_Statement and Budget_FY2025_PL_CF — nothing here is a separately sourced or hardcoded figure. "Other trading/operating items, net" are shown combined (income + expense) to match the Budget's presentation.</t>
   </si>
 </sst>
 </file>
@@ -1080,15 +1080,15 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color rgb="FF444444"/>
+      <sz val="11"/>
+      <color rgb="FF008000"/>
       <name val="Times New Roman"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF008000"/>
+      <sz val="9"/>
+      <color rgb="FF444444"/>
       <name val="Times New Roman"/>
       <family val="0"/>
       <charset val="1"/>
@@ -1339,6 +1339,30 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="20" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1351,7 +1375,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1367,11 +1391,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1379,15 +1399,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="20" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1400,18 +1412,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1466,12 +1466,12 @@
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
       <rgbColor rgb="FFFFCC99"/>
-      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FF4472C4"/>
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
       <rgbColor rgb="FFFFCC00"/>
       <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FFED7D31"/>
       <rgbColor rgb="FF666666"/>
       <rgbColor rgb="FF969696"/>
       <rgbColor rgb="FF1F4B44"/>
@@ -1806,6 +1806,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
+    <tabColor rgb="FF4472C4"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:Z15"/>
@@ -2847,6 +2848,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
+    <tabColor rgb="FF4472C4"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:V14"/>
@@ -3661,6 +3663,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
+    <tabColor rgb="FF4472C4"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:E39"/>
@@ -4315,6 +4318,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
+    <tabColor rgb="FF4472C4"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:E57"/>
@@ -4371,19 +4375,19 @@
         <v>111</v>
       </c>
       <c r="B5" s="28" t="n">
-        <f aca="false">Income_Statement!B16</f>
+        <f aca="false">'1. Income_Statement'!B16</f>
         <v>11679</v>
       </c>
       <c r="C5" s="28" t="n">
-        <f aca="false">Income_Statement!C16</f>
+        <f aca="false">'1. Income_Statement'!C16</f>
         <v>12326</v>
       </c>
       <c r="D5" s="28" t="n">
-        <f aca="false">Income_Statement!D16</f>
+        <f aca="false">'1. Income_Statement'!D16</f>
         <v>14063</v>
       </c>
       <c r="E5" s="28" t="n">
-        <f aca="false">Income_Statement!E16</f>
+        <f aca="false">'1. Income_Statement'!E16</f>
         <v>14724</v>
       </c>
     </row>
@@ -5138,19 +5142,19 @@
         <v>154</v>
       </c>
       <c r="B52" s="33" t="n">
-        <f aca="false">IFERROR(B50/Income_Statement!B4,"")</f>
+        <f aca="false">IFERROR(B50/'1. Income_Statement'!B4,"")</f>
         <v>0.0998989527833915</v>
       </c>
       <c r="C52" s="33" t="n">
-        <f aca="false">IFERROR(C50/Income_Statement!C4,"")</f>
+        <f aca="false">IFERROR(C50/'1. Income_Statement'!C4,"")</f>
         <v>0.0698974836905871</v>
       </c>
       <c r="D52" s="33" t="n">
-        <f aca="false">IFERROR(D50/Income_Statement!D4,"")</f>
+        <f aca="false">IFERROR(D50/'1. Income_Statement'!D4,"")</f>
         <v>0.11186262070152</v>
       </c>
       <c r="E52" s="33" t="n">
-        <f aca="false">IFERROR(E50/Income_Statement!E4,"")</f>
+        <f aca="false">IFERROR(E50/'1. Income_Statement'!E4,"")</f>
         <v>0.11675460297305</v>
       </c>
     </row>
@@ -5211,511 +5215,1421 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
+    <tabColor rgb="FF4472C4"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C48"/>
+  <dimension ref="A1:F114"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="8" width="46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="8" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="8" width="100"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="8" width="42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="2" style="8" width="14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="34" t="s">
         <v>159</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="23" t="s">
+    </row>
+    <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="31" t="s">
         <v>160</v>
       </c>
-      <c r="B3" s="23" t="s">
+    </row>
+    <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="23" t="s">
         <v>161</v>
       </c>
-      <c r="C3" s="23" t="s">
+      <c r="B4" s="35"/>
+      <c r="C4" s="35"/>
+      <c r="D4" s="35"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="35"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="23" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="35" t="s">
+      <c r="B5" s="23" t="s">
+        <v>73</v>
+      </c>
+      <c r="C5" s="23" t="s">
+        <v>75</v>
+      </c>
+      <c r="D5" s="23" t="s">
         <v>163</v>
       </c>
-      <c r="B4" s="36"/>
-      <c r="C4" s="36"/>
-    </row>
-    <row r="5" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="24" t="s">
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="24" t="s">
         <v>164</v>
       </c>
-      <c r="B5" s="37" t="n">
+      <c r="B6" s="36" t="n">
+        <f aca="false">'1. Segment_Data'!Q12</f>
+        <v>0.001</v>
+      </c>
+      <c r="C6" s="36" t="n">
+        <f aca="false">'1. Segment_Data'!V12</f>
+        <v>0.008</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="24" t="s">
+        <v>165</v>
+      </c>
+      <c r="B7" s="36" t="n">
+        <f aca="false">'1. Segment_Data'!R12</f>
+        <v>0.082</v>
+      </c>
+      <c r="C7" s="36" t="n">
+        <f aca="false">'1. Segment_Data'!W12</f>
+        <v>0.015</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="37" t="s">
+        <v>166</v>
+      </c>
+      <c r="B8" s="38" t="n">
+        <f aca="false">'1. Segment_Data'!S12</f>
+        <v>0.083</v>
+      </c>
+      <c r="C8" s="38" t="n">
+        <f aca="false">'1. Segment_Data'!X12</f>
+        <v>0.022</v>
+      </c>
+      <c r="D8" s="38" t="n">
+        <f aca="false">'2. Assumptions_FY2025'!B5</f>
         <v>0.03</v>
       </c>
-      <c r="C5" s="38" t="s">
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="24" t="s">
+        <v>167</v>
+      </c>
+      <c r="B9" s="36" t="n">
+        <f aca="false">'1. Segment_Data'!T12</f>
+        <v>0.011</v>
+      </c>
+      <c r="C9" s="36" t="n">
+        <f aca="false">'1. Segment_Data'!Y12</f>
+        <v>-0.003</v>
+      </c>
+      <c r="D9" s="36" t="n">
+        <f aca="false">'2. Assumptions_FY2025'!B6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="24" t="s">
+        <v>168</v>
+      </c>
+      <c r="B10" s="36" t="n">
+        <f aca="false">'1. Segment_Data'!U12</f>
+        <v>-0.009</v>
+      </c>
+      <c r="C10" s="36" t="n">
+        <f aca="false">'1. Segment_Data'!Z12</f>
+        <v>-0.037</v>
+      </c>
+      <c r="D10" s="36" t="n">
+        <f aca="false">'2. Assumptions_FY2025'!B7</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="37" t="s">
+        <v>169</v>
+      </c>
+      <c r="B11" s="38" t="n">
+        <f aca="false">B8+B9+B10</f>
+        <v>0.085</v>
+      </c>
+      <c r="C11" s="38" t="n">
+        <f aca="false">C8+C9+C10</f>
+        <v>-0.018</v>
+      </c>
+      <c r="D11" s="38" t="n">
+        <f aca="false">'2. Assumptions_FY2025'!B8</f>
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="39" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="24" t="s">
+        <v>171</v>
+      </c>
+      <c r="B14" s="36" t="n">
+        <f aca="false">'1. Segment_Data'!F12</f>
+        <v>0.0842366342090759</v>
+      </c>
+      <c r="C14" s="36" t="n">
+        <f aca="false">'1. Segment_Data'!H12</f>
+        <v>-0.0176777995225704</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="31" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="40" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="23" t="s">
+        <v>174</v>
+      </c>
+      <c r="B19" s="23" t="s">
+        <v>162</v>
+      </c>
+      <c r="C19" s="23" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="B20" s="24" t="s">
+        <v>176</v>
+      </c>
+      <c r="C20" s="29" t="n">
+        <f aca="false">B6</f>
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="B21" s="24" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="24" t="s">
-        <v>166</v>
-      </c>
-      <c r="B6" s="37" t="n">
+      <c r="C21" s="29" t="n">
+        <f aca="false">B7</f>
+        <v>0.082</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="B22" s="24" t="s">
+        <v>177</v>
+      </c>
+      <c r="C22" s="29" t="n">
+        <f aca="false">B9</f>
+        <v>0.011</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="B23" s="24" t="s">
+        <v>178</v>
+      </c>
+      <c r="C23" s="29" t="n">
+        <f aca="false">B10</f>
+        <v>-0.009</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="B24" s="24" t="s">
+        <v>169</v>
+      </c>
+      <c r="C24" s="29" t="n">
+        <f aca="false">B11</f>
+        <v>0.085</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="B25" s="24" t="s">
+        <v>176</v>
+      </c>
+      <c r="C25" s="29" t="n">
+        <f aca="false">C6</f>
+        <v>0.008</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="B26" s="24" t="s">
+        <v>165</v>
+      </c>
+      <c r="C26" s="29" t="n">
+        <f aca="false">C7</f>
+        <v>0.015</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="B27" s="24" t="s">
+        <v>177</v>
+      </c>
+      <c r="C27" s="29" t="n">
+        <f aca="false">C9</f>
+        <v>-0.003</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="B28" s="24" t="s">
+        <v>178</v>
+      </c>
+      <c r="C28" s="29" t="n">
+        <f aca="false">C10</f>
+        <v>-0.037</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="B29" s="24" t="s">
+        <v>169</v>
+      </c>
+      <c r="C29" s="29" t="n">
+        <f aca="false">C11</f>
+        <v>-0.018</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="24" t="s">
+        <v>163</v>
+      </c>
+      <c r="B30" s="24" t="s">
+        <v>179</v>
+      </c>
+      <c r="C30" s="29" t="n">
+        <f aca="false">D8</f>
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="24" t="s">
+        <v>163</v>
+      </c>
+      <c r="B31" s="24" t="s">
+        <v>177</v>
+      </c>
+      <c r="C31" s="29" t="n">
+        <f aca="false">D9</f>
         <v>0</v>
       </c>
-      <c r="C6" s="38" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="24" t="s">
-        <v>168</v>
-      </c>
-      <c r="B7" s="37" t="n">
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="24" t="s">
+        <v>163</v>
+      </c>
+      <c r="B32" s="24" t="s">
+        <v>178</v>
+      </c>
+      <c r="C32" s="29" t="n">
+        <f aca="false">D10</f>
         <v>0</v>
       </c>
-      <c r="C7" s="38" t="s">
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="24" t="s">
+        <v>163</v>
+      </c>
+      <c r="B33" s="24" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="24" t="s">
-        <v>170</v>
-      </c>
-      <c r="B8" s="29" t="n">
-        <f aca="false">Assumptions_FY2025!B5+Assumptions_FY2025!B6+Assumptions_FY2025!B7</f>
+      <c r="C33" s="29" t="n">
+        <f aca="false">D11</f>
         <v>0.03</v>
       </c>
-      <c r="C8" s="38" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="24" t="s">
-        <v>172</v>
-      </c>
-      <c r="B9" s="37" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="C9" s="38" t="s">
+    </row>
+    <row r="36" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="23" t="s">
+        <v>180</v>
+      </c>
+      <c r="B36" s="35"/>
+      <c r="C36" s="35"/>
+      <c r="D36" s="35"/>
+      <c r="E36" s="35"/>
+      <c r="F36" s="35"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="23" t="s">
+        <v>181</v>
+      </c>
+      <c r="B37" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="C37" s="23" t="s">
+        <v>73</v>
+      </c>
+      <c r="D37" s="23" t="s">
+        <v>74</v>
+      </c>
+      <c r="E37" s="23" t="s">
+        <v>75</v>
+      </c>
+      <c r="F37" s="23" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="24" t="s">
+        <v>182</v>
+      </c>
+      <c r="B38" s="36" t="n">
+        <f aca="false">-'1. Income_Statement'!B6/'1. Income_Statement'!B4</f>
+        <v>0.522092595994856</v>
+      </c>
+      <c r="C38" s="36" t="n">
+        <f aca="false">-'1. Income_Statement'!C6/'1. Income_Statement'!C4</f>
+        <v>0.548006862662035</v>
+      </c>
+      <c r="D38" s="36" t="n">
+        <f aca="false">-'1. Income_Statement'!D6/'1. Income_Statement'!D4</f>
+        <v>0.541172928450074</v>
+      </c>
+      <c r="E38" s="36" t="n">
+        <f aca="false">-'1. Income_Statement'!E6/'1. Income_Statement'!E4</f>
+        <v>0.532762659544191</v>
+      </c>
+      <c r="F38" s="36" t="n">
+        <f aca="false">-'2. Budget_FY2025_PL_CF'!C7/'2. Budget_FY2025_PL_CF'!C5</f>
+        <v>0.529</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="24" t="s">
+        <v>183</v>
+      </c>
+      <c r="B39" s="36" t="n">
+        <f aca="false">-'1. Income_Statement'!B7/'1. Income_Statement'!B4</f>
+        <v>0.0909310123093882</v>
+      </c>
+      <c r="C39" s="36" t="n">
+        <f aca="false">-'1. Income_Statement'!C7/'1. Income_Statement'!C4</f>
+        <v>0.0888121663983733</v>
+      </c>
+      <c r="D39" s="36" t="n">
+        <f aca="false">-'1. Income_Statement'!D7/'1. Income_Statement'!D4</f>
+        <v>0.0834964192778339</v>
+      </c>
+      <c r="E39" s="36" t="n">
+        <f aca="false">-'1. Income_Statement'!E7/'1. Income_Statement'!E4</f>
+        <v>0.0828316220417278</v>
+      </c>
+      <c r="F39" s="36" t="n">
+        <f aca="false">-'2. Budget_FY2025_PL_CF'!C8/'2. Budget_FY2025_PL_CF'!C5</f>
+        <v>0.082</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="24" t="s">
+        <v>184</v>
+      </c>
+      <c r="B40" s="36" t="n">
+        <f aca="false">-'1. Income_Statement'!B8/'1. Income_Statement'!B4</f>
+        <v>0.198580745912181</v>
+      </c>
+      <c r="C40" s="36" t="n">
+        <f aca="false">-'1. Income_Statement'!C8/'1. Income_Statement'!C4</f>
+        <v>0.178450393967635</v>
+      </c>
+      <c r="D40" s="36" t="n">
+        <f aca="false">-'1. Income_Statement'!D8/'1. Income_Statement'!D4</f>
+        <v>0.188702982859846</v>
+      </c>
+      <c r="E40" s="36" t="n">
+        <f aca="false">-'1. Income_Statement'!E8/'1. Income_Statement'!E4</f>
+        <v>0.198261707204939</v>
+      </c>
+      <c r="F40" s="36" t="n">
+        <f aca="false">-'2. Budget_FY2025_PL_CF'!C9/'2. Budget_FY2025_PL_CF'!C5</f>
+        <v>0.209</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="24" t="s">
+        <v>185</v>
+      </c>
+      <c r="B41" s="36" t="n">
+        <f aca="false">-'1. Income_Statement'!B9/'1. Income_Statement'!B4</f>
+        <v>0.0191760058791108</v>
+      </c>
+      <c r="C41" s="36" t="n">
+        <f aca="false">-'1. Income_Statement'!C9/'1. Income_Statement'!C4</f>
+        <v>0.0179615352029145</v>
+      </c>
+      <c r="D41" s="36" t="n">
+        <f aca="false">-'1. Income_Statement'!D9/'1. Income_Statement'!D4</f>
+        <v>0.0178068345555818</v>
+      </c>
+      <c r="E41" s="36" t="n">
+        <f aca="false">-'1. Income_Statement'!E9/'1. Income_Statement'!E4</f>
+        <v>0.018247695776868</v>
+      </c>
+      <c r="F41" s="36" t="n">
+        <f aca="false">-'2. Budget_FY2025_PL_CF'!C10/'2. Budget_FY2025_PL_CF'!C5</f>
+        <v>0.018</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="37" t="s">
+        <v>98</v>
+      </c>
+      <c r="B42" s="38" t="n">
+        <f aca="false">'1. Income_Statement'!B27</f>
+        <v>0.173606007716333</v>
+      </c>
+      <c r="C42" s="38" t="n">
+        <f aca="false">'1. Income_Statement'!C27</f>
+        <v>0.170539269677201</v>
+      </c>
+      <c r="D42" s="38" t="n">
+        <f aca="false">'1. Income_Statement'!D27</f>
+        <v>0.172616615411084</v>
+      </c>
+      <c r="E42" s="38" t="n">
+        <f aca="false">'1. Income_Statement'!E27</f>
+        <v>0.171902708146332</v>
+      </c>
+      <c r="F42" s="38" t="n">
+        <f aca="false">'2. Budget_FY2025_PL_CF'!C26</f>
+        <v>0.166</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="24" t="s">
+        <v>186</v>
+      </c>
+      <c r="B43" s="36" t="n">
+        <f aca="false">('1. Income_Statement'!B11+'1. Income_Statement'!B12)/'1. Income_Statement'!B4</f>
+        <v>-0.033988609222855</v>
+      </c>
+      <c r="C43" s="36" t="n">
+        <f aca="false">('1. Income_Statement'!C11+'1. Income_Statement'!C12)/'1. Income_Statement'!C4</f>
+        <v>-0.030797254935186</v>
+      </c>
+      <c r="D43" s="36" t="n">
+        <f aca="false">('1. Income_Statement'!D11+'1. Income_Statement'!D12)/'1. Income_Statement'!D4</f>
+        <v>-0.0164842254672144</v>
+      </c>
+      <c r="E43" s="36" t="n">
+        <f aca="false">('1. Income_Statement'!E11+'1. Income_Statement'!E12)/'1. Income_Statement'!E4</f>
+        <v>-0.0117236245812991</v>
+      </c>
+      <c r="F43" s="36" t="n">
+        <f aca="false">'2. Budget_FY2025_PL_CF'!C12/'2. Budget_FY2025_PL_CF'!C5</f>
+        <v>-0.014</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="37" t="s">
+        <v>99</v>
+      </c>
+      <c r="B44" s="38" t="n">
+        <f aca="false">'1. Income_Statement'!B28</f>
+        <v>0.139617398493478</v>
+      </c>
+      <c r="C44" s="38" t="n">
+        <f aca="false">'1. Income_Statement'!C28</f>
+        <v>0.139742014742015</v>
+      </c>
+      <c r="D44" s="38" t="n">
+        <f aca="false">'1. Income_Statement'!D28</f>
+        <v>0.15613238994387</v>
+      </c>
+      <c r="E44" s="38" t="n">
+        <f aca="false">'1. Income_Statement'!E28</f>
+        <v>0.160179083565033</v>
+      </c>
+      <c r="F44" s="38" t="n">
+        <f aca="false">'2. Budget_FY2025_PL_CF'!C27</f>
+        <v>0.152</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="24" t="s">
+        <v>187</v>
+      </c>
+      <c r="B45" s="36" t="n">
+        <f aca="false">('1. Income_Statement'!B14+'1. Income_Statement'!B15)/'1. Income_Statement'!B4</f>
+        <v>-0.00551166636046298</v>
+      </c>
+      <c r="C45" s="36" t="n">
+        <f aca="false">('1. Income_Statement'!C14+'1. Income_Statement'!C15)/'1. Income_Statement'!C4</f>
+        <v>-0.00920316868592731</v>
+      </c>
+      <c r="D45" s="36" t="n">
+        <f aca="false">('1. Income_Statement'!D14+'1. Income_Statement'!D15)/'1. Income_Statement'!D4</f>
+        <v>-0.0049140841738532</v>
+      </c>
+      <c r="E45" s="36" t="n">
+        <f aca="false">('1. Income_Statement'!E14+'1. Income_Statement'!E15)/'1. Income_Statement'!E4</f>
+        <v>0.000996124964424108</v>
+      </c>
+      <c r="F45" s="36" t="n">
+        <f aca="false">'2. Budget_FY2025_PL_CF'!C14/'2. Budget_FY2025_PL_CF'!C5</f>
+        <v>-0.002</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="37" t="s">
+        <v>100</v>
+      </c>
+      <c r="B46" s="38" t="n">
+        <f aca="false">'1. Income_Statement'!B29</f>
+        <v>0.134105732133015</v>
+      </c>
+      <c r="C46" s="38" t="n">
+        <f aca="false">'1. Income_Statement'!C29</f>
+        <v>0.130538846056087</v>
+      </c>
+      <c r="D46" s="38" t="n">
+        <f aca="false">'1. Income_Statement'!D29</f>
+        <v>0.151218305770017</v>
+      </c>
+      <c r="E46" s="38" t="n">
+        <f aca="false">'1. Income_Statement'!E29</f>
+        <v>0.161175208529457</v>
+      </c>
+      <c r="F46" s="38" t="n">
+        <f aca="false">'2. Budget_FY2025_PL_CF'!C28</f>
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="24" t="s">
+        <v>188</v>
+      </c>
+      <c r="B47" s="36" t="n">
+        <f aca="false">-'1. Income_Statement'!B19/'1. Income_Statement'!B4</f>
+        <v>0.010024343193092</v>
+      </c>
+      <c r="C47" s="36" t="n">
+        <f aca="false">-'1. Income_Statement'!C19/'1. Income_Statement'!C4</f>
+        <v>0.0110141489451834</v>
+      </c>
+      <c r="D47" s="36" t="n">
+        <f aca="false">-'1. Income_Statement'!D19/'1. Income_Statement'!D4</f>
+        <v>0.0146239704079658</v>
+      </c>
+      <c r="E47" s="36" t="n">
+        <f aca="false">-'1. Income_Statement'!E19/'1. Income_Statement'!E4</f>
+        <v>0.0162554458480198</v>
+      </c>
+      <c r="F47" s="36" t="n">
+        <f aca="false">-'2. Budget_FY2025_PL_CF'!C18/'2. Budget_FY2025_PL_CF'!C5</f>
+        <v>0.0165710855732241</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="24" t="s">
+        <v>189</v>
+      </c>
+      <c r="B48" s="36" t="n">
+        <f aca="false">'1. Income_Statement'!B31</f>
+        <v>0.209235609846382</v>
+      </c>
+      <c r="C48" s="36" t="n">
+        <f aca="false">'1. Income_Statement'!C31</f>
+        <v>0.241892610313663</v>
+      </c>
+      <c r="D48" s="36" t="n">
+        <f aca="false">'1. Income_Statement'!D31</f>
+        <v>0.182161694088011</v>
+      </c>
+      <c r="E48" s="36" t="n">
+        <f aca="false">'1. Income_Statement'!E31</f>
+        <v>0.250321021225168</v>
+      </c>
+      <c r="F48" s="36" t="n">
+        <f aca="false">'2. Budget_FY2025_PL_CF'!C30</f>
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="37" t="s">
+        <v>101</v>
+      </c>
+      <c r="B49" s="38" t="n">
+        <f aca="false">'1. Income_Statement'!B30</f>
+        <v>0.194113999632556</v>
+      </c>
+      <c r="C49" s="38" t="n">
+        <f aca="false">'1. Income_Statement'!C30</f>
+        <v>0.0981741930017792</v>
+      </c>
+      <c r="D49" s="38" t="n">
+        <f aca="false">'1. Income_Statement'!D30</f>
+        <v>0.120529473752124</v>
+      </c>
+      <c r="E49" s="38" t="n">
+        <f aca="false">'1. Income_Statement'!E30</f>
+        <v>0.119140924316396</v>
+      </c>
+      <c r="F49" s="38" t="n">
+        <f aca="false">'2. Budget_FY2025_PL_CF'!C29</f>
+        <v>0.112732471700507</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="31" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="40" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="24" t="s">
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="23" t="s">
         <v>174</v>
       </c>
-      <c r="B10" s="37" t="n">
+      <c r="B54" s="23" t="s">
+        <v>181</v>
+      </c>
+      <c r="C54" s="23" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="24" t="s">
+        <v>72</v>
+      </c>
+      <c r="B55" s="24" t="s">
+        <v>182</v>
+      </c>
+      <c r="C55" s="29" t="n">
+        <f aca="false">B38</f>
+        <v>0.522092595994856</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="B56" s="24" t="s">
+        <v>182</v>
+      </c>
+      <c r="C56" s="29" t="n">
+        <f aca="false">C38</f>
+        <v>0.548006862662035</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="24" t="s">
+        <v>74</v>
+      </c>
+      <c r="B57" s="24" t="s">
+        <v>182</v>
+      </c>
+      <c r="C57" s="29" t="n">
+        <f aca="false">D38</f>
+        <v>0.541172928450074</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="B58" s="24" t="s">
+        <v>182</v>
+      </c>
+      <c r="C58" s="29" t="n">
+        <f aca="false">E38</f>
+        <v>0.532762659544191</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="24" t="s">
+        <v>163</v>
+      </c>
+      <c r="B59" s="24" t="s">
+        <v>182</v>
+      </c>
+      <c r="C59" s="29" t="n">
+        <f aca="false">F38</f>
         <v>0.529</v>
       </c>
-      <c r="C10" s="38" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="24" t="s">
-        <v>176</v>
-      </c>
-      <c r="B11" s="37" t="n">
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="24" t="s">
+        <v>72</v>
+      </c>
+      <c r="B60" s="24" t="s">
+        <v>183</v>
+      </c>
+      <c r="C60" s="29" t="n">
+        <f aca="false">B39</f>
+        <v>0.0909310123093882</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="B61" s="24" t="s">
+        <v>183</v>
+      </c>
+      <c r="C61" s="29" t="n">
+        <f aca="false">C39</f>
+        <v>0.0888121663983733</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="24" t="s">
+        <v>74</v>
+      </c>
+      <c r="B62" s="24" t="s">
+        <v>183</v>
+      </c>
+      <c r="C62" s="29" t="n">
+        <f aca="false">D39</f>
+        <v>0.0834964192778339</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="B63" s="24" t="s">
+        <v>183</v>
+      </c>
+      <c r="C63" s="29" t="n">
+        <f aca="false">E39</f>
+        <v>0.0828316220417278</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="24" t="s">
+        <v>163</v>
+      </c>
+      <c r="B64" s="24" t="s">
+        <v>183</v>
+      </c>
+      <c r="C64" s="29" t="n">
+        <f aca="false">F39</f>
         <v>0.082</v>
       </c>
-      <c r="C11" s="38" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="24" t="s">
-        <v>178</v>
-      </c>
-      <c r="B12" s="37" t="n">
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="24" t="s">
+        <v>72</v>
+      </c>
+      <c r="B65" s="24" t="s">
+        <v>184</v>
+      </c>
+      <c r="C65" s="29" t="n">
+        <f aca="false">B40</f>
+        <v>0.198580745912181</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="B66" s="24" t="s">
+        <v>184</v>
+      </c>
+      <c r="C66" s="29" t="n">
+        <f aca="false">C40</f>
+        <v>0.178450393967635</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A67" s="24" t="s">
+        <v>74</v>
+      </c>
+      <c r="B67" s="24" t="s">
+        <v>184</v>
+      </c>
+      <c r="C67" s="29" t="n">
+        <f aca="false">D40</f>
+        <v>0.188702982859846</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="B68" s="24" t="s">
+        <v>184</v>
+      </c>
+      <c r="C68" s="29" t="n">
+        <f aca="false">E40</f>
+        <v>0.198261707204939</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A69" s="24" t="s">
+        <v>163</v>
+      </c>
+      <c r="B69" s="24" t="s">
+        <v>184</v>
+      </c>
+      <c r="C69" s="29" t="n">
+        <f aca="false">F40</f>
         <v>0.209</v>
       </c>
-      <c r="C12" s="38" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="24" t="s">
-        <v>180</v>
-      </c>
-      <c r="B13" s="37" t="n">
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A70" s="24" t="s">
+        <v>72</v>
+      </c>
+      <c r="B70" s="24" t="s">
+        <v>185</v>
+      </c>
+      <c r="C70" s="29" t="n">
+        <f aca="false">B41</f>
+        <v>0.0191760058791108</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A71" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="B71" s="24" t="s">
+        <v>185</v>
+      </c>
+      <c r="C71" s="29" t="n">
+        <f aca="false">C41</f>
+        <v>0.0179615352029145</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A72" s="24" t="s">
+        <v>74</v>
+      </c>
+      <c r="B72" s="24" t="s">
+        <v>185</v>
+      </c>
+      <c r="C72" s="29" t="n">
+        <f aca="false">D41</f>
+        <v>0.0178068345555818</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A73" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="B73" s="24" t="s">
+        <v>185</v>
+      </c>
+      <c r="C73" s="29" t="n">
+        <f aca="false">E41</f>
+        <v>0.018247695776868</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A74" s="24" t="s">
+        <v>163</v>
+      </c>
+      <c r="B74" s="24" t="s">
+        <v>185</v>
+      </c>
+      <c r="C74" s="29" t="n">
+        <f aca="false">F41</f>
         <v>0.018</v>
       </c>
-      <c r="C13" s="38" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="24" t="s">
-        <v>182</v>
-      </c>
-      <c r="B14" s="29" t="n">
-        <f aca="false">1+Assumptions_FY2025!B9-Assumptions_FY2025!B10-Assumptions_FY2025!B11-Assumptions_FY2025!B12-Assumptions_FY2025!B13</f>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A75" s="24" t="s">
+        <v>72</v>
+      </c>
+      <c r="B75" s="24" t="s">
+        <v>98</v>
+      </c>
+      <c r="C75" s="29" t="n">
+        <f aca="false">B42</f>
+        <v>0.173606007716333</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A76" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="B76" s="24" t="s">
+        <v>98</v>
+      </c>
+      <c r="C76" s="29" t="n">
+        <f aca="false">C42</f>
+        <v>0.170539269677201</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A77" s="24" t="s">
+        <v>74</v>
+      </c>
+      <c r="B77" s="24" t="s">
+        <v>98</v>
+      </c>
+      <c r="C77" s="29" t="n">
+        <f aca="false">D42</f>
+        <v>0.172616615411084</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A78" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="B78" s="24" t="s">
+        <v>98</v>
+      </c>
+      <c r="C78" s="29" t="n">
+        <f aca="false">E42</f>
+        <v>0.171902708146332</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A79" s="24" t="s">
+        <v>163</v>
+      </c>
+      <c r="B79" s="24" t="s">
+        <v>98</v>
+      </c>
+      <c r="C79" s="29" t="n">
+        <f aca="false">F42</f>
         <v>0.166</v>
       </c>
-      <c r="C14" s="38" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="24" t="s">
-        <v>184</v>
-      </c>
-      <c r="B15" s="37" t="n">
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A80" s="24" t="s">
+        <v>72</v>
+      </c>
+      <c r="B80" s="24" t="s">
+        <v>186</v>
+      </c>
+      <c r="C80" s="29" t="n">
+        <f aca="false">B43</f>
+        <v>-0.033988609222855</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A81" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="B81" s="24" t="s">
+        <v>186</v>
+      </c>
+      <c r="C81" s="29" t="n">
+        <f aca="false">C43</f>
+        <v>-0.030797254935186</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A82" s="24" t="s">
+        <v>74</v>
+      </c>
+      <c r="B82" s="24" t="s">
+        <v>186</v>
+      </c>
+      <c r="C82" s="29" t="n">
+        <f aca="false">D43</f>
+        <v>-0.0164842254672144</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A83" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="B83" s="24" t="s">
+        <v>186</v>
+      </c>
+      <c r="C83" s="29" t="n">
+        <f aca="false">E43</f>
+        <v>-0.0117236245812991</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A84" s="24" t="s">
+        <v>163</v>
+      </c>
+      <c r="B84" s="24" t="s">
+        <v>186</v>
+      </c>
+      <c r="C84" s="29" t="n">
+        <f aca="false">F43</f>
         <v>-0.014</v>
       </c>
-      <c r="C15" s="38" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="24" t="s">
-        <v>186</v>
-      </c>
-      <c r="B16" s="37" t="n">
+    </row>
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A85" s="24" t="s">
+        <v>72</v>
+      </c>
+      <c r="B85" s="24" t="s">
+        <v>99</v>
+      </c>
+      <c r="C85" s="29" t="n">
+        <f aca="false">B44</f>
+        <v>0.139617398493478</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A86" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="B86" s="24" t="s">
+        <v>99</v>
+      </c>
+      <c r="C86" s="29" t="n">
+        <f aca="false">C44</f>
+        <v>0.139742014742015</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A87" s="24" t="s">
+        <v>74</v>
+      </c>
+      <c r="B87" s="24" t="s">
+        <v>99</v>
+      </c>
+      <c r="C87" s="29" t="n">
+        <f aca="false">D44</f>
+        <v>0.15613238994387</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A88" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="B88" s="24" t="s">
+        <v>99</v>
+      </c>
+      <c r="C88" s="29" t="n">
+        <f aca="false">E44</f>
+        <v>0.160179083565033</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A89" s="24" t="s">
+        <v>163</v>
+      </c>
+      <c r="B89" s="24" t="s">
+        <v>99</v>
+      </c>
+      <c r="C89" s="29" t="n">
+        <f aca="false">F44</f>
+        <v>0.152</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A90" s="24" t="s">
+        <v>72</v>
+      </c>
+      <c r="B90" s="24" t="s">
+        <v>187</v>
+      </c>
+      <c r="C90" s="29" t="n">
+        <f aca="false">B45</f>
+        <v>-0.00551166636046298</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A91" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="B91" s="24" t="s">
+        <v>187</v>
+      </c>
+      <c r="C91" s="29" t="n">
+        <f aca="false">C45</f>
+        <v>-0.00920316868592731</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A92" s="24" t="s">
+        <v>74</v>
+      </c>
+      <c r="B92" s="24" t="s">
+        <v>187</v>
+      </c>
+      <c r="C92" s="29" t="n">
+        <f aca="false">D45</f>
+        <v>-0.0049140841738532</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A93" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="B93" s="24" t="s">
+        <v>187</v>
+      </c>
+      <c r="C93" s="29" t="n">
+        <f aca="false">E45</f>
+        <v>0.000996124964424108</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A94" s="24" t="s">
+        <v>163</v>
+      </c>
+      <c r="B94" s="24" t="s">
+        <v>187</v>
+      </c>
+      <c r="C94" s="29" t="n">
+        <f aca="false">F45</f>
         <v>-0.002</v>
       </c>
-      <c r="C16" s="38" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="24" t="s">
+    </row>
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A95" s="24" t="s">
+        <v>72</v>
+      </c>
+      <c r="B95" s="24" t="s">
+        <v>100</v>
+      </c>
+      <c r="C95" s="29" t="n">
+        <f aca="false">B46</f>
+        <v>0.134105732133015</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A96" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="B96" s="24" t="s">
+        <v>100</v>
+      </c>
+      <c r="C96" s="29" t="n">
+        <f aca="false">C46</f>
+        <v>0.130538846056087</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A97" s="24" t="s">
+        <v>74</v>
+      </c>
+      <c r="B97" s="24" t="s">
+        <v>100</v>
+      </c>
+      <c r="C97" s="29" t="n">
+        <f aca="false">D46</f>
+        <v>0.151218305770017</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A98" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="B98" s="24" t="s">
+        <v>100</v>
+      </c>
+      <c r="C98" s="29" t="n">
+        <f aca="false">E46</f>
+        <v>0.161175208529457</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A99" s="24" t="s">
+        <v>163</v>
+      </c>
+      <c r="B99" s="24" t="s">
+        <v>100</v>
+      </c>
+      <c r="C99" s="29" t="n">
+        <f aca="false">F46</f>
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A100" s="24" t="s">
+        <v>72</v>
+      </c>
+      <c r="B100" s="24" t="s">
         <v>188</v>
       </c>
-      <c r="B17" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" s="38" t="s">
+      <c r="C100" s="29" t="n">
+        <f aca="false">B47</f>
+        <v>0.010024343193092</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A101" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="B101" s="24" t="s">
+        <v>188</v>
+      </c>
+      <c r="C101" s="29" t="n">
+        <f aca="false">C47</f>
+        <v>0.0110141489451834</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A102" s="24" t="s">
+        <v>74</v>
+      </c>
+      <c r="B102" s="24" t="s">
+        <v>188</v>
+      </c>
+      <c r="C102" s="29" t="n">
+        <f aca="false">D47</f>
+        <v>0.0146239704079658</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A103" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="B103" s="24" t="s">
+        <v>188</v>
+      </c>
+      <c r="C103" s="29" t="n">
+        <f aca="false">E47</f>
+        <v>0.0162554458480198</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A104" s="24" t="s">
+        <v>163</v>
+      </c>
+      <c r="B104" s="24" t="s">
+        <v>188</v>
+      </c>
+      <c r="C104" s="29" t="n">
+        <f aca="false">F47</f>
+        <v>0.0165710855732241</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A105" s="24" t="s">
+        <v>72</v>
+      </c>
+      <c r="B105" s="24" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="18" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="24" t="s">
-        <v>190</v>
-      </c>
-      <c r="B18" s="37" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="C18" s="38" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="24" t="s">
-        <v>192</v>
-      </c>
-      <c r="B19" s="37" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="C19" s="38" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="24" t="s">
-        <v>194</v>
-      </c>
-      <c r="B20" s="37" t="n">
+      <c r="C105" s="29" t="n">
+        <f aca="false">B48</f>
+        <v>0.209235609846382</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A106" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="B106" s="24" t="s">
+        <v>189</v>
+      </c>
+      <c r="C106" s="29" t="n">
+        <f aca="false">C48</f>
+        <v>0.241892610313663</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A107" s="24" t="s">
+        <v>74</v>
+      </c>
+      <c r="B107" s="24" t="s">
+        <v>189</v>
+      </c>
+      <c r="C107" s="29" t="n">
+        <f aca="false">D48</f>
+        <v>0.182161694088011</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A108" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="B108" s="24" t="s">
+        <v>189</v>
+      </c>
+      <c r="C108" s="29" t="n">
+        <f aca="false">E48</f>
+        <v>0.250321021225168</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A109" s="24" t="s">
+        <v>163</v>
+      </c>
+      <c r="B109" s="24" t="s">
+        <v>189</v>
+      </c>
+      <c r="C109" s="29" t="n">
+        <f aca="false">F48</f>
         <v>0.24</v>
       </c>
-      <c r="C20" s="38" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="24" t="s">
-        <v>196</v>
-      </c>
-      <c r="B21" s="37" t="n">
-        <v>0.026</v>
-      </c>
-      <c r="C21" s="38" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="24" t="s">
-        <v>198</v>
-      </c>
-      <c r="B22" s="39" t="n">
-        <v>2554.7</v>
-      </c>
-      <c r="C22" s="38" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="3"/>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-    </row>
-    <row r="24" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="35" t="s">
-        <v>200</v>
-      </c>
-      <c r="B24" s="36"/>
-      <c r="C24" s="36"/>
-    </row>
-    <row r="25" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="24" t="s">
-        <v>201</v>
-      </c>
-      <c r="B25" s="37" t="n">
-        <v>0.039</v>
-      </c>
-      <c r="C25" s="38" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="24" t="s">
-        <v>203</v>
-      </c>
-      <c r="B26" s="40" t="n">
-        <v>580</v>
-      </c>
-      <c r="C26" s="38" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="24" t="s">
-        <v>205</v>
-      </c>
-      <c r="B27" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="C27" s="38" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="24" t="s">
-        <v>207</v>
-      </c>
-      <c r="B28" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="C28" s="38" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="24" t="s">
-        <v>209</v>
-      </c>
-      <c r="B29" s="37" t="n">
-        <v>0.835</v>
-      </c>
-      <c r="C29" s="38" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="24" t="s">
-        <v>211</v>
-      </c>
-      <c r="B30" s="37" t="n">
-        <v>0.763</v>
-      </c>
-      <c r="C30" s="38" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="24" t="s">
-        <v>213</v>
-      </c>
-      <c r="B31" s="37" t="n">
-        <v>0.727</v>
-      </c>
-      <c r="C31" s="38" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="B32" s="37" t="n">
-        <v>0.608</v>
-      </c>
-      <c r="C32" s="38" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="24" t="s">
-        <v>217</v>
-      </c>
-      <c r="B33" s="37" t="n">
-        <v>0.062</v>
-      </c>
-      <c r="C33" s="38" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="24" t="s">
-        <v>219</v>
-      </c>
-      <c r="B34" s="37" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="C34" s="38" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="24" t="s">
-        <v>221</v>
-      </c>
-      <c r="B35" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="C35" s="38" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="24" t="s">
-        <v>223</v>
-      </c>
-      <c r="B36" s="37" t="n">
-        <v>-0.006</v>
-      </c>
-      <c r="C36" s="38" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="24" t="s">
-        <v>225</v>
-      </c>
-      <c r="B37" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="C37" s="38" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="24" t="s">
-        <v>227</v>
-      </c>
-      <c r="B38" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="C38" s="38" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="24" t="s">
-        <v>229</v>
-      </c>
-      <c r="B39" s="37" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="C39" s="38" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="24" t="s">
-        <v>231</v>
-      </c>
-      <c r="B40" s="40" t="n">
-        <v>-174</v>
-      </c>
-      <c r="C40" s="38" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="24" t="s">
-        <v>233</v>
-      </c>
-      <c r="B41" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="C41" s="38" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="24" t="s">
-        <v>235</v>
-      </c>
-      <c r="B42" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="C42" s="38" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="24" t="s">
-        <v>237</v>
-      </c>
-      <c r="B43" s="40" t="n">
-        <v>7992</v>
-      </c>
-      <c r="C43" s="38" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="24" t="s">
-        <v>239</v>
-      </c>
-      <c r="B44" s="40" t="n">
-        <v>-5055</v>
-      </c>
-      <c r="C44" s="38" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="24" t="s">
-        <v>241</v>
-      </c>
-      <c r="B45" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="C45" s="38" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="24" t="s">
-        <v>243</v>
-      </c>
-      <c r="B46" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="C46" s="38" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="3"/>
-      <c r="B47" s="3"/>
-      <c r="C47" s="3"/>
-    </row>
-    <row r="48" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="31" t="s">
-        <v>245</v>
-      </c>
-      <c r="B48" s="3"/>
-      <c r="C48" s="3"/>
+    </row>
+    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A110" s="24" t="s">
+        <v>72</v>
+      </c>
+      <c r="B110" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="C110" s="29" t="n">
+        <f aca="false">B49</f>
+        <v>0.194113999632556</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A111" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="B111" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="C111" s="29" t="n">
+        <f aca="false">C49</f>
+        <v>0.0981741930017792</v>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A112" s="24" t="s">
+        <v>74</v>
+      </c>
+      <c r="B112" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="C112" s="29" t="n">
+        <f aca="false">D49</f>
+        <v>0.120529473752124</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A113" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="B113" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="C113" s="29" t="n">
+        <f aca="false">E49</f>
+        <v>0.119140924316396</v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A114" s="24" t="s">
+        <v>163</v>
+      </c>
+      <c r="B114" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="C114" s="29" t="n">
+        <f aca="false">F49</f>
+        <v>0.112732471700507</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -5731,1169 +6645,512 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
+    <tabColor rgb="FFED7D31"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D82"/>
+  <dimension ref="A1:C48"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="8" width="58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="8" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="8" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="8" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="8" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="8" width="100"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="34" t="s">
-        <v>246</v>
+        <v>191</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="23" t="s">
+        <v>192</v>
+      </c>
+      <c r="B3" s="23" t="s">
+        <v>193</v>
+      </c>
+      <c r="C3" s="23" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="41" t="s">
+        <v>195</v>
+      </c>
+      <c r="B4" s="42"/>
+      <c r="C4" s="42"/>
+    </row>
+    <row r="5" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="24" t="s">
+        <v>196</v>
+      </c>
+      <c r="B5" s="43" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="C5" s="44" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="24" t="s">
+        <v>167</v>
+      </c>
+      <c r="B6" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="44" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="24" t="s">
+        <v>168</v>
+      </c>
+      <c r="B7" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="44" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="24" t="s">
+        <v>200</v>
+      </c>
+      <c r="B8" s="29" t="n">
+        <f aca="false">'2. Assumptions_FY2025'!B5+'2. Assumptions_FY2025'!B6+'2. Assumptions_FY2025'!B7</f>
+        <v>0.03</v>
+      </c>
+      <c r="C8" s="44" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="24" t="s">
+        <v>202</v>
+      </c>
+      <c r="B9" s="43" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="C9" s="44" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="24" t="s">
+        <v>182</v>
+      </c>
+      <c r="B10" s="43" t="n">
+        <v>0.529</v>
+      </c>
+      <c r="C10" s="44" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="24" t="s">
+        <v>183</v>
+      </c>
+      <c r="B11" s="43" t="n">
+        <v>0.082</v>
+      </c>
+      <c r="C11" s="44" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="24" t="s">
+        <v>184</v>
+      </c>
+      <c r="B12" s="43" t="n">
+        <v>0.209</v>
+      </c>
+      <c r="C12" s="44" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="24" t="s">
+        <v>185</v>
+      </c>
+      <c r="B13" s="43" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="C13" s="44" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="24" t="s">
+        <v>208</v>
+      </c>
+      <c r="B14" s="29" t="n">
+        <f aca="false">1+'2. Assumptions_FY2025'!B9-'2. Assumptions_FY2025'!B10-'2. Assumptions_FY2025'!B11-'2. Assumptions_FY2025'!B12-'2. Assumptions_FY2025'!B13</f>
+        <v>0.166</v>
+      </c>
+      <c r="C14" s="44" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="24" t="s">
+        <v>186</v>
+      </c>
+      <c r="B15" s="43" t="n">
+        <v>-0.014</v>
+      </c>
+      <c r="C15" s="44" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="24" t="s">
+        <v>187</v>
+      </c>
+      <c r="B16" s="43" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="C16" s="44" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="24" t="s">
+        <v>212</v>
+      </c>
+      <c r="B17" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="44" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="24" t="s">
+        <v>214</v>
+      </c>
+      <c r="B18" s="43" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="C18" s="44" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="24" t="s">
+        <v>216</v>
+      </c>
+      <c r="B19" s="43" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="C19" s="44" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="24" t="s">
+        <v>189</v>
+      </c>
+      <c r="B20" s="43" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="C20" s="44" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="24" t="s">
+        <v>219</v>
+      </c>
+      <c r="B21" s="43" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="C21" s="44" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="24" t="s">
+        <v>221</v>
+      </c>
+      <c r="B22" s="45" t="n">
+        <v>2554.7</v>
+      </c>
+      <c r="C22" s="44" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="3"/>
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
+    </row>
+    <row r="24" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="41" t="s">
+        <v>223</v>
+      </c>
+      <c r="B24" s="42"/>
+      <c r="C24" s="42"/>
+    </row>
+    <row r="25" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="24" t="s">
+        <v>224</v>
+      </c>
+      <c r="B25" s="43" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="C25" s="44" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="24" t="s">
+        <v>226</v>
+      </c>
+      <c r="B26" s="46" t="n">
+        <v>580</v>
+      </c>
+      <c r="C26" s="44" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="24" t="s">
+        <v>228</v>
+      </c>
+      <c r="B27" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" s="44" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="24" t="s">
+        <v>230</v>
+      </c>
+      <c r="B28" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="44" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="24" t="s">
+        <v>232</v>
+      </c>
+      <c r="B29" s="43" t="n">
+        <v>0.835</v>
+      </c>
+      <c r="C29" s="44" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="24" t="s">
+        <v>234</v>
+      </c>
+      <c r="B30" s="43" t="n">
+        <v>0.763</v>
+      </c>
+      <c r="C30" s="44" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="24" t="s">
+        <v>236</v>
+      </c>
+      <c r="B31" s="43" t="n">
+        <v>0.727</v>
+      </c>
+      <c r="C31" s="44" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="24" t="s">
+        <v>238</v>
+      </c>
+      <c r="B32" s="43" t="n">
+        <v>0.608</v>
+      </c>
+      <c r="C32" s="44" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="24" t="s">
+        <v>240</v>
+      </c>
+      <c r="B33" s="43" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="C33" s="44" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="24" t="s">
+        <v>242</v>
+      </c>
+      <c r="B34" s="43" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="C34" s="44" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="24" t="s">
+        <v>244</v>
+      </c>
+      <c r="B35" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="44" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="24" t="s">
+        <v>246</v>
+      </c>
+      <c r="B36" s="43" t="n">
+        <v>-0.006</v>
+      </c>
+      <c r="C36" s="44" t="s">
         <v>247</v>
       </c>
-      <c r="B3" s="23" t="s">
+    </row>
+    <row r="37" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="24" t="s">
         <v>248</v>
       </c>
-      <c r="C3" s="23" t="s">
+      <c r="B37" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="44" t="s">
         <v>249</v>
       </c>
-      <c r="D3" s="23" t="s">
+    </row>
+    <row r="38" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="24" t="s">
         <v>250</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="23" t="s">
+      <c r="B38" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" s="44" t="s">
         <v>251</v>
       </c>
-      <c r="B4" s="41"/>
-      <c r="C4" s="41"/>
-      <c r="D4" s="41"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="24" t="s">
-        <v>76</v>
-      </c>
-      <c r="B5" s="42" t="n">
-        <f aca="false">Income_Statement!E4</f>
-        <v>91354</v>
-      </c>
-      <c r="C5" s="42" t="n">
-        <f aca="false">B5*(1+Assumptions_FY2025!B8)</f>
-        <v>94094.62</v>
-      </c>
-      <c r="D5" s="29" t="n">
-        <f aca="false">IFERROR(C5/B5-1,"")</f>
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="24" t="s">
-        <v>77</v>
-      </c>
-      <c r="B6" s="42" t="n">
-        <f aca="false">Income_Statement!E5</f>
-        <v>366</v>
-      </c>
-      <c r="C6" s="42" t="n">
-        <f aca="false">C5*Assumptions_FY2025!B9</f>
-        <v>376.37848</v>
-      </c>
-      <c r="D6" s="29" t="n">
-        <f aca="false">IFERROR(C6/B6-1,"")</f>
-        <v>0.0283565027322403</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="24" t="s">
-        <v>78</v>
-      </c>
-      <c r="B7" s="42" t="n">
-        <f aca="false">Income_Statement!E6</f>
-        <v>-48670</v>
-      </c>
-      <c r="C7" s="42" t="n">
-        <f aca="false">-C5*Assumptions_FY2025!B10</f>
-        <v>-49776.05398</v>
-      </c>
-      <c r="D7" s="29" t="n">
-        <f aca="false">IFERROR(C7/B7-1,"")</f>
-        <v>0.0227255800287651</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="24" t="s">
-        <v>79</v>
-      </c>
-      <c r="B8" s="42" t="n">
-        <f aca="false">Income_Statement!E7</f>
-        <v>-7567</v>
-      </c>
-      <c r="C8" s="42" t="n">
-        <f aca="false">-C5*Assumptions_FY2025!B11</f>
-        <v>-7715.75884</v>
-      </c>
-      <c r="D8" s="29" t="n">
-        <f aca="false">IFERROR(C8/B8-1,"")</f>
-        <v>0.0196588925597991</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="24" t="s">
-        <v>80</v>
-      </c>
-      <c r="B9" s="42" t="n">
-        <f aca="false">Income_Statement!E8</f>
-        <v>-18112</v>
-      </c>
-      <c r="C9" s="42" t="n">
-        <f aca="false">-C5*Assumptions_FY2025!B12</f>
-        <v>-19665.77558</v>
-      </c>
-      <c r="D9" s="29" t="n">
-        <f aca="false">IFERROR(C9/B9-1,"")</f>
-        <v>0.0857870792844522</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="24" t="s">
-        <v>81</v>
-      </c>
-      <c r="B10" s="42" t="n">
-        <f aca="false">Income_Statement!E9</f>
-        <v>-1667</v>
-      </c>
-      <c r="C10" s="42" t="n">
-        <f aca="false">-C5*Assumptions_FY2025!B13</f>
-        <v>-1693.70316</v>
-      </c>
-      <c r="D10" s="29" t="n">
-        <f aca="false">IFERROR(C10/B10-1,"")</f>
-        <v>0.0160186922615475</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="43" t="s">
+    </row>
+    <row r="39" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="24" t="s">
         <v>252</v>
       </c>
-      <c r="B11" s="44" t="n">
-        <f aca="false">Income_Statement!E10</f>
-        <v>15704</v>
-      </c>
-      <c r="C11" s="27" t="n">
-        <f aca="false">SUM(C5:C10)</f>
-        <v>15619.70692</v>
-      </c>
-      <c r="D11" s="45" t="n">
-        <f aca="false">IFERROR(C11/B11-1,"")</f>
-        <v>-0.00536761844116129</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="24" t="s">
+      <c r="B39" s="43" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="C39" s="44" t="s">
         <v>253</v>
       </c>
-      <c r="B12" s="42" t="n">
-        <f aca="false">Income_Statement!E11+Income_Statement!E12</f>
-        <v>-1071</v>
-      </c>
-      <c r="C12" s="42" t="n">
-        <f aca="false">C5*Assumptions_FY2025!B15</f>
-        <v>-1317.32468</v>
-      </c>
-      <c r="D12" s="29" t="n">
-        <f aca="false">IFERROR(C12/B12-1,"")</f>
-        <v>0.229995032679738</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="43" t="s">
-        <v>85</v>
-      </c>
-      <c r="B13" s="44" t="n">
-        <f aca="false">Income_Statement!E13</f>
-        <v>14633</v>
-      </c>
-      <c r="C13" s="27" t="n">
-        <f aca="false">C11+C12</f>
-        <v>14302.38224</v>
-      </c>
-      <c r="D13" s="45" t="n">
-        <f aca="false">IFERROR(C13/B13-1,"")</f>
-        <v>-0.0225939834620377</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="24" t="s">
+    </row>
+    <row r="40" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="24" t="s">
         <v>254</v>
       </c>
-      <c r="B14" s="42" t="n">
-        <f aca="false">Income_Statement!E14+Income_Statement!E15</f>
-        <v>91</v>
-      </c>
-      <c r="C14" s="42" t="n">
-        <f aca="false">C5*Assumptions_FY2025!B16</f>
-        <v>-188.18924</v>
-      </c>
-      <c r="D14" s="29" t="n">
-        <f aca="false">IFERROR(C14/B14-1,"")</f>
-        <v>-3.06801362637363</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="43" t="s">
-        <v>88</v>
-      </c>
-      <c r="B15" s="44" t="n">
-        <f aca="false">Income_Statement!E16</f>
-        <v>14724</v>
-      </c>
-      <c r="C15" s="27" t="n">
-        <f aca="false">C13+C14</f>
-        <v>14114.193</v>
-      </c>
-      <c r="D15" s="45" t="n">
-        <f aca="false">IFERROR(C15/B15-1,"")</f>
-        <v>-0.0414158516707415</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="24" t="s">
-        <v>89</v>
-      </c>
-      <c r="B16" s="42" t="n">
-        <f aca="false">Income_Statement!E17</f>
-        <v>358</v>
-      </c>
-      <c r="C16" s="42" t="n">
-        <f aca="false">B16*(1+Assumptions_FY2025!B17)</f>
-        <v>358</v>
-      </c>
-      <c r="D16" s="29" t="n">
-        <f aca="false">IFERROR(C16/B16-1,"")</f>
+      <c r="B40" s="46" t="n">
+        <v>-174</v>
+      </c>
+      <c r="C40" s="44" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="24" t="s">
+        <v>256</v>
+      </c>
+      <c r="B41" s="46" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="24" t="s">
-        <v>90</v>
-      </c>
-      <c r="B17" s="42" t="n">
-        <f aca="false">Income_Statement!E18</f>
-        <v>-1843</v>
-      </c>
-      <c r="C17" s="42" t="n">
-        <f aca="false">(Income_Statement!E19*(1+Assumptions_FY2025!B18))-C16</f>
-        <v>-1917.25</v>
-      </c>
-      <c r="D17" s="29" t="n">
-        <f aca="false">IFERROR(C17/B17-1,"")</f>
-        <v>0.0402875746066196</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="43" t="s">
-        <v>91</v>
-      </c>
-      <c r="B18" s="44" t="n">
-        <f aca="false">Income_Statement!E19</f>
-        <v>-1485</v>
-      </c>
-      <c r="C18" s="27" t="n">
-        <f aca="false">C16+C17</f>
-        <v>-1559.25</v>
-      </c>
-      <c r="D18" s="45" t="n">
-        <f aca="false">IFERROR(C18/B18-1,"")</f>
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="43" t="s">
-        <v>92</v>
-      </c>
-      <c r="B19" s="44" t="n">
-        <f aca="false">Income_Statement!E20</f>
-        <v>13239</v>
-      </c>
-      <c r="C19" s="27" t="n">
-        <f aca="false">C15+C18</f>
-        <v>12554.943</v>
-      </c>
-      <c r="D19" s="45" t="n">
-        <f aca="false">IFERROR(C19/B19-1,"")</f>
-        <v>-0.0516698391117152</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="24" t="s">
-        <v>93</v>
-      </c>
-      <c r="B20" s="42" t="n">
-        <f aca="false">Income_Statement!E21</f>
-        <v>1249</v>
-      </c>
-      <c r="C20" s="42" t="n">
-        <f aca="false">B20*(1+Assumptions_FY2025!B19)</f>
-        <v>1348.92</v>
-      </c>
-      <c r="D20" s="29" t="n">
-        <f aca="false">IFERROR(C20/B20-1,"")</f>
-        <v>0.0800000000000001</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="24" t="s">
-        <v>94</v>
-      </c>
-      <c r="B21" s="42" t="n">
-        <f aca="false">Income_Statement!E22</f>
-        <v>-3314</v>
-      </c>
-      <c r="C21" s="42" t="n">
-        <f aca="false">-C19*Assumptions_FY2025!B20</f>
-        <v>-3013.18632</v>
-      </c>
-      <c r="D21" s="29" t="n">
-        <f aca="false">IFERROR(C21/B21-1,"")</f>
-        <v>-0.0907705733252865</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="43" t="s">
-        <v>95</v>
-      </c>
-      <c r="B22" s="44" t="n">
-        <f aca="false">Income_Statement!E23</f>
-        <v>11174</v>
-      </c>
-      <c r="C22" s="27" t="n">
-        <f aca="false">C19+C20+C21</f>
-        <v>10890.67668</v>
-      </c>
-      <c r="D22" s="45" t="n">
-        <f aca="false">IFERROR(C22/B22-1,"")</f>
-        <v>-0.0253555861822085</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="24" t="s">
-        <v>96</v>
-      </c>
-      <c r="B23" s="42" t="n">
-        <f aca="false">Income_Statement!E24</f>
-        <v>290</v>
-      </c>
-      <c r="C23" s="42" t="n">
-        <f aca="false">C22*Assumptions_FY2025!B21</f>
-        <v>283.15759368</v>
-      </c>
-      <c r="D23" s="29" t="n">
-        <f aca="false">IFERROR(C23/B23-1,"")</f>
-        <v>-0.023594504551724</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="43" t="s">
-        <v>97</v>
-      </c>
-      <c r="B24" s="44" t="n">
-        <f aca="false">Income_Statement!E25</f>
-        <v>10884</v>
-      </c>
-      <c r="C24" s="27" t="n">
-        <f aca="false">C22-C23</f>
-        <v>10607.51908632</v>
-      </c>
-      <c r="D24" s="45" t="n">
-        <f aca="false">IFERROR(C24/B24-1,"")</f>
-        <v>-0.0254025095259094</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="3"/>
-      <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="24" t="s">
-        <v>98</v>
-      </c>
-      <c r="B26" s="46" t="n">
-        <f aca="false">IFERROR(B11/B5,"")</f>
-        <v>0.171902708146332</v>
-      </c>
-      <c r="C26" s="29" t="n">
-        <f aca="false">IFERROR(C11/C5,"")</f>
-        <v>0.166</v>
-      </c>
-      <c r="D26" s="3"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="24" t="s">
-        <v>99</v>
-      </c>
-      <c r="B27" s="46" t="n">
-        <f aca="false">IFERROR(B13/B5,"")</f>
-        <v>0.160179083565033</v>
-      </c>
-      <c r="C27" s="29" t="n">
-        <f aca="false">IFERROR(C13/C5,"")</f>
-        <v>0.152</v>
-      </c>
-      <c r="D27" s="3"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="24" t="s">
-        <v>100</v>
-      </c>
-      <c r="B28" s="46" t="n">
-        <f aca="false">IFERROR(B15/B5,"")</f>
-        <v>0.161175208529457</v>
-      </c>
-      <c r="C28" s="29" t="n">
-        <f aca="false">IFERROR(C15/C5,"")</f>
-        <v>0.15</v>
-      </c>
-      <c r="D28" s="3"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="24" t="s">
-        <v>101</v>
-      </c>
-      <c r="B29" s="46" t="n">
-        <f aca="false">IFERROR(B24/B5,"")</f>
-        <v>0.119140924316396</v>
-      </c>
-      <c r="C29" s="29" t="n">
-        <f aca="false">IFERROR(C24/C5,"")</f>
-        <v>0.112732471700507</v>
-      </c>
-      <c r="D29" s="3"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="24" t="s">
-        <v>194</v>
-      </c>
-      <c r="B30" s="46" t="n">
-        <f aca="false">IFERROR(-B21/B19,"")</f>
-        <v>0.250321021225168</v>
-      </c>
-      <c r="C30" s="29" t="n">
-        <f aca="false">IFERROR(-C21/C19,"")</f>
-        <v>0.24</v>
-      </c>
-      <c r="D30" s="3"/>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="3"/>
-      <c r="B31" s="3"/>
-      <c r="C31" s="3"/>
-      <c r="D31" s="3"/>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="24" t="s">
-        <v>255</v>
-      </c>
-      <c r="B32" s="47" t="n">
-        <f aca="false">Income_Statement!E33</f>
-        <v>4.19</v>
-      </c>
-      <c r="C32" s="48" t="n">
-        <f aca="false">IFERROR(C24/Assumptions_FY2025!B22,"")</f>
-        <v>4.15215840854895</v>
-      </c>
-      <c r="D32" s="3"/>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="3"/>
-      <c r="B33" s="3"/>
-      <c r="C33" s="3"/>
-      <c r="D33" s="3"/>
-    </row>
-    <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="23" t="s">
-        <v>256</v>
-      </c>
-      <c r="B34" s="41"/>
-      <c r="C34" s="41"/>
-      <c r="D34" s="41"/>
-    </row>
-    <row r="35" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="49" t="s">
-        <v>110</v>
-      </c>
-      <c r="B35" s="3"/>
-      <c r="C35" s="3"/>
-      <c r="D35" s="3"/>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="24" t="s">
+      <c r="C41" s="44" t="s">
         <v>257</v>
       </c>
-      <c r="B36" s="42" t="n">
-        <f aca="false">Cash_Flow_Statement!E5</f>
-        <v>14724</v>
-      </c>
-      <c r="C36" s="50" t="n">
-        <f aca="false">C15</f>
-        <v>14114.193</v>
-      </c>
-      <c r="D36" s="29" t="n">
-        <f aca="false">IFERROR(C36/B36-1,"")</f>
-        <v>-0.0414158516707415</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="24" t="s">
-        <v>112</v>
-      </c>
-      <c r="B37" s="42" t="n">
-        <f aca="false">Cash_Flow_Statement!E6</f>
-        <v>3582</v>
-      </c>
-      <c r="C37" s="42" t="n">
-        <f aca="false">C5*Assumptions_FY2025!B25</f>
-        <v>3669.69018</v>
-      </c>
-      <c r="D37" s="29" t="n">
-        <f aca="false">IFERROR(C37/B37-1,"")</f>
-        <v>0.0244807872696817</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="24" t="s">
-        <v>113</v>
-      </c>
-      <c r="B38" s="42" t="n">
-        <f aca="false">Cash_Flow_Statement!E7</f>
-        <v>580</v>
-      </c>
-      <c r="C38" s="42" t="n">
-        <f aca="false">Assumptions_FY2025!B26</f>
-        <v>580</v>
-      </c>
-      <c r="D38" s="29" t="n">
-        <f aca="false">IFERROR(C38/B38-1,"")</f>
+    </row>
+    <row r="42" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="24" t="s">
+        <v>258</v>
+      </c>
+      <c r="B42" s="46" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="24" t="s">
-        <v>258</v>
-      </c>
-      <c r="B39" s="42" t="n">
-        <f aca="false">Cash_Flow_Statement!E8+Cash_Flow_Statement!E9</f>
-        <v>-167</v>
-      </c>
-      <c r="C39" s="42" t="n">
-        <f aca="false">Assumptions_FY2025!B27</f>
+      <c r="C42" s="44" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="24" t="s">
+        <v>260</v>
+      </c>
+      <c r="B43" s="46" t="n">
+        <v>7992</v>
+      </c>
+      <c r="C43" s="44" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="24" t="s">
+        <v>262</v>
+      </c>
+      <c r="B44" s="46" t="n">
+        <v>-5055</v>
+      </c>
+      <c r="C44" s="44" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="24" t="s">
+        <v>264</v>
+      </c>
+      <c r="B45" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="D39" s="29" t="n">
-        <f aca="false">IFERROR(C39/B39-1,"")</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="43" t="s">
-        <v>116</v>
-      </c>
-      <c r="B40" s="44" t="n">
-        <f aca="false">Cash_Flow_Statement!E10</f>
-        <v>18719</v>
-      </c>
-      <c r="C40" s="27" t="n">
-        <f aca="false">SUM(C36:C39)</f>
-        <v>18363.88318</v>
-      </c>
-      <c r="D40" s="45" t="n">
-        <f aca="false">IFERROR(C40/B40-1,"")</f>
-        <v>-0.0189709290026174</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="24" t="s">
-        <v>259</v>
-      </c>
-      <c r="B41" s="42" t="n">
-        <f aca="false">Cash_Flow_Statement!E11+Cash_Flow_Statement!E12</f>
-        <v>874</v>
-      </c>
-      <c r="C41" s="42" t="n">
-        <f aca="false">Assumptions_FY2025!B28</f>
+      <c r="C45" s="44" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="24" t="s">
+        <v>266</v>
+      </c>
+      <c r="B46" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="D41" s="29" t="n">
-        <f aca="false">IFERROR(C41/B41-1,"")</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="43" t="s">
-        <v>119</v>
-      </c>
-      <c r="B42" s="44" t="n">
-        <f aca="false">Cash_Flow_Statement!E13</f>
-        <v>19593</v>
-      </c>
-      <c r="C42" s="27" t="n">
-        <f aca="false">C40+C41</f>
-        <v>18363.88318</v>
-      </c>
-      <c r="D42" s="45" t="n">
-        <f aca="false">IFERROR(C42/B42-1,"")</f>
-        <v>-0.0627324462818352</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="24" t="s">
-        <v>120</v>
-      </c>
-      <c r="B43" s="42" t="n">
-        <f aca="false">Cash_Flow_Statement!E14</f>
-        <v>-1539</v>
-      </c>
-      <c r="C43" s="42" t="n">
-        <f aca="false">C17*Assumptions_FY2025!B29</f>
-        <v>-1600.90375</v>
-      </c>
-      <c r="D43" s="29" t="n">
-        <f aca="false">IFERROR(C43/B43-1,"")</f>
-        <v>0.0402233593242365</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="24" t="s">
-        <v>121</v>
-      </c>
-      <c r="B44" s="42" t="n">
-        <f aca="false">Cash_Flow_Statement!E15</f>
-        <v>273</v>
-      </c>
-      <c r="C44" s="42" t="n">
-        <f aca="false">C16*Assumptions_FY2025!B30</f>
-        <v>273.154</v>
-      </c>
-      <c r="D44" s="29" t="n">
-        <f aca="false">IFERROR(C44/B44-1,"")</f>
-        <v>0.000564102564102553</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="24" t="s">
-        <v>122</v>
-      </c>
-      <c r="B45" s="42" t="n">
-        <f aca="false">Cash_Flow_Statement!E16</f>
-        <v>-2411</v>
-      </c>
-      <c r="C45" s="42" t="n">
-        <f aca="false">C21*Assumptions_FY2025!B31</f>
-        <v>-2190.58645464</v>
-      </c>
-      <c r="D45" s="29" t="n">
-        <f aca="false">IFERROR(C45/B45-1,"")</f>
-        <v>-0.0914199690418912</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="24" t="s">
-        <v>123</v>
-      </c>
-      <c r="B46" s="42" t="n">
-        <f aca="false">Cash_Flow_Statement!E17</f>
-        <v>759</v>
-      </c>
-      <c r="C46" s="42" t="n">
-        <f aca="false">C20*Assumptions_FY2025!B32</f>
-        <v>820.14336</v>
-      </c>
-      <c r="D46" s="29" t="n">
-        <f aca="false">IFERROR(C46/B46-1,"")</f>
-        <v>0.0805577865612648</v>
+      <c r="C46" s="44" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="43" t="s">
-        <v>124</v>
-      </c>
-      <c r="B47" s="44" t="n">
-        <f aca="false">Cash_Flow_Statement!E18</f>
-        <v>16675</v>
-      </c>
-      <c r="C47" s="27" t="n">
-        <f aca="false">C42+C43+C44+C45+C46</f>
-        <v>15665.69033536</v>
-      </c>
-      <c r="D47" s="45" t="n">
-        <f aca="false">IFERROR(C47/B47-1,"")</f>
-        <v>-0.0605283157205396</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="3"/>
+      <c r="A47" s="3"/>
+      <c r="B47" s="3"/>
+      <c r="C47" s="3"/>
+    </row>
+    <row r="48" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="31" t="s">
+        <v>268</v>
+      </c>
       <c r="B48" s="3"/>
       <c r="C48" s="3"/>
-      <c r="D48" s="3"/>
-    </row>
-    <row r="49" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="49" t="s">
-        <v>125</v>
-      </c>
-      <c r="B49" s="3"/>
-      <c r="C49" s="3"/>
-      <c r="D49" s="3"/>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="24" t="s">
-        <v>126</v>
-      </c>
-      <c r="B50" s="42" t="n">
-        <f aca="false">Cash_Flow_Statement!E21</f>
-        <v>-5638</v>
-      </c>
-      <c r="C50" s="42" t="n">
-        <f aca="false">-C5*Assumptions_FY2025!B33</f>
-        <v>-5833.86644</v>
-      </c>
-      <c r="D50" s="29" t="n">
-        <f aca="false">IFERROR(C50/B50-1,"")</f>
-        <v>0.0347404114934373</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="24" t="s">
-        <v>127</v>
-      </c>
-      <c r="B51" s="42" t="n">
-        <f aca="false">Cash_Flow_Statement!E22</f>
-        <v>-325</v>
-      </c>
-      <c r="C51" s="42" t="n">
-        <f aca="false">-C5*Assumptions_FY2025!B34</f>
-        <v>-376.37848</v>
-      </c>
-      <c r="D51" s="29" t="n">
-        <f aca="false">IFERROR(C51/B51-1,"")</f>
-        <v>0.158087630769231</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="24" t="s">
-        <v>260</v>
-      </c>
-      <c r="B52" s="42" t="n">
-        <f aca="false">Cash_Flow_Statement!E23+Cash_Flow_Statement!E24</f>
-        <v>-832</v>
-      </c>
-      <c r="C52" s="42" t="n">
-        <f aca="false">Assumptions_FY2025!B35</f>
-        <v>0</v>
-      </c>
-      <c r="D52" s="29" t="n">
-        <f aca="false">IFERROR(C52/B52-1,"")</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="24" t="s">
-        <v>130</v>
-      </c>
-      <c r="B53" s="42" t="n">
-        <f aca="false">Cash_Flow_Statement!E25</f>
-        <v>-532</v>
-      </c>
-      <c r="C53" s="42" t="n">
-        <f aca="false">C5*Assumptions_FY2025!B36</f>
-        <v>-564.56772</v>
-      </c>
-      <c r="D53" s="29" t="n">
-        <f aca="false">IFERROR(C53/B53-1,"")</f>
-        <v>0.0612175187969926</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="24" t="s">
-        <v>131</v>
-      </c>
-      <c r="B54" s="42" t="n">
-        <f aca="false">Cash_Flow_Statement!E26</f>
-        <v>0</v>
-      </c>
-      <c r="C54" s="42" t="n">
-        <f aca="false">Assumptions_FY2025!B37</f>
-        <v>0</v>
-      </c>
-      <c r="D54" s="29" t="str">
-        <f aca="false">IFERROR(C54/B54-1,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="24" t="s">
-        <v>261</v>
-      </c>
-      <c r="B55" s="42" t="n">
-        <f aca="false">Cash_Flow_Statement!E27+Cash_Flow_Statement!E28</f>
-        <v>-1297</v>
-      </c>
-      <c r="C55" s="42" t="n">
-        <f aca="false">Assumptions_FY2025!B38</f>
-        <v>0</v>
-      </c>
-      <c r="D55" s="29" t="n">
-        <f aca="false">IFERROR(C55/B55-1,"")</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="43" t="s">
-        <v>134</v>
-      </c>
-      <c r="B56" s="44" t="n">
-        <f aca="false">Cash_Flow_Statement!E29</f>
-        <v>-8624</v>
-      </c>
-      <c r="C56" s="27" t="n">
-        <f aca="false">SUM(C50:C55)</f>
-        <v>-6774.81264</v>
-      </c>
-      <c r="D56" s="45" t="n">
-        <f aca="false">IFERROR(C56/B56-1,"")</f>
-        <v>-0.214423395176252</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="3"/>
-      <c r="B57" s="3"/>
-      <c r="C57" s="3"/>
-      <c r="D57" s="3"/>
-    </row>
-    <row r="58" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="49" t="s">
-        <v>135</v>
-      </c>
-      <c r="B58" s="3"/>
-      <c r="C58" s="3"/>
-      <c r="D58" s="3"/>
-    </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="24" t="s">
-        <v>136</v>
-      </c>
-      <c r="B59" s="42" t="n">
-        <f aca="false">Cash_Flow_Statement!E32</f>
-        <v>-7816</v>
-      </c>
-      <c r="C59" s="42" t="n">
-        <f aca="false">B59*(1+Assumptions_FY2025!B39)</f>
-        <v>-7972.32</v>
-      </c>
-      <c r="D59" s="29" t="n">
-        <f aca="false">IFERROR(C59/B59-1,"")</f>
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="24" t="s">
-        <v>137</v>
-      </c>
-      <c r="B60" s="42" t="n">
-        <f aca="false">Cash_Flow_Statement!E33</f>
-        <v>-174</v>
-      </c>
-      <c r="C60" s="42" t="n">
-        <f aca="false">Assumptions_FY2025!B40</f>
-        <v>-174</v>
-      </c>
-      <c r="D60" s="29" t="n">
-        <f aca="false">IFERROR(C60/B60-1,"")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="24" t="s">
-        <v>138</v>
-      </c>
-      <c r="B61" s="42" t="n">
-        <f aca="false">Cash_Flow_Statement!E34</f>
-        <v>-27</v>
-      </c>
-      <c r="C61" s="42" t="n">
-        <f aca="false">Assumptions_FY2025!B41</f>
-        <v>0</v>
-      </c>
-      <c r="D61" s="29" t="n">
-        <f aca="false">IFERROR(C61/B61-1,"")</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="24" t="s">
-        <v>139</v>
-      </c>
-      <c r="B62" s="42" t="n">
-        <f aca="false">Cash_Flow_Statement!E35</f>
-        <v>-4678</v>
-      </c>
-      <c r="C62" s="42" t="n">
-        <f aca="false">Assumptions_FY2025!B42</f>
-        <v>0</v>
-      </c>
-      <c r="D62" s="29" t="n">
-        <f aca="false">IFERROR(C62/B62-1,"")</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="24" t="s">
-        <v>140</v>
-      </c>
-      <c r="B63" s="42" t="n">
-        <f aca="false">Cash_Flow_Statement!E36</f>
-        <v>7992</v>
-      </c>
-      <c r="C63" s="42" t="n">
-        <f aca="false">Assumptions_FY2025!B43</f>
-        <v>7992</v>
-      </c>
-      <c r="D63" s="29" t="n">
-        <f aca="false">IFERROR(C63/B63-1,"")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="24" t="s">
-        <v>141</v>
-      </c>
-      <c r="B64" s="42" t="n">
-        <f aca="false">Cash_Flow_Statement!E37</f>
-        <v>-5055</v>
-      </c>
-      <c r="C64" s="42" t="n">
-        <f aca="false">Assumptions_FY2025!B44</f>
-        <v>-5055</v>
-      </c>
-      <c r="D64" s="29" t="n">
-        <f aca="false">IFERROR(C64/B64-1,"")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="24" t="s">
-        <v>142</v>
-      </c>
-      <c r="B65" s="42" t="n">
-        <f aca="false">Cash_Flow_Statement!E38</f>
-        <v>2396</v>
-      </c>
-      <c r="C65" s="42" t="n">
-        <f aca="false">Assumptions_FY2025!B45</f>
-        <v>0</v>
-      </c>
-      <c r="D65" s="29" t="n">
-        <f aca="false">IFERROR(C65/B65-1,"")</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="43" t="s">
-        <v>143</v>
-      </c>
-      <c r="B66" s="44" t="n">
-        <f aca="false">Cash_Flow_Statement!E39</f>
-        <v>-7362</v>
-      </c>
-      <c r="C66" s="27" t="n">
-        <f aca="false">SUM(C59:C65)</f>
-        <v>-5209.32</v>
-      </c>
-      <c r="D66" s="45" t="n">
-        <f aca="false">IFERROR(C66/B66-1,"")</f>
-        <v>-0.29240423797881</v>
-      </c>
-    </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A67" s="3"/>
-      <c r="B67" s="3"/>
-      <c r="C67" s="3"/>
-      <c r="D67" s="3"/>
-    </row>
-    <row r="68" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A68" s="49" t="s">
-        <v>144</v>
-      </c>
-      <c r="B68" s="3"/>
-      <c r="C68" s="3"/>
-      <c r="D68" s="3"/>
-    </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="24" t="s">
-        <v>145</v>
-      </c>
-      <c r="B69" s="42" t="n">
-        <f aca="false">Cash_Flow_Statement!E42</f>
-        <v>53</v>
-      </c>
-      <c r="C69" s="42" t="n">
-        <f aca="false">Assumptions_FY2025!B46</f>
-        <v>0</v>
-      </c>
-      <c r="D69" s="29" t="n">
-        <f aca="false">IFERROR(C69/B69-1,"")</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A70" s="43" t="s">
-        <v>146</v>
-      </c>
-      <c r="B70" s="44" t="n">
-        <f aca="false">Cash_Flow_Statement!E43</f>
-        <v>742</v>
-      </c>
-      <c r="C70" s="27" t="n">
-        <f aca="false">C47+C56+C66+C69</f>
-        <v>3681.55769536</v>
-      </c>
-      <c r="D70" s="45" t="n">
-        <f aca="false">IFERROR(C70/B70-1,"")</f>
-        <v>3.96166805304582</v>
-      </c>
-    </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A71" s="24" t="s">
-        <v>147</v>
-      </c>
-      <c r="B71" s="42" t="n">
-        <f aca="false">Cash_Flow_Statement!E44</f>
-        <v>4816</v>
-      </c>
-      <c r="C71" s="42" t="n">
-        <f aca="false">Cash_Flow_Statement!E45</f>
-        <v>5558</v>
-      </c>
-      <c r="D71" s="29" t="n">
-        <f aca="false">IFERROR(C71/B71-1,"")</f>
-        <v>0.154069767441861</v>
-      </c>
-    </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A72" s="43" t="s">
-        <v>148</v>
-      </c>
-      <c r="B72" s="44" t="n">
-        <f aca="false">Cash_Flow_Statement!E45</f>
-        <v>5558</v>
-      </c>
-      <c r="C72" s="27" t="n">
-        <f aca="false">C70+C71</f>
-        <v>9239.55769536</v>
-      </c>
-      <c r="D72" s="45" t="n">
-        <f aca="false">IFERROR(C72/B72-1,"")</f>
-        <v>0.662388934033825</v>
-      </c>
-    </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="3"/>
-      <c r="B73" s="3"/>
-      <c r="C73" s="3"/>
-      <c r="D73" s="3"/>
-    </row>
-    <row r="74" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A74" s="49" t="s">
-        <v>151</v>
-      </c>
-      <c r="B74" s="3"/>
-      <c r="C74" s="3"/>
-      <c r="D74" s="3"/>
-    </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A75" s="43" t="s">
-        <v>153</v>
-      </c>
-      <c r="B75" s="44" t="n">
-        <f aca="false">Cash_Flow_Statement!E51</f>
-        <v>10712</v>
-      </c>
-      <c r="C75" s="27" t="n">
-        <f aca="false">C47+C50+C51</f>
-        <v>9455.44541536</v>
-      </c>
-      <c r="D75" s="45" t="n">
-        <f aca="false">IFERROR(C75/B75-1,"")</f>
-        <v>-0.117303452636296</v>
-      </c>
-    </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A76" s="24" t="s">
-        <v>262</v>
-      </c>
-      <c r="B76" s="46" t="n">
-        <f aca="false">IFERROR(B75/B5,"")</f>
-        <v>0.117258138669352</v>
-      </c>
-      <c r="C76" s="29" t="n">
-        <f aca="false">IFERROR(C75/C5,"")</f>
-        <v>0.100488693353138</v>
-      </c>
-      <c r="D76" s="3"/>
-    </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A77" s="3"/>
-      <c r="B77" s="3"/>
-      <c r="C77" s="3"/>
-      <c r="D77" s="3"/>
-    </row>
-    <row r="78" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A78" s="31" t="s">
-        <v>263</v>
-      </c>
-      <c r="B78" s="3"/>
-      <c r="C78" s="3"/>
-      <c r="D78" s="3"/>
-    </row>
-    <row r="79" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="31" t="s">
-        <v>264</v>
-      </c>
-      <c r="B79" s="3"/>
-      <c r="C79" s="3"/>
-      <c r="D79" s="3"/>
-    </row>
-    <row r="80" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A80" s="31" t="s">
-        <v>265</v>
-      </c>
-      <c r="B80" s="3"/>
-      <c r="C80" s="3"/>
-      <c r="D80" s="3"/>
-    </row>
-    <row r="81" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A81" s="31" t="s">
-        <v>266</v>
-      </c>
-      <c r="B81" s="3"/>
-      <c r="C81" s="3"/>
-      <c r="D81" s="3"/>
-    </row>
-    <row r="82" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A82" s="31" t="s">
-        <v>267</v>
-      </c>
-      <c r="B82" s="3"/>
-      <c r="C82" s="3"/>
-      <c r="D82" s="3"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -6909,1420 +7166,1170 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
+    <tabColor rgb="FFED7D31"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F114"/>
+  <dimension ref="A1:D82"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="8" width="42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="2" style="8" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="8" width="58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="8" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="8" width="16"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="34" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="31" t="s">
         <v>269</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="23" t="s">
+        <v>181</v>
+      </c>
+      <c r="B3" s="23" t="s">
+        <v>270</v>
+      </c>
+      <c r="C3" s="23" t="s">
+        <v>163</v>
+      </c>
+      <c r="D3" s="23" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="23" t="s">
-        <v>270</v>
-      </c>
-      <c r="B4" s="51"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51"/>
+        <v>272</v>
+      </c>
+      <c r="B4" s="47"/>
+      <c r="C4" s="47"/>
+      <c r="D4" s="47"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="23" t="s">
-        <v>271</v>
-      </c>
-      <c r="B5" s="23" t="s">
-        <v>73</v>
-      </c>
-      <c r="C5" s="23" t="s">
-        <v>75</v>
-      </c>
-      <c r="D5" s="23" t="s">
-        <v>249</v>
+      <c r="A5" s="24" t="s">
+        <v>76</v>
+      </c>
+      <c r="B5" s="48" t="n">
+        <f aca="false">'1. Income_Statement'!E4</f>
+        <v>91354</v>
+      </c>
+      <c r="C5" s="48" t="n">
+        <f aca="false">B5*(1+'2. Assumptions_FY2025'!B8)</f>
+        <v>94094.62</v>
+      </c>
+      <c r="D5" s="29" t="n">
+        <f aca="false">IFERROR(C5/B5-1,"")</f>
+        <v>0.03</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="24" t="s">
-        <v>272</v>
-      </c>
-      <c r="B6" s="46" t="n">
-        <f aca="false">Segment_Data!Q12</f>
-        <v>0.001</v>
-      </c>
-      <c r="C6" s="46" t="n">
-        <f aca="false">Segment_Data!V12</f>
-        <v>0.008</v>
+        <v>77</v>
+      </c>
+      <c r="B6" s="48" t="n">
+        <f aca="false">'1. Income_Statement'!E5</f>
+        <v>366</v>
+      </c>
+      <c r="C6" s="48" t="n">
+        <f aca="false">C5*'2. Assumptions_FY2025'!B9</f>
+        <v>376.37848</v>
+      </c>
+      <c r="D6" s="29" t="n">
+        <f aca="false">IFERROR(C6/B6-1,"")</f>
+        <v>0.0283565027322403</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="24" t="s">
-        <v>273</v>
-      </c>
-      <c r="B7" s="46" t="n">
-        <f aca="false">Segment_Data!R12</f>
-        <v>0.082</v>
-      </c>
-      <c r="C7" s="46" t="n">
-        <f aca="false">Segment_Data!W12</f>
-        <v>0.015</v>
+        <v>78</v>
+      </c>
+      <c r="B7" s="48" t="n">
+        <f aca="false">'1. Income_Statement'!E6</f>
+        <v>-48670</v>
+      </c>
+      <c r="C7" s="48" t="n">
+        <f aca="false">-C5*'2. Assumptions_FY2025'!B10</f>
+        <v>-49776.05398</v>
+      </c>
+      <c r="D7" s="29" t="n">
+        <f aca="false">IFERROR(C7/B7-1,"")</f>
+        <v>0.0227255800287651</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="43" t="s">
-        <v>274</v>
-      </c>
-      <c r="B8" s="45" t="n">
-        <f aca="false">Segment_Data!S12</f>
-        <v>0.083</v>
-      </c>
-      <c r="C8" s="45" t="n">
-        <f aca="false">Segment_Data!X12</f>
-        <v>0.022</v>
-      </c>
-      <c r="D8" s="45" t="n">
-        <f aca="false">Assumptions_FY2025!B5</f>
-        <v>0.03</v>
+      <c r="A8" s="24" t="s">
+        <v>79</v>
+      </c>
+      <c r="B8" s="48" t="n">
+        <f aca="false">'1. Income_Statement'!E7</f>
+        <v>-7567</v>
+      </c>
+      <c r="C8" s="48" t="n">
+        <f aca="false">-C5*'2. Assumptions_FY2025'!B11</f>
+        <v>-7715.75884</v>
+      </c>
+      <c r="D8" s="29" t="n">
+        <f aca="false">IFERROR(C8/B8-1,"")</f>
+        <v>0.0196588925597991</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="24" t="s">
-        <v>166</v>
-      </c>
-      <c r="B9" s="46" t="n">
-        <f aca="false">Segment_Data!T12</f>
-        <v>0.011</v>
-      </c>
-      <c r="C9" s="46" t="n">
-        <f aca="false">Segment_Data!Y12</f>
-        <v>-0.003</v>
-      </c>
-      <c r="D9" s="46" t="n">
-        <f aca="false">Assumptions_FY2025!B6</f>
-        <v>0</v>
+        <v>80</v>
+      </c>
+      <c r="B9" s="48" t="n">
+        <f aca="false">'1. Income_Statement'!E8</f>
+        <v>-18112</v>
+      </c>
+      <c r="C9" s="48" t="n">
+        <f aca="false">-C5*'2. Assumptions_FY2025'!B12</f>
+        <v>-19665.77558</v>
+      </c>
+      <c r="D9" s="29" t="n">
+        <f aca="false">IFERROR(C9/B9-1,"")</f>
+        <v>0.0857870792844522</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="24" t="s">
-        <v>168</v>
-      </c>
-      <c r="B10" s="46" t="n">
-        <f aca="false">Segment_Data!U12</f>
-        <v>-0.009</v>
-      </c>
-      <c r="C10" s="46" t="n">
-        <f aca="false">Segment_Data!Z12</f>
-        <v>-0.037</v>
-      </c>
-      <c r="D10" s="46" t="n">
-        <f aca="false">Assumptions_FY2025!B7</f>
-        <v>0</v>
+        <v>81</v>
+      </c>
+      <c r="B10" s="48" t="n">
+        <f aca="false">'1. Income_Statement'!E9</f>
+        <v>-1667</v>
+      </c>
+      <c r="C10" s="48" t="n">
+        <f aca="false">-C5*'2. Assumptions_FY2025'!B13</f>
+        <v>-1693.70316</v>
+      </c>
+      <c r="D10" s="29" t="n">
+        <f aca="false">IFERROR(C10/B10-1,"")</f>
+        <v>0.0160186922615475</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="43" t="s">
-        <v>275</v>
-      </c>
-      <c r="B11" s="45" t="n">
-        <f aca="false">B8+B9+B10</f>
-        <v>0.085</v>
-      </c>
-      <c r="C11" s="45" t="n">
-        <f aca="false">C8+C9+C10</f>
-        <v>-0.018</v>
-      </c>
-      <c r="D11" s="45" t="n">
-        <f aca="false">Assumptions_FY2025!B8</f>
-        <v>0.03</v>
+      <c r="A11" s="37" t="s">
+        <v>273</v>
+      </c>
+      <c r="B11" s="49" t="n">
+        <f aca="false">'1. Income_Statement'!E10</f>
+        <v>15704</v>
+      </c>
+      <c r="C11" s="27" t="n">
+        <f aca="false">SUM(C5:C10)</f>
+        <v>15619.70692</v>
+      </c>
+      <c r="D11" s="38" t="n">
+        <f aca="false">IFERROR(C11/B11-1,"")</f>
+        <v>-0.00536761844116129</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="24" t="s">
+        <v>274</v>
+      </c>
+      <c r="B12" s="48" t="n">
+        <f aca="false">'1. Income_Statement'!E11+'1. Income_Statement'!E12</f>
+        <v>-1071</v>
+      </c>
+      <c r="C12" s="48" t="n">
+        <f aca="false">C5*'2. Assumptions_FY2025'!B15</f>
+        <v>-1317.32468</v>
+      </c>
+      <c r="D12" s="29" t="n">
+        <f aca="false">IFERROR(C12/B12-1,"")</f>
+        <v>0.229995032679738</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="52" t="s">
-        <v>276</v>
+      <c r="A13" s="37" t="s">
+        <v>85</v>
+      </c>
+      <c r="B13" s="49" t="n">
+        <f aca="false">'1. Income_Statement'!E13</f>
+        <v>14633</v>
+      </c>
+      <c r="C13" s="27" t="n">
+        <f aca="false">C11+C12</f>
+        <v>14302.38224</v>
+      </c>
+      <c r="D13" s="38" t="n">
+        <f aca="false">IFERROR(C13/B13-1,"")</f>
+        <v>-0.0225939834620377</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="24" t="s">
-        <v>277</v>
-      </c>
-      <c r="B14" s="46" t="n">
-        <f aca="false">Segment_Data!F12</f>
-        <v>0.0842366342090759</v>
-      </c>
-      <c r="C14" s="46" t="n">
-        <f aca="false">Segment_Data!H12</f>
-        <v>-0.0176777995225704</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="31" t="s">
-        <v>278</v>
+        <v>275</v>
+      </c>
+      <c r="B14" s="48" t="n">
+        <f aca="false">'1. Income_Statement'!E14+'1. Income_Statement'!E15</f>
+        <v>91</v>
+      </c>
+      <c r="C14" s="48" t="n">
+        <f aca="false">C5*'2. Assumptions_FY2025'!B16</f>
+        <v>-188.18924</v>
+      </c>
+      <c r="D14" s="29" t="n">
+        <f aca="false">IFERROR(C14/B14-1,"")</f>
+        <v>-3.06801362637363</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="37" t="s">
+        <v>88</v>
+      </c>
+      <c r="B15" s="49" t="n">
+        <f aca="false">'1. Income_Statement'!E16</f>
+        <v>14724</v>
+      </c>
+      <c r="C15" s="27" t="n">
+        <f aca="false">C13+C14</f>
+        <v>14114.193</v>
+      </c>
+      <c r="D15" s="38" t="n">
+        <f aca="false">IFERROR(C15/B15-1,"")</f>
+        <v>-0.0414158516707415</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="B16" s="48" t="n">
+        <f aca="false">'1. Income_Statement'!E17</f>
+        <v>358</v>
+      </c>
+      <c r="C16" s="48" t="n">
+        <f aca="false">B16*(1+'2. Assumptions_FY2025'!B17)</f>
+        <v>358</v>
+      </c>
+      <c r="D16" s="29" t="n">
+        <f aca="false">IFERROR(C16/B16-1,"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="B17" s="48" t="n">
+        <f aca="false">'1. Income_Statement'!E18</f>
+        <v>-1843</v>
+      </c>
+      <c r="C17" s="48" t="n">
+        <f aca="false">('1. Income_Statement'!E19*(1+'2. Assumptions_FY2025'!B18))-C16</f>
+        <v>-1917.25</v>
+      </c>
+      <c r="D17" s="29" t="n">
+        <f aca="false">IFERROR(C17/B17-1,"")</f>
+        <v>0.0402875746066196</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="53" t="s">
-        <v>279</v>
+      <c r="A18" s="37" t="s">
+        <v>91</v>
+      </c>
+      <c r="B18" s="49" t="n">
+        <f aca="false">'1. Income_Statement'!E19</f>
+        <v>-1485</v>
+      </c>
+      <c r="C18" s="27" t="n">
+        <f aca="false">C16+C17</f>
+        <v>-1559.25</v>
+      </c>
+      <c r="D18" s="38" t="n">
+        <f aca="false">IFERROR(C18/B18-1,"")</f>
+        <v>0.05</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="23" t="s">
-        <v>280</v>
-      </c>
-      <c r="B19" s="23" t="s">
-        <v>271</v>
-      </c>
-      <c r="C19" s="23" t="s">
-        <v>281</v>
+      <c r="A19" s="37" t="s">
+        <v>92</v>
+      </c>
+      <c r="B19" s="49" t="n">
+        <f aca="false">'1. Income_Statement'!E20</f>
+        <v>13239</v>
+      </c>
+      <c r="C19" s="27" t="n">
+        <f aca="false">C15+C18</f>
+        <v>12554.943</v>
+      </c>
+      <c r="D19" s="38" t="n">
+        <f aca="false">IFERROR(C19/B19-1,"")</f>
+        <v>-0.0516698391117152</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="24" t="s">
-        <v>73</v>
-      </c>
-      <c r="B20" s="24" t="s">
-        <v>282</v>
-      </c>
-      <c r="C20" s="29" t="n">
-        <f aca="false">B6</f>
-        <v>0.001</v>
+        <v>93</v>
+      </c>
+      <c r="B20" s="48" t="n">
+        <f aca="false">'1. Income_Statement'!E21</f>
+        <v>1249</v>
+      </c>
+      <c r="C20" s="48" t="n">
+        <f aca="false">B20*(1+'2. Assumptions_FY2025'!B19)</f>
+        <v>1348.92</v>
+      </c>
+      <c r="D20" s="29" t="n">
+        <f aca="false">IFERROR(C20/B20-1,"")</f>
+        <v>0.0800000000000001</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="24" t="s">
-        <v>73</v>
-      </c>
-      <c r="B21" s="24" t="s">
-        <v>273</v>
-      </c>
-      <c r="C21" s="29" t="n">
-        <f aca="false">B7</f>
-        <v>0.082</v>
+        <v>94</v>
+      </c>
+      <c r="B21" s="48" t="n">
+        <f aca="false">'1. Income_Statement'!E22</f>
+        <v>-3314</v>
+      </c>
+      <c r="C21" s="48" t="n">
+        <f aca="false">-C19*'2. Assumptions_FY2025'!B20</f>
+        <v>-3013.18632</v>
+      </c>
+      <c r="D21" s="29" t="n">
+        <f aca="false">IFERROR(C21/B21-1,"")</f>
+        <v>-0.0907705733252865</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="24" t="s">
-        <v>73</v>
-      </c>
-      <c r="B22" s="24" t="s">
-        <v>283</v>
-      </c>
-      <c r="C22" s="29" t="n">
-        <f aca="false">B9</f>
-        <v>0.011</v>
+      <c r="A22" s="37" t="s">
+        <v>95</v>
+      </c>
+      <c r="B22" s="49" t="n">
+        <f aca="false">'1. Income_Statement'!E23</f>
+        <v>11174</v>
+      </c>
+      <c r="C22" s="27" t="n">
+        <f aca="false">C19+C20+C21</f>
+        <v>10890.67668</v>
+      </c>
+      <c r="D22" s="38" t="n">
+        <f aca="false">IFERROR(C22/B22-1,"")</f>
+        <v>-0.0253555861822085</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="24" t="s">
-        <v>73</v>
-      </c>
-      <c r="B23" s="24" t="s">
-        <v>284</v>
-      </c>
-      <c r="C23" s="29" t="n">
-        <f aca="false">B10</f>
-        <v>-0.009</v>
+        <v>96</v>
+      </c>
+      <c r="B23" s="48" t="n">
+        <f aca="false">'1. Income_Statement'!E24</f>
+        <v>290</v>
+      </c>
+      <c r="C23" s="48" t="n">
+        <f aca="false">C22*'2. Assumptions_FY2025'!B21</f>
+        <v>283.15759368</v>
+      </c>
+      <c r="D23" s="29" t="n">
+        <f aca="false">IFERROR(C23/B23-1,"")</f>
+        <v>-0.023594504551724</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="24" t="s">
-        <v>73</v>
-      </c>
-      <c r="B24" s="24" t="s">
-        <v>275</v>
-      </c>
-      <c r="C24" s="29" t="n">
-        <f aca="false">B11</f>
-        <v>0.085</v>
+      <c r="A24" s="37" t="s">
+        <v>97</v>
+      </c>
+      <c r="B24" s="49" t="n">
+        <f aca="false">'1. Income_Statement'!E25</f>
+        <v>10884</v>
+      </c>
+      <c r="C24" s="27" t="n">
+        <f aca="false">C22-C23</f>
+        <v>10607.51908632</v>
+      </c>
+      <c r="D24" s="38" t="n">
+        <f aca="false">IFERROR(C24/B24-1,"")</f>
+        <v>-0.0254025095259094</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="24" t="s">
-        <v>75</v>
-      </c>
-      <c r="B25" s="24" t="s">
-        <v>282</v>
-      </c>
-      <c r="C25" s="29" t="n">
-        <f aca="false">C6</f>
-        <v>0.008</v>
-      </c>
+      <c r="A25" s="3"/>
+      <c r="B25" s="3"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="24" t="s">
-        <v>75</v>
-      </c>
-      <c r="B26" s="24" t="s">
-        <v>273</v>
+        <v>98</v>
+      </c>
+      <c r="B26" s="36" t="n">
+        <f aca="false">IFERROR(B11/B5,"")</f>
+        <v>0.171902708146332</v>
       </c>
       <c r="C26" s="29" t="n">
-        <f aca="false">C7</f>
-        <v>0.015</v>
-      </c>
+        <f aca="false">IFERROR(C11/C5,"")</f>
+        <v>0.166</v>
+      </c>
+      <c r="D26" s="3"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="24" t="s">
-        <v>75</v>
-      </c>
-      <c r="B27" s="24" t="s">
-        <v>283</v>
+        <v>99</v>
+      </c>
+      <c r="B27" s="36" t="n">
+        <f aca="false">IFERROR(B13/B5,"")</f>
+        <v>0.160179083565033</v>
       </c>
       <c r="C27" s="29" t="n">
-        <f aca="false">C9</f>
-        <v>-0.003</v>
-      </c>
+        <f aca="false">IFERROR(C13/C5,"")</f>
+        <v>0.152</v>
+      </c>
+      <c r="D27" s="3"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="24" t="s">
-        <v>75</v>
-      </c>
-      <c r="B28" s="24" t="s">
-        <v>284</v>
+        <v>100</v>
+      </c>
+      <c r="B28" s="36" t="n">
+        <f aca="false">IFERROR(B15/B5,"")</f>
+        <v>0.161175208529457</v>
       </c>
       <c r="C28" s="29" t="n">
-        <f aca="false">C10</f>
-        <v>-0.037</v>
-      </c>
+        <f aca="false">IFERROR(C15/C5,"")</f>
+        <v>0.15</v>
+      </c>
+      <c r="D28" s="3"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="24" t="s">
-        <v>75</v>
-      </c>
-      <c r="B29" s="24" t="s">
-        <v>275</v>
+        <v>101</v>
+      </c>
+      <c r="B29" s="36" t="n">
+        <f aca="false">IFERROR(B24/B5,"")</f>
+        <v>0.119140924316396</v>
       </c>
       <c r="C29" s="29" t="n">
-        <f aca="false">C11</f>
-        <v>-0.018</v>
-      </c>
+        <f aca="false">IFERROR(C24/C5,"")</f>
+        <v>0.112732471700507</v>
+      </c>
+      <c r="D29" s="3"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="24" t="s">
-        <v>249</v>
-      </c>
-      <c r="B30" s="24" t="s">
-        <v>285</v>
+        <v>189</v>
+      </c>
+      <c r="B30" s="36" t="n">
+        <f aca="false">IFERROR(-B21/B19,"")</f>
+        <v>0.250321021225168</v>
       </c>
       <c r="C30" s="29" t="n">
-        <f aca="false">D8</f>
-        <v>0.03</v>
-      </c>
+        <f aca="false">IFERROR(-C21/C19,"")</f>
+        <v>0.24</v>
+      </c>
+      <c r="D30" s="3"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="24" t="s">
-        <v>249</v>
-      </c>
-      <c r="B31" s="24" t="s">
-        <v>283</v>
-      </c>
-      <c r="C31" s="29" t="n">
-        <f aca="false">D9</f>
-        <v>0</v>
-      </c>
+      <c r="A31" s="3"/>
+      <c r="B31" s="3"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="24" t="s">
-        <v>249</v>
-      </c>
-      <c r="B32" s="24" t="s">
-        <v>284</v>
-      </c>
-      <c r="C32" s="29" t="n">
-        <f aca="false">D10</f>
-        <v>0</v>
-      </c>
+        <v>276</v>
+      </c>
+      <c r="B32" s="50" t="n">
+        <f aca="false">'1. Income_Statement'!E33</f>
+        <v>4.19</v>
+      </c>
+      <c r="C32" s="51" t="n">
+        <f aca="false">IFERROR(C24/'2. Assumptions_FY2025'!B22,"")</f>
+        <v>4.15215840854895</v>
+      </c>
+      <c r="D32" s="3"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="24" t="s">
-        <v>249</v>
-      </c>
-      <c r="B33" s="24" t="s">
-        <v>275</v>
-      </c>
-      <c r="C33" s="29" t="n">
-        <f aca="false">D11</f>
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="23" t="s">
-        <v>286</v>
-      </c>
-      <c r="B36" s="51"/>
-      <c r="C36" s="51"/>
-      <c r="D36" s="51"/>
-      <c r="E36" s="51"/>
-      <c r="F36" s="51"/>
+      <c r="A33" s="3"/>
+      <c r="B33" s="3"/>
+      <c r="C33" s="3"/>
+      <c r="D33" s="3"/>
+    </row>
+    <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="23" t="s">
+        <v>277</v>
+      </c>
+      <c r="B34" s="47"/>
+      <c r="C34" s="47"/>
+      <c r="D34" s="47"/>
+    </row>
+    <row r="35" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="52" t="s">
+        <v>110</v>
+      </c>
+      <c r="B35" s="3"/>
+      <c r="C35" s="3"/>
+      <c r="D35" s="3"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="24" t="s">
+        <v>278</v>
+      </c>
+      <c r="B36" s="48" t="n">
+        <f aca="false">'1. Cash_Flow_Statement'!E5</f>
+        <v>14724</v>
+      </c>
+      <c r="C36" s="53" t="n">
+        <f aca="false">C15</f>
+        <v>14114.193</v>
+      </c>
+      <c r="D36" s="29" t="n">
+        <f aca="false">IFERROR(C36/B36-1,"")</f>
+        <v>-0.0414158516707415</v>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="23" t="s">
-        <v>247</v>
-      </c>
-      <c r="B37" s="23" t="s">
-        <v>72</v>
-      </c>
-      <c r="C37" s="23" t="s">
-        <v>73</v>
-      </c>
-      <c r="D37" s="23" t="s">
-        <v>74</v>
-      </c>
-      <c r="E37" s="23" t="s">
-        <v>75</v>
-      </c>
-      <c r="F37" s="23" t="s">
-        <v>249</v>
+      <c r="A37" s="24" t="s">
+        <v>112</v>
+      </c>
+      <c r="B37" s="48" t="n">
+        <f aca="false">'1. Cash_Flow_Statement'!E6</f>
+        <v>3582</v>
+      </c>
+      <c r="C37" s="48" t="n">
+        <f aca="false">C5*'2. Assumptions_FY2025'!B25</f>
+        <v>3669.69018</v>
+      </c>
+      <c r="D37" s="29" t="n">
+        <f aca="false">IFERROR(C37/B37-1,"")</f>
+        <v>0.0244807872696817</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="24" t="s">
-        <v>174</v>
-      </c>
-      <c r="B38" s="46" t="n">
-        <f aca="false">-Income_Statement!B6/Income_Statement!B4</f>
-        <v>0.522092595994856</v>
-      </c>
-      <c r="C38" s="46" t="n">
-        <f aca="false">-Income_Statement!C6/Income_Statement!C4</f>
-        <v>0.548006862662035</v>
-      </c>
-      <c r="D38" s="46" t="n">
-        <f aca="false">-Income_Statement!D6/Income_Statement!D4</f>
-        <v>0.541172928450074</v>
-      </c>
-      <c r="E38" s="46" t="n">
-        <f aca="false">-Income_Statement!E6/Income_Statement!E4</f>
-        <v>0.532762659544191</v>
-      </c>
-      <c r="F38" s="46" t="n">
-        <f aca="false">-Budget_FY2025_PL_CF!C7/Budget_FY2025_PL_CF!C5</f>
-        <v>0.529</v>
+        <v>113</v>
+      </c>
+      <c r="B38" s="48" t="n">
+        <f aca="false">'1. Cash_Flow_Statement'!E7</f>
+        <v>580</v>
+      </c>
+      <c r="C38" s="48" t="n">
+        <f aca="false">'2. Assumptions_FY2025'!B26</f>
+        <v>580</v>
+      </c>
+      <c r="D38" s="29" t="n">
+        <f aca="false">IFERROR(C38/B38-1,"")</f>
+        <v>0</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="24" t="s">
-        <v>176</v>
-      </c>
-      <c r="B39" s="46" t="n">
-        <f aca="false">-Income_Statement!B7/Income_Statement!B4</f>
-        <v>0.0909310123093882</v>
-      </c>
-      <c r="C39" s="46" t="n">
-        <f aca="false">-Income_Statement!C7/Income_Statement!C4</f>
-        <v>0.0888121663983733</v>
-      </c>
-      <c r="D39" s="46" t="n">
-        <f aca="false">-Income_Statement!D7/Income_Statement!D4</f>
-        <v>0.0834964192778339</v>
-      </c>
-      <c r="E39" s="46" t="n">
-        <f aca="false">-Income_Statement!E7/Income_Statement!E4</f>
-        <v>0.0828316220417278</v>
-      </c>
-      <c r="F39" s="46" t="n">
-        <f aca="false">-Budget_FY2025_PL_CF!C8/Budget_FY2025_PL_CF!C5</f>
-        <v>0.082</v>
+        <v>279</v>
+      </c>
+      <c r="B39" s="48" t="n">
+        <f aca="false">'1. Cash_Flow_Statement'!E8+'1. Cash_Flow_Statement'!E9</f>
+        <v>-167</v>
+      </c>
+      <c r="C39" s="48" t="n">
+        <f aca="false">'2. Assumptions_FY2025'!B27</f>
+        <v>0</v>
+      </c>
+      <c r="D39" s="29" t="n">
+        <f aca="false">IFERROR(C39/B39-1,"")</f>
+        <v>-1</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="24" t="s">
-        <v>178</v>
-      </c>
-      <c r="B40" s="46" t="n">
-        <f aca="false">-Income_Statement!B8/Income_Statement!B4</f>
-        <v>0.198580745912181</v>
-      </c>
-      <c r="C40" s="46" t="n">
-        <f aca="false">-Income_Statement!C8/Income_Statement!C4</f>
-        <v>0.178450393967635</v>
-      </c>
-      <c r="D40" s="46" t="n">
-        <f aca="false">-Income_Statement!D8/Income_Statement!D4</f>
-        <v>0.188702982859846</v>
-      </c>
-      <c r="E40" s="46" t="n">
-        <f aca="false">-Income_Statement!E8/Income_Statement!E4</f>
-        <v>0.198261707204939</v>
-      </c>
-      <c r="F40" s="46" t="n">
-        <f aca="false">-Budget_FY2025_PL_CF!C9/Budget_FY2025_PL_CF!C5</f>
-        <v>0.209</v>
+      <c r="A40" s="37" t="s">
+        <v>116</v>
+      </c>
+      <c r="B40" s="49" t="n">
+        <f aca="false">'1. Cash_Flow_Statement'!E10</f>
+        <v>18719</v>
+      </c>
+      <c r="C40" s="27" t="n">
+        <f aca="false">SUM(C36:C39)</f>
+        <v>18363.88318</v>
+      </c>
+      <c r="D40" s="38" t="n">
+        <f aca="false">IFERROR(C40/B40-1,"")</f>
+        <v>-0.0189709290026174</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="24" t="s">
-        <v>180</v>
-      </c>
-      <c r="B41" s="46" t="n">
-        <f aca="false">-Income_Statement!B9/Income_Statement!B4</f>
-        <v>0.0191760058791108</v>
-      </c>
-      <c r="C41" s="46" t="n">
-        <f aca="false">-Income_Statement!C9/Income_Statement!C4</f>
-        <v>0.0179615352029145</v>
-      </c>
-      <c r="D41" s="46" t="n">
-        <f aca="false">-Income_Statement!D9/Income_Statement!D4</f>
-        <v>0.0178068345555818</v>
-      </c>
-      <c r="E41" s="46" t="n">
-        <f aca="false">-Income_Statement!E9/Income_Statement!E4</f>
-        <v>0.018247695776868</v>
-      </c>
-      <c r="F41" s="46" t="n">
-        <f aca="false">-Budget_FY2025_PL_CF!C10/Budget_FY2025_PL_CF!C5</f>
-        <v>0.018</v>
+        <v>280</v>
+      </c>
+      <c r="B41" s="48" t="n">
+        <f aca="false">'1. Cash_Flow_Statement'!E11+'1. Cash_Flow_Statement'!E12</f>
+        <v>874</v>
+      </c>
+      <c r="C41" s="48" t="n">
+        <f aca="false">'2. Assumptions_FY2025'!B28</f>
+        <v>0</v>
+      </c>
+      <c r="D41" s="29" t="n">
+        <f aca="false">IFERROR(C41/B41-1,"")</f>
+        <v>-1</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="43" t="s">
-        <v>98</v>
-      </c>
-      <c r="B42" s="45" t="n">
-        <f aca="false">Income_Statement!B27</f>
-        <v>0.173606007716333</v>
-      </c>
-      <c r="C42" s="45" t="n">
-        <f aca="false">Income_Statement!C27</f>
-        <v>0.170539269677201</v>
-      </c>
-      <c r="D42" s="45" t="n">
-        <f aca="false">Income_Statement!D27</f>
-        <v>0.172616615411084</v>
-      </c>
-      <c r="E42" s="45" t="n">
-        <f aca="false">Income_Statement!E27</f>
-        <v>0.171902708146332</v>
-      </c>
-      <c r="F42" s="45" t="n">
-        <f aca="false">Budget_FY2025_PL_CF!C26</f>
-        <v>0.166</v>
+      <c r="A42" s="37" t="s">
+        <v>119</v>
+      </c>
+      <c r="B42" s="49" t="n">
+        <f aca="false">'1. Cash_Flow_Statement'!E13</f>
+        <v>19593</v>
+      </c>
+      <c r="C42" s="27" t="n">
+        <f aca="false">C40+C41</f>
+        <v>18363.88318</v>
+      </c>
+      <c r="D42" s="38" t="n">
+        <f aca="false">IFERROR(C42/B42-1,"")</f>
+        <v>-0.0627324462818352</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="24" t="s">
-        <v>184</v>
-      </c>
-      <c r="B43" s="46" t="n">
-        <f aca="false">(Income_Statement!B11+Income_Statement!B12)/Income_Statement!B4</f>
-        <v>-0.033988609222855</v>
-      </c>
-      <c r="C43" s="46" t="n">
-        <f aca="false">(Income_Statement!C11+Income_Statement!C12)/Income_Statement!C4</f>
-        <v>-0.030797254935186</v>
-      </c>
-      <c r="D43" s="46" t="n">
-        <f aca="false">(Income_Statement!D11+Income_Statement!D12)/Income_Statement!D4</f>
-        <v>-0.0164842254672144</v>
-      </c>
-      <c r="E43" s="46" t="n">
-        <f aca="false">(Income_Statement!E11+Income_Statement!E12)/Income_Statement!E4</f>
-        <v>-0.0117236245812991</v>
-      </c>
-      <c r="F43" s="46" t="n">
-        <f aca="false">Budget_FY2025_PL_CF!C12/Budget_FY2025_PL_CF!C5</f>
-        <v>-0.014</v>
+        <v>120</v>
+      </c>
+      <c r="B43" s="48" t="n">
+        <f aca="false">'1. Cash_Flow_Statement'!E14</f>
+        <v>-1539</v>
+      </c>
+      <c r="C43" s="48" t="n">
+        <f aca="false">C17*'2. Assumptions_FY2025'!B29</f>
+        <v>-1600.90375</v>
+      </c>
+      <c r="D43" s="29" t="n">
+        <f aca="false">IFERROR(C43/B43-1,"")</f>
+        <v>0.0402233593242365</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="43" t="s">
-        <v>99</v>
-      </c>
-      <c r="B44" s="45" t="n">
-        <f aca="false">Income_Statement!B28</f>
-        <v>0.139617398493478</v>
-      </c>
-      <c r="C44" s="45" t="n">
-        <f aca="false">Income_Statement!C28</f>
-        <v>0.139742014742015</v>
-      </c>
-      <c r="D44" s="45" t="n">
-        <f aca="false">Income_Statement!D28</f>
-        <v>0.15613238994387</v>
-      </c>
-      <c r="E44" s="45" t="n">
-        <f aca="false">Income_Statement!E28</f>
-        <v>0.160179083565033</v>
-      </c>
-      <c r="F44" s="45" t="n">
-        <f aca="false">Budget_FY2025_PL_CF!C27</f>
-        <v>0.152</v>
+      <c r="A44" s="24" t="s">
+        <v>121</v>
+      </c>
+      <c r="B44" s="48" t="n">
+        <f aca="false">'1. Cash_Flow_Statement'!E15</f>
+        <v>273</v>
+      </c>
+      <c r="C44" s="48" t="n">
+        <f aca="false">C16*'2. Assumptions_FY2025'!B30</f>
+        <v>273.154</v>
+      </c>
+      <c r="D44" s="29" t="n">
+        <f aca="false">IFERROR(C44/B44-1,"")</f>
+        <v>0.000564102564102553</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="24" t="s">
-        <v>186</v>
-      </c>
-      <c r="B45" s="46" t="n">
-        <f aca="false">(Income_Statement!B14+Income_Statement!B15)/Income_Statement!B4</f>
-        <v>-0.00551166636046298</v>
-      </c>
-      <c r="C45" s="46" t="n">
-        <f aca="false">(Income_Statement!C14+Income_Statement!C15)/Income_Statement!C4</f>
-        <v>-0.00920316868592731</v>
-      </c>
-      <c r="D45" s="46" t="n">
-        <f aca="false">(Income_Statement!D14+Income_Statement!D15)/Income_Statement!D4</f>
-        <v>-0.0049140841738532</v>
-      </c>
-      <c r="E45" s="46" t="n">
-        <f aca="false">(Income_Statement!E14+Income_Statement!E15)/Income_Statement!E4</f>
-        <v>0.000996124964424108</v>
-      </c>
-      <c r="F45" s="46" t="n">
-        <f aca="false">Budget_FY2025_PL_CF!C14/Budget_FY2025_PL_CF!C5</f>
-        <v>-0.002</v>
+        <v>122</v>
+      </c>
+      <c r="B45" s="48" t="n">
+        <f aca="false">'1. Cash_Flow_Statement'!E16</f>
+        <v>-2411</v>
+      </c>
+      <c r="C45" s="48" t="n">
+        <f aca="false">C21*'2. Assumptions_FY2025'!B31</f>
+        <v>-2190.58645464</v>
+      </c>
+      <c r="D45" s="29" t="n">
+        <f aca="false">IFERROR(C45/B45-1,"")</f>
+        <v>-0.0914199690418912</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="43" t="s">
-        <v>100</v>
-      </c>
-      <c r="B46" s="45" t="n">
-        <f aca="false">Income_Statement!B29</f>
-        <v>0.134105732133015</v>
-      </c>
-      <c r="C46" s="45" t="n">
-        <f aca="false">Income_Statement!C29</f>
-        <v>0.130538846056087</v>
-      </c>
-      <c r="D46" s="45" t="n">
-        <f aca="false">Income_Statement!D29</f>
-        <v>0.151218305770017</v>
-      </c>
-      <c r="E46" s="45" t="n">
-        <f aca="false">Income_Statement!E29</f>
-        <v>0.161175208529457</v>
-      </c>
-      <c r="F46" s="45" t="n">
-        <f aca="false">Budget_FY2025_PL_CF!C28</f>
-        <v>0.15</v>
+      <c r="A46" s="24" t="s">
+        <v>123</v>
+      </c>
+      <c r="B46" s="48" t="n">
+        <f aca="false">'1. Cash_Flow_Statement'!E17</f>
+        <v>759</v>
+      </c>
+      <c r="C46" s="48" t="n">
+        <f aca="false">C20*'2. Assumptions_FY2025'!B32</f>
+        <v>820.14336</v>
+      </c>
+      <c r="D46" s="29" t="n">
+        <f aca="false">IFERROR(C46/B46-1,"")</f>
+        <v>0.0805577865612648</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="24" t="s">
-        <v>287</v>
-      </c>
-      <c r="B47" s="46" t="n">
-        <f aca="false">-Income_Statement!B19/Income_Statement!B4</f>
-        <v>0.010024343193092</v>
-      </c>
-      <c r="C47" s="46" t="n">
-        <f aca="false">-Income_Statement!C19/Income_Statement!C4</f>
-        <v>0.0110141489451834</v>
-      </c>
-      <c r="D47" s="46" t="n">
-        <f aca="false">-Income_Statement!D19/Income_Statement!D4</f>
-        <v>0.0146239704079658</v>
-      </c>
-      <c r="E47" s="46" t="n">
-        <f aca="false">-Income_Statement!E19/Income_Statement!E4</f>
-        <v>0.0162554458480198</v>
-      </c>
-      <c r="F47" s="46" t="n">
-        <f aca="false">-Budget_FY2025_PL_CF!C18/Budget_FY2025_PL_CF!C5</f>
-        <v>0.0165710855732241</v>
+      <c r="A47" s="37" t="s">
+        <v>124</v>
+      </c>
+      <c r="B47" s="49" t="n">
+        <f aca="false">'1. Cash_Flow_Statement'!E18</f>
+        <v>16675</v>
+      </c>
+      <c r="C47" s="27" t="n">
+        <f aca="false">C42+C43+C44+C45+C46</f>
+        <v>15665.69033536</v>
+      </c>
+      <c r="D47" s="38" t="n">
+        <f aca="false">IFERROR(C47/B47-1,"")</f>
+        <v>-0.0605283157205396</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="24" t="s">
-        <v>194</v>
-      </c>
-      <c r="B48" s="46" t="n">
-        <f aca="false">Income_Statement!B31</f>
-        <v>0.209235609846382</v>
-      </c>
-      <c r="C48" s="46" t="n">
-        <f aca="false">Income_Statement!C31</f>
-        <v>0.241892610313663</v>
-      </c>
-      <c r="D48" s="46" t="n">
-        <f aca="false">Income_Statement!D31</f>
-        <v>0.182161694088011</v>
-      </c>
-      <c r="E48" s="46" t="n">
-        <f aca="false">Income_Statement!E31</f>
-        <v>0.250321021225168</v>
-      </c>
-      <c r="F48" s="46" t="n">
-        <f aca="false">Budget_FY2025_PL_CF!C30</f>
-        <v>0.24</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="43" t="s">
-        <v>101</v>
-      </c>
-      <c r="B49" s="45" t="n">
-        <f aca="false">Income_Statement!B30</f>
-        <v>0.194113999632556</v>
-      </c>
-      <c r="C49" s="45" t="n">
-        <f aca="false">Income_Statement!C30</f>
-        <v>0.0981741930017792</v>
-      </c>
-      <c r="D49" s="45" t="n">
-        <f aca="false">Income_Statement!D30</f>
-        <v>0.120529473752124</v>
-      </c>
-      <c r="E49" s="45" t="n">
-        <f aca="false">Income_Statement!E30</f>
-        <v>0.119140924316396</v>
-      </c>
-      <c r="F49" s="45" t="n">
-        <f aca="false">Budget_FY2025_PL_CF!C29</f>
-        <v>0.112732471700507</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="31" t="s">
-        <v>288</v>
+      <c r="A48" s="3"/>
+      <c r="B48" s="3"/>
+      <c r="C48" s="3"/>
+      <c r="D48" s="3"/>
+    </row>
+    <row r="49" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="52" t="s">
+        <v>125</v>
+      </c>
+      <c r="B49" s="3"/>
+      <c r="C49" s="3"/>
+      <c r="D49" s="3"/>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="24" t="s">
+        <v>126</v>
+      </c>
+      <c r="B50" s="48" t="n">
+        <f aca="false">'1. Cash_Flow_Statement'!E21</f>
+        <v>-5638</v>
+      </c>
+      <c r="C50" s="48" t="n">
+        <f aca="false">-C5*'2. Assumptions_FY2025'!B33</f>
+        <v>-5833.86644</v>
+      </c>
+      <c r="D50" s="29" t="n">
+        <f aca="false">IFERROR(C50/B50-1,"")</f>
+        <v>0.0347404114934373</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="24" t="s">
+        <v>127</v>
+      </c>
+      <c r="B51" s="48" t="n">
+        <f aca="false">'1. Cash_Flow_Statement'!E22</f>
+        <v>-325</v>
+      </c>
+      <c r="C51" s="48" t="n">
+        <f aca="false">-C5*'2. Assumptions_FY2025'!B34</f>
+        <v>-376.37848</v>
+      </c>
+      <c r="D51" s="29" t="n">
+        <f aca="false">IFERROR(C51/B51-1,"")</f>
+        <v>0.158087630769231</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="24" t="s">
+        <v>281</v>
+      </c>
+      <c r="B52" s="48" t="n">
+        <f aca="false">'1. Cash_Flow_Statement'!E23+'1. Cash_Flow_Statement'!E24</f>
+        <v>-832</v>
+      </c>
+      <c r="C52" s="48" t="n">
+        <f aca="false">'2. Assumptions_FY2025'!B35</f>
+        <v>0</v>
+      </c>
+      <c r="D52" s="29" t="n">
+        <f aca="false">IFERROR(C52/B52-1,"")</f>
+        <v>-1</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="53" t="s">
-        <v>279</v>
+      <c r="A53" s="24" t="s">
+        <v>130</v>
+      </c>
+      <c r="B53" s="48" t="n">
+        <f aca="false">'1. Cash_Flow_Statement'!E25</f>
+        <v>-532</v>
+      </c>
+      <c r="C53" s="48" t="n">
+        <f aca="false">C5*'2. Assumptions_FY2025'!B36</f>
+        <v>-564.56772</v>
+      </c>
+      <c r="D53" s="29" t="n">
+        <f aca="false">IFERROR(C53/B53-1,"")</f>
+        <v>0.0612175187969926</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="23" t="s">
-        <v>280</v>
-      </c>
-      <c r="B54" s="23" t="s">
-        <v>247</v>
-      </c>
-      <c r="C54" s="23" t="s">
-        <v>281</v>
+      <c r="A54" s="24" t="s">
+        <v>131</v>
+      </c>
+      <c r="B54" s="48" t="n">
+        <f aca="false">'1. Cash_Flow_Statement'!E26</f>
+        <v>0</v>
+      </c>
+      <c r="C54" s="48" t="n">
+        <f aca="false">'2. Assumptions_FY2025'!B37</f>
+        <v>0</v>
+      </c>
+      <c r="D54" s="29" t="str">
+        <f aca="false">IFERROR(C54/B54-1,"")</f>
+        <v/>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="24" t="s">
-        <v>72</v>
-      </c>
-      <c r="B55" s="24" t="s">
-        <v>174</v>
-      </c>
-      <c r="C55" s="29" t="n">
-        <f aca="false">B38</f>
-        <v>0.522092595994856</v>
+        <v>282</v>
+      </c>
+      <c r="B55" s="48" t="n">
+        <f aca="false">'1. Cash_Flow_Statement'!E27+'1. Cash_Flow_Statement'!E28</f>
+        <v>-1297</v>
+      </c>
+      <c r="C55" s="48" t="n">
+        <f aca="false">'2. Assumptions_FY2025'!B38</f>
+        <v>0</v>
+      </c>
+      <c r="D55" s="29" t="n">
+        <f aca="false">IFERROR(C55/B55-1,"")</f>
+        <v>-1</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="24" t="s">
-        <v>73</v>
-      </c>
-      <c r="B56" s="24" t="s">
-        <v>174</v>
-      </c>
-      <c r="C56" s="29" t="n">
-        <f aca="false">C38</f>
-        <v>0.548006862662035</v>
+      <c r="A56" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="B56" s="49" t="n">
+        <f aca="false">'1. Cash_Flow_Statement'!E29</f>
+        <v>-8624</v>
+      </c>
+      <c r="C56" s="27" t="n">
+        <f aca="false">SUM(C50:C55)</f>
+        <v>-6774.81264</v>
+      </c>
+      <c r="D56" s="38" t="n">
+        <f aca="false">IFERROR(C56/B56-1,"")</f>
+        <v>-0.214423395176252</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="24" t="s">
-        <v>74</v>
-      </c>
-      <c r="B57" s="24" t="s">
-        <v>174</v>
-      </c>
-      <c r="C57" s="29" t="n">
-        <f aca="false">D38</f>
-        <v>0.541172928450074</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="24" t="s">
-        <v>75</v>
-      </c>
-      <c r="B58" s="24" t="s">
-        <v>174</v>
-      </c>
-      <c r="C58" s="29" t="n">
-        <f aca="false">E38</f>
-        <v>0.532762659544191</v>
-      </c>
+      <c r="A57" s="3"/>
+      <c r="B57" s="3"/>
+      <c r="C57" s="3"/>
+      <c r="D57" s="3"/>
+    </row>
+    <row r="58" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="52" t="s">
+        <v>135</v>
+      </c>
+      <c r="B58" s="3"/>
+      <c r="C58" s="3"/>
+      <c r="D58" s="3"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="24" t="s">
-        <v>249</v>
-      </c>
-      <c r="B59" s="24" t="s">
-        <v>174</v>
-      </c>
-      <c r="C59" s="29" t="n">
-        <f aca="false">F38</f>
-        <v>0.529</v>
+        <v>136</v>
+      </c>
+      <c r="B59" s="48" t="n">
+        <f aca="false">'1. Cash_Flow_Statement'!E32</f>
+        <v>-7816</v>
+      </c>
+      <c r="C59" s="48" t="n">
+        <f aca="false">B59*(1+'2. Assumptions_FY2025'!B39)</f>
+        <v>-7972.32</v>
+      </c>
+      <c r="D59" s="29" t="n">
+        <f aca="false">IFERROR(C59/B59-1,"")</f>
+        <v>0.02</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="24" t="s">
-        <v>72</v>
-      </c>
-      <c r="B60" s="24" t="s">
-        <v>176</v>
-      </c>
-      <c r="C60" s="29" t="n">
-        <f aca="false">B39</f>
-        <v>0.0909310123093882</v>
+        <v>137</v>
+      </c>
+      <c r="B60" s="48" t="n">
+        <f aca="false">'1. Cash_Flow_Statement'!E33</f>
+        <v>-174</v>
+      </c>
+      <c r="C60" s="48" t="n">
+        <f aca="false">'2. Assumptions_FY2025'!B40</f>
+        <v>-174</v>
+      </c>
+      <c r="D60" s="29" t="n">
+        <f aca="false">IFERROR(C60/B60-1,"")</f>
+        <v>0</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="24" t="s">
-        <v>73</v>
-      </c>
-      <c r="B61" s="24" t="s">
-        <v>176</v>
-      </c>
-      <c r="C61" s="29" t="n">
-        <f aca="false">C39</f>
-        <v>0.0888121663983733</v>
+        <v>138</v>
+      </c>
+      <c r="B61" s="48" t="n">
+        <f aca="false">'1. Cash_Flow_Statement'!E34</f>
+        <v>-27</v>
+      </c>
+      <c r="C61" s="48" t="n">
+        <f aca="false">'2. Assumptions_FY2025'!B41</f>
+        <v>0</v>
+      </c>
+      <c r="D61" s="29" t="n">
+        <f aca="false">IFERROR(C61/B61-1,"")</f>
+        <v>-1</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="24" t="s">
-        <v>74</v>
-      </c>
-      <c r="B62" s="24" t="s">
-        <v>176</v>
-      </c>
-      <c r="C62" s="29" t="n">
-        <f aca="false">D39</f>
-        <v>0.0834964192778339</v>
+        <v>139</v>
+      </c>
+      <c r="B62" s="48" t="n">
+        <f aca="false">'1. Cash_Flow_Statement'!E35</f>
+        <v>-4678</v>
+      </c>
+      <c r="C62" s="48" t="n">
+        <f aca="false">'2. Assumptions_FY2025'!B42</f>
+        <v>0</v>
+      </c>
+      <c r="D62" s="29" t="n">
+        <f aca="false">IFERROR(C62/B62-1,"")</f>
+        <v>-1</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="24" t="s">
-        <v>75</v>
-      </c>
-      <c r="B63" s="24" t="s">
-        <v>176</v>
-      </c>
-      <c r="C63" s="29" t="n">
-        <f aca="false">E39</f>
-        <v>0.0828316220417278</v>
+        <v>140</v>
+      </c>
+      <c r="B63" s="48" t="n">
+        <f aca="false">'1. Cash_Flow_Statement'!E36</f>
+        <v>7992</v>
+      </c>
+      <c r="C63" s="48" t="n">
+        <f aca="false">'2. Assumptions_FY2025'!B43</f>
+        <v>7992</v>
+      </c>
+      <c r="D63" s="29" t="n">
+        <f aca="false">IFERROR(C63/B63-1,"")</f>
+        <v>0</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="24" t="s">
-        <v>249</v>
-      </c>
-      <c r="B64" s="24" t="s">
-        <v>176</v>
-      </c>
-      <c r="C64" s="29" t="n">
-        <f aca="false">F39</f>
-        <v>0.082</v>
+        <v>141</v>
+      </c>
+      <c r="B64" s="48" t="n">
+        <f aca="false">'1. Cash_Flow_Statement'!E37</f>
+        <v>-5055</v>
+      </c>
+      <c r="C64" s="48" t="n">
+        <f aca="false">'2. Assumptions_FY2025'!B44</f>
+        <v>-5055</v>
+      </c>
+      <c r="D64" s="29" t="n">
+        <f aca="false">IFERROR(C64/B64-1,"")</f>
+        <v>0</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="24" t="s">
-        <v>72</v>
-      </c>
-      <c r="B65" s="24" t="s">
-        <v>178</v>
-      </c>
-      <c r="C65" s="29" t="n">
-        <f aca="false">B40</f>
-        <v>0.198580745912181</v>
+        <v>142</v>
+      </c>
+      <c r="B65" s="48" t="n">
+        <f aca="false">'1. Cash_Flow_Statement'!E38</f>
+        <v>2396</v>
+      </c>
+      <c r="C65" s="48" t="n">
+        <f aca="false">'2. Assumptions_FY2025'!B45</f>
+        <v>0</v>
+      </c>
+      <c r="D65" s="29" t="n">
+        <f aca="false">IFERROR(C65/B65-1,"")</f>
+        <v>-1</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="24" t="s">
-        <v>73</v>
-      </c>
-      <c r="B66" s="24" t="s">
-        <v>178</v>
-      </c>
-      <c r="C66" s="29" t="n">
-        <f aca="false">C40</f>
-        <v>0.178450393967635</v>
+      <c r="A66" s="37" t="s">
+        <v>143</v>
+      </c>
+      <c r="B66" s="49" t="n">
+        <f aca="false">'1. Cash_Flow_Statement'!E39</f>
+        <v>-7362</v>
+      </c>
+      <c r="C66" s="27" t="n">
+        <f aca="false">SUM(C59:C65)</f>
+        <v>-5209.32</v>
+      </c>
+      <c r="D66" s="38" t="n">
+        <f aca="false">IFERROR(C66/B66-1,"")</f>
+        <v>-0.29240423797881</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A67" s="24" t="s">
-        <v>74</v>
-      </c>
-      <c r="B67" s="24" t="s">
-        <v>178</v>
-      </c>
-      <c r="C67" s="29" t="n">
-        <f aca="false">D40</f>
-        <v>0.188702982859846</v>
-      </c>
-    </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A68" s="24" t="s">
-        <v>75</v>
-      </c>
-      <c r="B68" s="24" t="s">
-        <v>178</v>
-      </c>
-      <c r="C68" s="29" t="n">
-        <f aca="false">E40</f>
-        <v>0.198261707204939</v>
-      </c>
+      <c r="A67" s="3"/>
+      <c r="B67" s="3"/>
+      <c r="C67" s="3"/>
+      <c r="D67" s="3"/>
+    </row>
+    <row r="68" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="52" t="s">
+        <v>144</v>
+      </c>
+      <c r="B68" s="3"/>
+      <c r="C68" s="3"/>
+      <c r="D68" s="3"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="24" t="s">
-        <v>249</v>
-      </c>
-      <c r="B69" s="24" t="s">
-        <v>178</v>
-      </c>
-      <c r="C69" s="29" t="n">
-        <f aca="false">F40</f>
-        <v>0.209</v>
+        <v>145</v>
+      </c>
+      <c r="B69" s="48" t="n">
+        <f aca="false">'1. Cash_Flow_Statement'!E42</f>
+        <v>53</v>
+      </c>
+      <c r="C69" s="48" t="n">
+        <f aca="false">'2. Assumptions_FY2025'!B46</f>
+        <v>0</v>
+      </c>
+      <c r="D69" s="29" t="n">
+        <f aca="false">IFERROR(C69/B69-1,"")</f>
+        <v>-1</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A70" s="24" t="s">
-        <v>72</v>
-      </c>
-      <c r="B70" s="24" t="s">
-        <v>180</v>
-      </c>
-      <c r="C70" s="29" t="n">
-        <f aca="false">B41</f>
-        <v>0.0191760058791108</v>
+      <c r="A70" s="37" t="s">
+        <v>146</v>
+      </c>
+      <c r="B70" s="49" t="n">
+        <f aca="false">'1. Cash_Flow_Statement'!E43</f>
+        <v>742</v>
+      </c>
+      <c r="C70" s="27" t="n">
+        <f aca="false">C47+C56+C66+C69</f>
+        <v>3681.55769536</v>
+      </c>
+      <c r="D70" s="38" t="n">
+        <f aca="false">IFERROR(C70/B70-1,"")</f>
+        <v>3.96166805304582</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="24" t="s">
-        <v>73</v>
-      </c>
-      <c r="B71" s="24" t="s">
-        <v>180</v>
-      </c>
-      <c r="C71" s="29" t="n">
-        <f aca="false">C41</f>
-        <v>0.0179615352029145</v>
+        <v>147</v>
+      </c>
+      <c r="B71" s="48" t="n">
+        <f aca="false">'1. Cash_Flow_Statement'!E44</f>
+        <v>4816</v>
+      </c>
+      <c r="C71" s="48" t="n">
+        <f aca="false">'1. Cash_Flow_Statement'!E45</f>
+        <v>5558</v>
+      </c>
+      <c r="D71" s="29" t="n">
+        <f aca="false">IFERROR(C71/B71-1,"")</f>
+        <v>0.154069767441861</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A72" s="24" t="s">
-        <v>74</v>
-      </c>
-      <c r="B72" s="24" t="s">
-        <v>180</v>
-      </c>
-      <c r="C72" s="29" t="n">
-        <f aca="false">D41</f>
-        <v>0.0178068345555818</v>
+      <c r="A72" s="37" t="s">
+        <v>148</v>
+      </c>
+      <c r="B72" s="49" t="n">
+        <f aca="false">'1. Cash_Flow_Statement'!E45</f>
+        <v>5558</v>
+      </c>
+      <c r="C72" s="27" t="n">
+        <f aca="false">C70+C71</f>
+        <v>9239.55769536</v>
+      </c>
+      <c r="D72" s="38" t="n">
+        <f aca="false">IFERROR(C72/B72-1,"")</f>
+        <v>0.662388934033825</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="24" t="s">
-        <v>75</v>
-      </c>
-      <c r="B73" s="24" t="s">
-        <v>180</v>
-      </c>
-      <c r="C73" s="29" t="n">
-        <f aca="false">E41</f>
-        <v>0.018247695776868</v>
-      </c>
-    </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A74" s="24" t="s">
-        <v>249</v>
-      </c>
-      <c r="B74" s="24" t="s">
-        <v>180</v>
-      </c>
-      <c r="C74" s="29" t="n">
-        <f aca="false">F41</f>
-        <v>0.018</v>
-      </c>
+      <c r="A73" s="3"/>
+      <c r="B73" s="3"/>
+      <c r="C73" s="3"/>
+      <c r="D73" s="3"/>
+    </row>
+    <row r="74" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A74" s="52" t="s">
+        <v>151</v>
+      </c>
+      <c r="B74" s="3"/>
+      <c r="C74" s="3"/>
+      <c r="D74" s="3"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A75" s="24" t="s">
-        <v>72</v>
-      </c>
-      <c r="B75" s="24" t="s">
-        <v>98</v>
-      </c>
-      <c r="C75" s="29" t="n">
-        <f aca="false">B42</f>
-        <v>0.173606007716333</v>
+      <c r="A75" s="37" t="s">
+        <v>153</v>
+      </c>
+      <c r="B75" s="49" t="n">
+        <f aca="false">'1. Cash_Flow_Statement'!E51</f>
+        <v>10712</v>
+      </c>
+      <c r="C75" s="27" t="n">
+        <f aca="false">C47+C50+C51</f>
+        <v>9455.44541536</v>
+      </c>
+      <c r="D75" s="38" t="n">
+        <f aca="false">IFERROR(C75/B75-1,"")</f>
+        <v>-0.117303452636296</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="24" t="s">
-        <v>73</v>
-      </c>
-      <c r="B76" s="24" t="s">
-        <v>98</v>
+        <v>283</v>
+      </c>
+      <c r="B76" s="36" t="n">
+        <f aca="false">IFERROR(B75/B5,"")</f>
+        <v>0.117258138669352</v>
       </c>
       <c r="C76" s="29" t="n">
-        <f aca="false">C42</f>
-        <v>0.170539269677201</v>
-      </c>
+        <f aca="false">IFERROR(C75/C5,"")</f>
+        <v>0.100488693353138</v>
+      </c>
+      <c r="D76" s="3"/>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A77" s="24" t="s">
-        <v>74</v>
-      </c>
-      <c r="B77" s="24" t="s">
-        <v>98</v>
-      </c>
-      <c r="C77" s="29" t="n">
-        <f aca="false">D42</f>
-        <v>0.172616615411084</v>
-      </c>
-    </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A78" s="24" t="s">
-        <v>75</v>
-      </c>
-      <c r="B78" s="24" t="s">
-        <v>98</v>
-      </c>
-      <c r="C78" s="29" t="n">
-        <f aca="false">E42</f>
-        <v>0.171902708146332</v>
-      </c>
-    </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="24" t="s">
-        <v>249</v>
-      </c>
-      <c r="B79" s="24" t="s">
-        <v>98</v>
-      </c>
-      <c r="C79" s="29" t="n">
-        <f aca="false">F42</f>
-        <v>0.166</v>
-      </c>
-    </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A80" s="24" t="s">
-        <v>72</v>
-      </c>
-      <c r="B80" s="24" t="s">
-        <v>184</v>
-      </c>
-      <c r="C80" s="29" t="n">
-        <f aca="false">B43</f>
-        <v>-0.033988609222855</v>
-      </c>
-    </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A81" s="24" t="s">
-        <v>73</v>
-      </c>
-      <c r="B81" s="24" t="s">
-        <v>184</v>
-      </c>
-      <c r="C81" s="29" t="n">
-        <f aca="false">C43</f>
-        <v>-0.030797254935186</v>
-      </c>
-    </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A82" s="24" t="s">
-        <v>74</v>
-      </c>
-      <c r="B82" s="24" t="s">
-        <v>184</v>
-      </c>
-      <c r="C82" s="29" t="n">
-        <f aca="false">D43</f>
-        <v>-0.0164842254672144</v>
-      </c>
-    </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A83" s="24" t="s">
-        <v>75</v>
-      </c>
-      <c r="B83" s="24" t="s">
-        <v>184</v>
-      </c>
-      <c r="C83" s="29" t="n">
-        <f aca="false">E43</f>
-        <v>-0.0117236245812991</v>
-      </c>
-    </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A84" s="24" t="s">
-        <v>249</v>
-      </c>
-      <c r="B84" s="24" t="s">
-        <v>184</v>
-      </c>
-      <c r="C84" s="29" t="n">
-        <f aca="false">F43</f>
-        <v>-0.014</v>
-      </c>
-    </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A85" s="24" t="s">
-        <v>72</v>
-      </c>
-      <c r="B85" s="24" t="s">
-        <v>99</v>
-      </c>
-      <c r="C85" s="29" t="n">
-        <f aca="false">B44</f>
-        <v>0.139617398493478</v>
-      </c>
-    </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A86" s="24" t="s">
-        <v>73</v>
-      </c>
-      <c r="B86" s="24" t="s">
-        <v>99</v>
-      </c>
-      <c r="C86" s="29" t="n">
-        <f aca="false">C44</f>
-        <v>0.139742014742015</v>
-      </c>
-    </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A87" s="24" t="s">
-        <v>74</v>
-      </c>
-      <c r="B87" s="24" t="s">
-        <v>99</v>
-      </c>
-      <c r="C87" s="29" t="n">
-        <f aca="false">D44</f>
-        <v>0.15613238994387</v>
-      </c>
-    </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A88" s="24" t="s">
-        <v>75</v>
-      </c>
-      <c r="B88" s="24" t="s">
-        <v>99</v>
-      </c>
-      <c r="C88" s="29" t="n">
-        <f aca="false">E44</f>
-        <v>0.160179083565033</v>
-      </c>
-    </row>
-    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A89" s="24" t="s">
-        <v>249</v>
-      </c>
-      <c r="B89" s="24" t="s">
-        <v>99</v>
-      </c>
-      <c r="C89" s="29" t="n">
-        <f aca="false">F44</f>
-        <v>0.152</v>
-      </c>
-    </row>
-    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A90" s="24" t="s">
-        <v>72</v>
-      </c>
-      <c r="B90" s="24" t="s">
-        <v>186</v>
-      </c>
-      <c r="C90" s="29" t="n">
-        <f aca="false">B45</f>
-        <v>-0.00551166636046298</v>
-      </c>
-    </row>
-    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A91" s="24" t="s">
-        <v>73</v>
-      </c>
-      <c r="B91" s="24" t="s">
-        <v>186</v>
-      </c>
-      <c r="C91" s="29" t="n">
-        <f aca="false">C45</f>
-        <v>-0.00920316868592731</v>
-      </c>
-    </row>
-    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A92" s="24" t="s">
-        <v>74</v>
-      </c>
-      <c r="B92" s="24" t="s">
-        <v>186</v>
-      </c>
-      <c r="C92" s="29" t="n">
-        <f aca="false">D45</f>
-        <v>-0.0049140841738532</v>
-      </c>
-    </row>
-    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A93" s="24" t="s">
-        <v>75</v>
-      </c>
-      <c r="B93" s="24" t="s">
-        <v>186</v>
-      </c>
-      <c r="C93" s="29" t="n">
-        <f aca="false">E45</f>
-        <v>0.000996124964424108</v>
-      </c>
-    </row>
-    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A94" s="24" t="s">
-        <v>249</v>
-      </c>
-      <c r="B94" s="24" t="s">
-        <v>186</v>
-      </c>
-      <c r="C94" s="29" t="n">
-        <f aca="false">F45</f>
-        <v>-0.002</v>
-      </c>
-    </row>
-    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A95" s="24" t="s">
-        <v>72</v>
-      </c>
-      <c r="B95" s="24" t="s">
-        <v>100</v>
-      </c>
-      <c r="C95" s="29" t="n">
-        <f aca="false">B46</f>
-        <v>0.134105732133015</v>
-      </c>
-    </row>
-    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A96" s="24" t="s">
-        <v>73</v>
-      </c>
-      <c r="B96" s="24" t="s">
-        <v>100</v>
-      </c>
-      <c r="C96" s="29" t="n">
-        <f aca="false">C46</f>
-        <v>0.130538846056087</v>
-      </c>
-    </row>
-    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A97" s="24" t="s">
-        <v>74</v>
-      </c>
-      <c r="B97" s="24" t="s">
-        <v>100</v>
-      </c>
-      <c r="C97" s="29" t="n">
-        <f aca="false">D46</f>
-        <v>0.151218305770017</v>
-      </c>
-    </row>
-    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A98" s="24" t="s">
-        <v>75</v>
-      </c>
-      <c r="B98" s="24" t="s">
-        <v>100</v>
-      </c>
-      <c r="C98" s="29" t="n">
-        <f aca="false">E46</f>
-        <v>0.161175208529457</v>
-      </c>
-    </row>
-    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A99" s="24" t="s">
-        <v>249</v>
-      </c>
-      <c r="B99" s="24" t="s">
-        <v>100</v>
-      </c>
-      <c r="C99" s="29" t="n">
-        <f aca="false">F46</f>
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A100" s="24" t="s">
-        <v>72</v>
-      </c>
-      <c r="B100" s="24" t="s">
+      <c r="A77" s="3"/>
+      <c r="B77" s="3"/>
+      <c r="C77" s="3"/>
+      <c r="D77" s="3"/>
+    </row>
+    <row r="78" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A78" s="31" t="s">
+        <v>284</v>
+      </c>
+      <c r="B78" s="3"/>
+      <c r="C78" s="3"/>
+      <c r="D78" s="3"/>
+    </row>
+    <row r="79" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A79" s="31" t="s">
+        <v>285</v>
+      </c>
+      <c r="B79" s="3"/>
+      <c r="C79" s="3"/>
+      <c r="D79" s="3"/>
+    </row>
+    <row r="80" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A80" s="31" t="s">
+        <v>286</v>
+      </c>
+      <c r="B80" s="3"/>
+      <c r="C80" s="3"/>
+      <c r="D80" s="3"/>
+    </row>
+    <row r="81" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A81" s="31" t="s">
         <v>287</v>
       </c>
-      <c r="C100" s="29" t="n">
-        <f aca="false">B47</f>
-        <v>0.010024343193092</v>
-      </c>
-    </row>
-    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A101" s="24" t="s">
-        <v>73</v>
-      </c>
-      <c r="B101" s="24" t="s">
-        <v>287</v>
-      </c>
-      <c r="C101" s="29" t="n">
-        <f aca="false">C47</f>
-        <v>0.0110141489451834</v>
-      </c>
-    </row>
-    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A102" s="24" t="s">
-        <v>74</v>
-      </c>
-      <c r="B102" s="24" t="s">
-        <v>287</v>
-      </c>
-      <c r="C102" s="29" t="n">
-        <f aca="false">D47</f>
-        <v>0.0146239704079658</v>
-      </c>
-    </row>
-    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A103" s="24" t="s">
-        <v>75</v>
-      </c>
-      <c r="B103" s="24" t="s">
-        <v>287</v>
-      </c>
-      <c r="C103" s="29" t="n">
-        <f aca="false">E47</f>
-        <v>0.0162554458480198</v>
-      </c>
-    </row>
-    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A104" s="24" t="s">
-        <v>249</v>
-      </c>
-      <c r="B104" s="24" t="s">
-        <v>287</v>
-      </c>
-      <c r="C104" s="29" t="n">
-        <f aca="false">F47</f>
-        <v>0.0165710855732241</v>
-      </c>
-    </row>
-    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A105" s="24" t="s">
-        <v>72</v>
-      </c>
-      <c r="B105" s="24" t="s">
-        <v>194</v>
-      </c>
-      <c r="C105" s="29" t="n">
-        <f aca="false">B48</f>
-        <v>0.209235609846382</v>
-      </c>
-    </row>
-    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A106" s="24" t="s">
-        <v>73</v>
-      </c>
-      <c r="B106" s="24" t="s">
-        <v>194</v>
-      </c>
-      <c r="C106" s="29" t="n">
-        <f aca="false">C48</f>
-        <v>0.241892610313663</v>
-      </c>
-    </row>
-    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A107" s="24" t="s">
-        <v>74</v>
-      </c>
-      <c r="B107" s="24" t="s">
-        <v>194</v>
-      </c>
-      <c r="C107" s="29" t="n">
-        <f aca="false">D48</f>
-        <v>0.182161694088011</v>
-      </c>
-    </row>
-    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A108" s="24" t="s">
-        <v>75</v>
-      </c>
-      <c r="B108" s="24" t="s">
-        <v>194</v>
-      </c>
-      <c r="C108" s="29" t="n">
-        <f aca="false">E48</f>
-        <v>0.250321021225168</v>
-      </c>
-    </row>
-    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A109" s="24" t="s">
-        <v>249</v>
-      </c>
-      <c r="B109" s="24" t="s">
-        <v>194</v>
-      </c>
-      <c r="C109" s="29" t="n">
-        <f aca="false">F48</f>
-        <v>0.24</v>
-      </c>
-    </row>
-    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A110" s="24" t="s">
-        <v>72</v>
-      </c>
-      <c r="B110" s="24" t="s">
-        <v>101</v>
-      </c>
-      <c r="C110" s="29" t="n">
-        <f aca="false">B49</f>
-        <v>0.194113999632556</v>
-      </c>
-    </row>
-    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A111" s="24" t="s">
-        <v>73</v>
-      </c>
-      <c r="B111" s="24" t="s">
-        <v>101</v>
-      </c>
-      <c r="C111" s="29" t="n">
-        <f aca="false">C49</f>
-        <v>0.0981741930017792</v>
-      </c>
-    </row>
-    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A112" s="24" t="s">
-        <v>74</v>
-      </c>
-      <c r="B112" s="24" t="s">
-        <v>101</v>
-      </c>
-      <c r="C112" s="29" t="n">
-        <f aca="false">D49</f>
-        <v>0.120529473752124</v>
-      </c>
-    </row>
-    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A113" s="24" t="s">
-        <v>75</v>
-      </c>
-      <c r="B113" s="24" t="s">
-        <v>101</v>
-      </c>
-      <c r="C113" s="29" t="n">
-        <f aca="false">E49</f>
-        <v>0.119140924316396</v>
-      </c>
-    </row>
-    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A114" s="24" t="s">
-        <v>249</v>
-      </c>
-      <c r="B114" s="24" t="s">
-        <v>101</v>
-      </c>
-      <c r="C114" s="29" t="n">
-        <f aca="false">F49</f>
-        <v>0.112732471700507</v>
-      </c>
+      <c r="B81" s="3"/>
+      <c r="C81" s="3"/>
+      <c r="D81" s="3"/>
+    </row>
+    <row r="82" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A82" s="31" t="s">
+        <v>288</v>
+      </c>
+      <c r="B82" s="3"/>
+      <c r="C82" s="3"/>
+      <c r="D82" s="3"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
